--- a/bodegas/02.xlsx
+++ b/bodegas/02.xlsx
@@ -15023,10 +15023,10 @@
         <v>50</v>
       </c>
       <c r="N335" t="n">
-        <v>4242.3899305556</v>
+        <v>4193.85</v>
       </c>
       <c r="O335" t="n">
-        <v>212119.49652778</v>
+        <v>209692.5</v>
       </c>
       <c r="P335" t="n">
         <v>7500</v>
@@ -24561,10 +24561,10 @@
         <v>10</v>
       </c>
       <c r="N551" t="n">
-        <v>5234.4433367983</v>
+        <v>5218.1704573805</v>
       </c>
       <c r="O551" t="n">
-        <v>52344.433367983</v>
+        <v>52181.704573805</v>
       </c>
       <c r="P551" t="n">
         <v>8500</v>
@@ -24929,10 +24929,10 @@
         <v>5</v>
       </c>
       <c r="N559" t="n">
-        <v>1821.7243939394</v>
+        <v>1812.57</v>
       </c>
       <c r="O559" t="n">
-        <v>9108.621969697</v>
+        <v>9062.85</v>
       </c>
       <c r="P559" t="n">
         <v>2900</v>
@@ -34360,10 +34360,10 @@
         <v>326</v>
       </c>
       <c r="N763" t="n">
-        <v>2861.1357880311</v>
+        <v>2857.22</v>
       </c>
       <c r="O763" t="n">
-        <v>932730.2668981387</v>
+        <v>931453.72</v>
       </c>
       <c r="P763" t="n">
         <v>4900</v>

--- a/bodegas/02.xlsx
+++ b/bodegas/02.xlsx
@@ -895,10 +895,10 @@
         <v>3</v>
       </c>
       <c r="N12" t="n">
-        <v>27225.941422594</v>
+        <v>27000</v>
       </c>
       <c r="O12" t="n">
-        <v>81677.82426778201</v>
+        <v>81000</v>
       </c>
       <c r="P12" t="n">
         <v>30000</v>
@@ -1051,10 +1051,10 @@
         <v>10</v>
       </c>
       <c r="N16" t="n">
-        <v>5784.4419026549</v>
+        <v>5758.9597787611</v>
       </c>
       <c r="O16" t="n">
-        <v>57844.419026549</v>
+        <v>57589.597787611</v>
       </c>
       <c r="P16" t="n">
         <v>16900</v>
@@ -1857,10 +1857,10 @@
         <v>12</v>
       </c>
       <c r="N36" t="n">
-        <v>2421.5176470588</v>
+        <v>2413.0011764706</v>
       </c>
       <c r="O36" t="n">
-        <v>29058.2117647056</v>
+        <v>28956.0141176472</v>
       </c>
       <c r="P36" t="n">
         <v>4700</v>
@@ -1896,10 +1896,10 @@
         <v>15</v>
       </c>
       <c r="N37" t="n">
-        <v>2487.0572046589</v>
+        <v>2474.7042429285</v>
       </c>
       <c r="O37" t="n">
-        <v>37305.8580698835</v>
+        <v>37120.5636439275</v>
       </c>
       <c r="P37" t="n">
         <v>4500</v>
@@ -2208,10 +2208,10 @@
         <v>4</v>
       </c>
       <c r="N45" t="n">
-        <v>21510.733070539</v>
+        <v>21333.69</v>
       </c>
       <c r="O45" t="n">
-        <v>86042.93228215601</v>
+        <v>85334.75999999999</v>
       </c>
       <c r="P45" t="n">
         <v>30000</v>
@@ -3431,10 +3431,10 @@
         <v>1</v>
       </c>
       <c r="N73" t="n">
-        <v>15834.716054688</v>
+        <v>15711.966289063</v>
       </c>
       <c r="O73" t="n">
-        <v>15834.716054688</v>
+        <v>15711.966289063</v>
       </c>
       <c r="P73" t="n">
         <v>28500</v>
@@ -5178,10 +5178,10 @@
         <v>11</v>
       </c>
       <c r="N114" t="n">
-        <v>27232.75862069</v>
+        <v>27000</v>
       </c>
       <c r="O114" t="n">
-        <v>299560.34482759</v>
+        <v>297000</v>
       </c>
       <c r="P114" t="n">
         <v>20000</v>
@@ -6465,10 +6465,10 @@
         <v>1</v>
       </c>
       <c r="N144" t="n">
-        <v>2576.9026455026</v>
+        <v>2563.34</v>
       </c>
       <c r="O144" t="n">
-        <v>2576.9026455026</v>
+        <v>2563.34</v>
       </c>
       <c r="P144" t="n">
         <v>4700</v>
@@ -6553,10 +6553,10 @@
         <v>7</v>
       </c>
       <c r="N146" t="n">
-        <v>11705.0765</v>
+        <v>11513.19</v>
       </c>
       <c r="O146" t="n">
-        <v>81935.5355</v>
+        <v>80592.33</v>
       </c>
       <c r="P146" t="n">
         <v>17900</v>
@@ -10871,10 +10871,10 @@
         <v>17</v>
       </c>
       <c r="N242" t="n">
-        <v>13624.59908046</v>
+        <v>13593.35</v>
       </c>
       <c r="O242" t="n">
-        <v>231618.18436782</v>
+        <v>231086.95</v>
       </c>
       <c r="P242" t="n">
         <v>25500</v>
@@ -17201,10 +17201,10 @@
         <v>6</v>
       </c>
       <c r="N383" t="n">
-        <v>11658.147712418</v>
+        <v>11507.72</v>
       </c>
       <c r="O383" t="n">
-        <v>69948.886274508</v>
+        <v>69046.31999999999</v>
       </c>
       <c r="P383" t="n">
         <v>25800</v>
@@ -19428,10 +19428,10 @@
         <v>22</v>
       </c>
       <c r="N433" t="n">
-        <v>4508.1255605381</v>
+        <v>4488</v>
       </c>
       <c r="O433" t="n">
-        <v>99178.76233183821</v>
+        <v>98736</v>
       </c>
       <c r="P433" t="n">
         <v>6200</v>
@@ -21613,10 +21613,10 @@
         <v>9</v>
       </c>
       <c r="N484" t="n">
-        <v>5453.6557676349</v>
+        <v>5431.12</v>
       </c>
       <c r="O484" t="n">
-        <v>49082.90190871411</v>
+        <v>48880.08</v>
       </c>
       <c r="P484" t="n">
         <v>8900</v>
@@ -21792,10 +21792,10 @@
         <v>13</v>
       </c>
       <c r="N488" t="n">
-        <v>27226.972222222</v>
+        <v>26854</v>
       </c>
       <c r="O488" t="n">
-        <v>353950.638888886</v>
+        <v>349102</v>
       </c>
       <c r="P488" t="n">
         <v>43900</v>
@@ -24127,10 +24127,10 @@
         <v>8</v>
       </c>
       <c r="N541" t="n">
-        <v>9099.032608695699</v>
+        <v>8878.450000000001</v>
       </c>
       <c r="O541" t="n">
-        <v>72792.26086956559</v>
+        <v>71027.60000000001</v>
       </c>
       <c r="P541" t="n">
         <v>14100</v>
@@ -24173,10 +24173,10 @@
         <v>8</v>
       </c>
       <c r="N542" t="n">
-        <v>2498.7228351648</v>
+        <v>2495.98</v>
       </c>
       <c r="O542" t="n">
-        <v>19989.7826813184</v>
+        <v>19967.84</v>
       </c>
       <c r="P542" t="n">
         <v>4100</v>
@@ -24449,10 +24449,10 @@
         <v>9</v>
       </c>
       <c r="N548" t="n">
-        <v>3969.9272029703</v>
+        <v>3965.02</v>
       </c>
       <c r="O548" t="n">
-        <v>35729.3448267327</v>
+        <v>35685.18</v>
       </c>
       <c r="P548" t="n">
         <v>6500</v>
@@ -24541,10 +24541,10 @@
         <v>4</v>
       </c>
       <c r="N550" t="n">
-        <v>22317.65</v>
+        <v>17358.17</v>
       </c>
       <c r="O550" t="n">
-        <v>89270.60000000001</v>
+        <v>69432.67999999999</v>
       </c>
       <c r="P550" t="n">
         <v>24500</v>
@@ -24633,10 +24633,10 @@
         <v>5</v>
       </c>
       <c r="N552" t="n">
-        <v>1817.3525065963</v>
+        <v>1812.57</v>
       </c>
       <c r="O552" t="n">
-        <v>9086.7625329815</v>
+        <v>9062.85</v>
       </c>
       <c r="P552" t="n">
         <v>2900</v>
@@ -25604,10 +25604,10 @@
         <v>8</v>
       </c>
       <c r="N573" t="n">
-        <v>16092.045229682</v>
+        <v>16058</v>
       </c>
       <c r="O573" t="n">
-        <v>128736.361837456</v>
+        <v>128464</v>
       </c>
       <c r="P573" t="n">
         <v>25900</v>
@@ -27965,10 +27965,10 @@
         <v>4</v>
       </c>
       <c r="N624" t="n">
-        <v>9368.9914285714</v>
+        <v>7715.64</v>
       </c>
       <c r="O624" t="n">
-        <v>37475.9657142856</v>
+        <v>30862.56</v>
       </c>
       <c r="P624" t="n">
         <v>9900</v>
@@ -28106,10 +28106,10 @@
         <v>10</v>
       </c>
       <c r="N627" t="n">
-        <v>21748.414253898</v>
+        <v>21676</v>
       </c>
       <c r="O627" t="n">
-        <v>217484.14253898</v>
+        <v>216760</v>
       </c>
       <c r="P627" t="n">
         <v>34900</v>
@@ -29814,10 +29814,10 @@
         <v>6</v>
       </c>
       <c r="N664" t="n">
-        <v>27422.4</v>
+        <v>27186</v>
       </c>
       <c r="O664" t="n">
-        <v>164534.4</v>
+        <v>163116</v>
       </c>
       <c r="P664" t="n">
         <v>43900</v>
@@ -29952,10 +29952,10 @@
         <v>12</v>
       </c>
       <c r="N667" t="n">
-        <v>3903.9739463602</v>
+        <v>3898</v>
       </c>
       <c r="O667" t="n">
-        <v>46847.6873563224</v>
+        <v>46776</v>
       </c>
       <c r="P667" t="n">
         <v>6900</v>
@@ -29998,10 +29998,10 @@
         <v>27</v>
       </c>
       <c r="N668" t="n">
-        <v>13585.460030166</v>
+        <v>13565</v>
       </c>
       <c r="O668" t="n">
-        <v>366807.420814482</v>
+        <v>366255</v>
       </c>
       <c r="P668" t="n">
         <v>22500</v>
@@ -31328,10 +31328,10 @@
         <v>37</v>
       </c>
       <c r="N697" t="n">
-        <v>3647.235915493</v>
+        <v>3639.35</v>
       </c>
       <c r="O697" t="n">
-        <v>134947.728873241</v>
+        <v>134655.95</v>
       </c>
       <c r="P697" t="n">
         <v>7500</v>
@@ -31466,10 +31466,10 @@
         <v>11</v>
       </c>
       <c r="N700" t="n">
-        <v>10816.221634615</v>
+        <v>10713.21</v>
       </c>
       <c r="O700" t="n">
-        <v>118978.437980765</v>
+        <v>117845.31</v>
       </c>
       <c r="P700" t="n">
         <v>20900</v>
@@ -31512,10 +31512,10 @@
         <v>9</v>
       </c>
       <c r="N701" t="n">
-        <v>12664.079439252</v>
+        <v>12489</v>
       </c>
       <c r="O701" t="n">
-        <v>113976.714953268</v>
+        <v>112401</v>
       </c>
       <c r="P701" t="n">
         <v>20900</v>
@@ -39693,10 +39693,10 @@
         <v>17</v>
       </c>
       <c r="N877" t="n">
-        <v>8330.0435897436</v>
+        <v>7923.7</v>
       </c>
       <c r="O877" t="n">
-        <v>141610.7410256412</v>
+        <v>134702.9</v>
       </c>
       <c r="P877" t="n">
         <v>16600</v>
@@ -41289,10 +41289,10 @@
         <v>6</v>
       </c>
       <c r="N910" t="n">
-        <v>2870.9917808219</v>
+        <v>2832.1946575342</v>
       </c>
       <c r="O910" t="n">
-        <v>17225.9506849314</v>
+        <v>16993.1679452052</v>
       </c>
       <c r="P910" t="n">
         <v>12900</v>
@@ -42294,10 +42294,10 @@
         <v>12</v>
       </c>
       <c r="N931" t="n">
-        <v>10649.1</v>
+        <v>9874.620000000001</v>
       </c>
       <c r="O931" t="n">
-        <v>127789.2</v>
+        <v>118495.44</v>
       </c>
       <c r="P931" t="n">
         <v>14700</v>
@@ -42830,10 +42830,10 @@
         <v>10</v>
       </c>
       <c r="N942" t="n">
-        <v>10020.157196262</v>
+        <v>9746.8801869159</v>
       </c>
       <c r="O942" t="n">
-        <v>100201.57196262</v>
+        <v>97468.801869159</v>
       </c>
       <c r="P942" t="n">
         <v>18500</v>
@@ -44762,10 +44762,10 @@
         <v>5</v>
       </c>
       <c r="N982" t="n">
-        <v>4360.6660810811</v>
+        <v>4190.77</v>
       </c>
       <c r="O982" t="n">
-        <v>21803.3304054055</v>
+        <v>20953.85</v>
       </c>
       <c r="P982" t="n">
         <v>5900</v>
@@ -45587,10 +45587,10 @@
         <v>7</v>
       </c>
       <c r="N999" t="n">
-        <v>6053.1143</v>
+        <v>5876.81</v>
       </c>
       <c r="O999" t="n">
-        <v>42371.8001</v>
+        <v>41137.67000000001</v>
       </c>
       <c r="P999" t="n">
         <v>22900</v>
@@ -47603,10 +47603,10 @@
         <v>9</v>
       </c>
       <c r="N1041" t="n">
-        <v>16236.522</v>
+        <v>15033.8164</v>
       </c>
       <c r="O1041" t="n">
-        <v>146128.698</v>
+        <v>135304.3476</v>
       </c>
       <c r="P1041" t="n">
         <v>19900</v>
@@ -47799,10 +47799,10 @@
         <v>4</v>
       </c>
       <c r="N1045" t="n">
-        <v>15827.732631579</v>
+        <v>14320.330526316</v>
       </c>
       <c r="O1045" t="n">
-        <v>63310.930526316</v>
+        <v>57281.322105264</v>
       </c>
       <c r="P1045" t="n">
         <v>19900</v>
@@ -47897,10 +47897,10 @@
         <v>2</v>
       </c>
       <c r="N1047" t="n">
-        <v>17438.2184</v>
+        <v>16146.4984</v>
       </c>
       <c r="O1047" t="n">
-        <v>34876.4368</v>
+        <v>32292.9968</v>
       </c>
       <c r="P1047" t="n">
         <v>26900</v>
@@ -50495,10 +50495,10 @@
         <v>12</v>
       </c>
       <c r="N1102" t="n">
-        <v>23008.657146402</v>
+        <v>22951.705012407</v>
       </c>
       <c r="O1102" t="n">
-        <v>276103.885756824</v>
+        <v>275420.460148884</v>
       </c>
       <c r="P1102" t="n">
         <v>37900</v>
@@ -57577,10 +57577,10 @@
         <v>8</v>
       </c>
       <c r="N1256" t="n">
-        <v>449.18534246575</v>
+        <v>415.07</v>
       </c>
       <c r="O1256" t="n">
-        <v>3593.482739726</v>
+        <v>3320.56</v>
       </c>
       <c r="P1256" t="n">
         <v>2900</v>
@@ -58829,10 +58829,10 @@
         <v>6</v>
       </c>
       <c r="N1283" t="n">
-        <v>1039.9621428571</v>
+        <v>970.63142857143</v>
       </c>
       <c r="O1283" t="n">
-        <v>6239.7728571426</v>
+        <v>5823.78857142858</v>
       </c>
       <c r="P1283" t="n">
         <v>7200</v>

--- a/bodegas/02.xlsx
+++ b/bodegas/02.xlsx
@@ -856,10 +856,10 @@
         <v>134</v>
       </c>
       <c r="N11" t="n">
-        <v>1815.9962867012</v>
+        <v>1811.3037996546</v>
       </c>
       <c r="O11" t="n">
-        <v>243343.5024179608</v>
+        <v>242714.7091537164</v>
       </c>
       <c r="P11" t="n">
         <v>2600</v>
@@ -1531,10 +1531,10 @@
         <v>6</v>
       </c>
       <c r="N28" t="n">
-        <v>6300.2067296512</v>
+        <v>6272.8541860465</v>
       </c>
       <c r="O28" t="n">
-        <v>37801.2403779072</v>
+        <v>37637.125116279</v>
       </c>
       <c r="P28" t="n">
         <v>7900</v>
@@ -5482,10 +5482,10 @@
         <v>8</v>
       </c>
       <c r="N121" t="n">
-        <v>3872.3234767642</v>
+        <v>3865.67</v>
       </c>
       <c r="O121" t="n">
-        <v>30978.5878141136</v>
+        <v>30925.36</v>
       </c>
       <c r="P121" t="n">
         <v>5500</v>
@@ -5659,10 +5659,10 @@
         <v>19</v>
       </c>
       <c r="N125" t="n">
-        <v>2589.9594489247</v>
+        <v>2572.67</v>
       </c>
       <c r="O125" t="n">
-        <v>49209.2295295693</v>
+        <v>48880.73</v>
       </c>
       <c r="P125" t="n">
         <v>4700</v>
@@ -5797,10 +5797,10 @@
         <v>1</v>
       </c>
       <c r="N128" t="n">
-        <v>2597.4440764331</v>
+        <v>2570.16</v>
       </c>
       <c r="O128" t="n">
-        <v>2597.4440764331</v>
+        <v>2570.16</v>
       </c>
       <c r="P128" t="n">
         <v>4700</v>
@@ -5882,10 +5882,10 @@
         <v>13</v>
       </c>
       <c r="N130" t="n">
-        <v>3126.0967950311</v>
+        <v>3114.49</v>
       </c>
       <c r="O130" t="n">
-        <v>40639.2583354043</v>
+        <v>40488.37</v>
       </c>
       <c r="P130" t="n">
         <v>5500</v>
@@ -6116,10 +6116,10 @@
         <v>13</v>
       </c>
       <c r="N136" t="n">
-        <v>4411.4198473282</v>
+        <v>4378</v>
       </c>
       <c r="O136" t="n">
-        <v>57348.4580152666</v>
+        <v>56914</v>
       </c>
       <c r="P136" t="n">
         <v>3900</v>
@@ -6507,10 +6507,10 @@
         <v>1</v>
       </c>
       <c r="N145" t="n">
-        <v>2597.7011260054</v>
+        <v>2563.34</v>
       </c>
       <c r="O145" t="n">
-        <v>2597.7011260054</v>
+        <v>2563.34</v>
       </c>
       <c r="P145" t="n">
         <v>4700</v>
@@ -10211,10 +10211,10 @@
         <v>7</v>
       </c>
       <c r="N227" t="n">
-        <v>3489.6196317829</v>
+        <v>3456.13</v>
       </c>
       <c r="O227" t="n">
-        <v>24427.3374224803</v>
+        <v>24192.91</v>
       </c>
       <c r="P227" t="n">
         <v>5700</v>
@@ -12614,10 +12614,10 @@
         <v>4</v>
       </c>
       <c r="N281" t="n">
-        <v>7538.62740638</v>
+        <v>7507.39</v>
       </c>
       <c r="O281" t="n">
-        <v>30154.50962552</v>
+        <v>30029.56</v>
       </c>
       <c r="P281" t="n">
         <v>13500</v>
@@ -12712,10 +12712,10 @@
         <v>2</v>
       </c>
       <c r="N283" t="n">
-        <v>8907.908396946599</v>
+        <v>8796</v>
       </c>
       <c r="O283" t="n">
-        <v>17815.8167938932</v>
+        <v>17592</v>
       </c>
       <c r="P283" t="n">
         <v>14900</v>
@@ -12932,10 +12932,10 @@
         <v>10</v>
       </c>
       <c r="N288" t="n">
-        <v>3801.7317574476</v>
+        <v>3795.7100070509</v>
       </c>
       <c r="O288" t="n">
-        <v>38017.317574476</v>
+        <v>37957.100070509</v>
       </c>
       <c r="P288" t="n">
         <v>6200</v>
@@ -12978,10 +12978,10 @@
         <v>6</v>
       </c>
       <c r="N289" t="n">
-        <v>3695.2967632027</v>
+        <v>3684</v>
       </c>
       <c r="O289" t="n">
-        <v>22171.7805792162</v>
+        <v>22104</v>
       </c>
       <c r="P289" t="n">
         <v>6200</v>
@@ -13961,10 +13961,10 @@
         <v>1</v>
       </c>
       <c r="N311" t="n">
-        <v>8209.849315068501</v>
+        <v>8154</v>
       </c>
       <c r="O311" t="n">
-        <v>8209.849315068501</v>
+        <v>8154</v>
       </c>
       <c r="P311" t="n">
         <v>13500</v>
@@ -17639,10 +17639,10 @@
         <v>21</v>
       </c>
       <c r="N393" t="n">
-        <v>1303.6380504587</v>
+        <v>1301.3994036697</v>
       </c>
       <c r="O393" t="n">
-        <v>27376.3990596327</v>
+        <v>27329.3874770637</v>
       </c>
       <c r="P393" t="n">
         <v>2000</v>
@@ -17961,10 +17961,10 @@
         <v>145</v>
       </c>
       <c r="N400" t="n">
-        <v>2030.7740585774</v>
+        <v>1965</v>
       </c>
       <c r="O400" t="n">
-        <v>294462.238493723</v>
+        <v>284925</v>
       </c>
       <c r="P400" t="n">
         <v>3700</v>
@@ -18419,10 +18419,10 @@
         <v>14</v>
       </c>
       <c r="N410" t="n">
-        <v>210.96774011299</v>
+        <v>204.05079096045</v>
       </c>
       <c r="O410" t="n">
-        <v>2953.54836158186</v>
+        <v>2856.7110734463</v>
       </c>
       <c r="P410" t="n">
         <v>500</v>
@@ -18635,10 +18635,10 @@
         <v>73</v>
       </c>
       <c r="N415" t="n">
-        <v>948.69545706371</v>
+        <v>933.18537396122</v>
       </c>
       <c r="O415" t="n">
-        <v>69254.76836565083</v>
+        <v>68122.53229916906</v>
       </c>
       <c r="P415" t="n">
         <v>1200</v>
@@ -19470,10 +19470,10 @@
         <v>22</v>
       </c>
       <c r="N434" t="n">
-        <v>4550.9158878505</v>
+        <v>4488</v>
       </c>
       <c r="O434" t="n">
-        <v>100120.149532711</v>
+        <v>98736</v>
       </c>
       <c r="P434" t="n">
         <v>6200</v>
@@ -19552,10 +19552,10 @@
         <v>6</v>
       </c>
       <c r="N436" t="n">
-        <v>8818.9498942682</v>
+        <v>8794.48</v>
       </c>
       <c r="O436" t="n">
-        <v>52913.6993656092</v>
+        <v>52766.88</v>
       </c>
       <c r="P436" t="n">
         <v>14500</v>
@@ -19634,10 +19634,10 @@
         <v>53</v>
       </c>
       <c r="N438" t="n">
-        <v>2558.6841592313</v>
+        <v>2517.22</v>
       </c>
       <c r="O438" t="n">
-        <v>135610.2604392589</v>
+        <v>133412.66</v>
       </c>
       <c r="P438" t="n">
         <v>4200</v>
@@ -19675,10 +19675,10 @@
         <v>97</v>
       </c>
       <c r="N439" t="n">
-        <v>2035.7801454898</v>
+        <v>2029.8736372454</v>
       </c>
       <c r="O439" t="n">
-        <v>197470.6741125106</v>
+        <v>196897.7428128038</v>
       </c>
       <c r="P439" t="n">
         <v>3600</v>
@@ -19716,10 +19716,10 @@
         <v>8</v>
       </c>
       <c r="N440" t="n">
-        <v>22561.918644068</v>
+        <v>22485.695932203</v>
       </c>
       <c r="O440" t="n">
-        <v>180495.349152544</v>
+        <v>179885.567457624</v>
       </c>
       <c r="P440" t="n">
         <v>36500</v>
@@ -19880,10 +19880,10 @@
         <v>11</v>
       </c>
       <c r="N444" t="n">
-        <v>7136.7702060222</v>
+        <v>7103</v>
       </c>
       <c r="O444" t="n">
-        <v>78504.47226624421</v>
+        <v>78133</v>
       </c>
       <c r="P444" t="n">
         <v>10700</v>
@@ -23714,10 +23714,10 @@
         <v>24</v>
       </c>
       <c r="N532" t="n">
-        <v>3779.7578947368</v>
+        <v>3590.77</v>
       </c>
       <c r="O532" t="n">
-        <v>90714.1894736832</v>
+        <v>86178.48</v>
       </c>
       <c r="P532" t="n">
         <v>3900</v>
@@ -25876,10 +25876,10 @@
         <v>6</v>
       </c>
       <c r="N579" t="n">
-        <v>11682.094594595</v>
+        <v>11450</v>
       </c>
       <c r="O579" t="n">
-        <v>70092.56756757</v>
+        <v>68700</v>
       </c>
       <c r="P579" t="n">
         <v>18300</v>
@@ -25968,10 +25968,10 @@
         <v>8</v>
       </c>
       <c r="N581" t="n">
-        <v>6365.625</v>
+        <v>6300</v>
       </c>
       <c r="O581" t="n">
-        <v>50925</v>
+        <v>50400</v>
       </c>
       <c r="P581" t="n">
         <v>10200</v>
@@ -26152,10 +26152,10 @@
         <v>15</v>
       </c>
       <c r="N585" t="n">
-        <v>7371.3029315961</v>
+        <v>7230</v>
       </c>
       <c r="O585" t="n">
-        <v>110569.5439739415</v>
+        <v>108450</v>
       </c>
       <c r="P585" t="n">
         <v>11600</v>
@@ -26198,10 +26198,10 @@
         <v>6</v>
       </c>
       <c r="N586" t="n">
-        <v>5291.8727915194</v>
+        <v>5200</v>
       </c>
       <c r="O586" t="n">
-        <v>31751.2367491164</v>
+        <v>31200</v>
       </c>
       <c r="P586" t="n">
         <v>8500</v>
@@ -26244,10 +26244,10 @@
         <v>3</v>
       </c>
       <c r="N587" t="n">
-        <v>1420.3389830508</v>
+        <v>1400</v>
       </c>
       <c r="O587" t="n">
-        <v>4261.016949152399</v>
+        <v>4200</v>
       </c>
       <c r="P587" t="n">
         <v>2300</v>
@@ -26290,10 +26290,10 @@
         <v>17</v>
       </c>
       <c r="N588" t="n">
-        <v>6085.1063829787</v>
+        <v>6000</v>
       </c>
       <c r="O588" t="n">
-        <v>103446.8085106379</v>
+        <v>102000</v>
       </c>
       <c r="P588" t="n">
         <v>10000</v>
@@ -26382,10 +26382,10 @@
         <v>24</v>
       </c>
       <c r="N590" t="n">
-        <v>1243.273381295</v>
+        <v>1230</v>
       </c>
       <c r="O590" t="n">
-        <v>29838.56115108</v>
+        <v>29520</v>
       </c>
       <c r="P590" t="n">
         <v>2000</v>
@@ -26574,10 +26574,10 @@
         <v>13</v>
       </c>
       <c r="N594" t="n">
-        <v>1944.3046357616</v>
+        <v>1870</v>
       </c>
       <c r="O594" t="n">
-        <v>25275.9602649008</v>
+        <v>24310</v>
       </c>
       <c r="P594" t="n">
         <v>3000</v>
@@ -26620,10 +26620,10 @@
         <v>3</v>
       </c>
       <c r="N595" t="n">
-        <v>2110.9815037594</v>
+        <v>2019.86</v>
       </c>
       <c r="O595" t="n">
-        <v>6332.9445112782</v>
+        <v>6059.58</v>
       </c>
       <c r="P595" t="n">
         <v>3300</v>
@@ -26666,10 +26666,10 @@
         <v>72</v>
       </c>
       <c r="N596" t="n">
-        <v>539.28902627512</v>
+        <v>520</v>
       </c>
       <c r="O596" t="n">
-        <v>38828.80989180864</v>
+        <v>37440</v>
       </c>
       <c r="P596" t="n">
         <v>850</v>
@@ -26758,10 +26758,10 @@
         <v>50</v>
       </c>
       <c r="N598" t="n">
-        <v>2318.1974248927</v>
+        <v>2260</v>
       </c>
       <c r="O598" t="n">
-        <v>115909.871244635</v>
+        <v>113000</v>
       </c>
       <c r="P598" t="n">
         <v>3800</v>
@@ -26850,10 +26850,10 @@
         <v>34</v>
       </c>
       <c r="N600" t="n">
-        <v>1872.4705882353</v>
+        <v>1840</v>
       </c>
       <c r="O600" t="n">
-        <v>63664.0000000002</v>
+        <v>62560</v>
       </c>
       <c r="P600" t="n">
         <v>3000</v>
@@ -26942,10 +26942,10 @@
         <v>40</v>
       </c>
       <c r="N602" t="n">
-        <v>2878.4650112867</v>
+        <v>2840</v>
       </c>
       <c r="O602" t="n">
-        <v>115138.600451468</v>
+        <v>113600</v>
       </c>
       <c r="P602" t="n">
         <v>4600</v>
@@ -27178,10 +27178,10 @@
         <v>4</v>
       </c>
       <c r="N607" t="n">
-        <v>13863.987068966</v>
+        <v>13687</v>
       </c>
       <c r="O607" t="n">
-        <v>55455.948275864</v>
+        <v>54748</v>
       </c>
       <c r="P607" t="n">
         <v>21900</v>
@@ -27820,10 +27820,10 @@
         <v>8</v>
       </c>
       <c r="N621" t="n">
-        <v>6112.6956521739</v>
+        <v>5858</v>
       </c>
       <c r="O621" t="n">
-        <v>48901.5652173912</v>
+        <v>46864</v>
       </c>
       <c r="P621" t="n">
         <v>9500</v>
@@ -28522,10 +28522,10 @@
         <v>6</v>
       </c>
       <c r="N636" t="n">
-        <v>9045.4669811321</v>
+        <v>9003</v>
       </c>
       <c r="O636" t="n">
-        <v>54272.8018867926</v>
+        <v>54018</v>
       </c>
       <c r="P636" t="n">
         <v>14900</v>
@@ -29258,10 +29258,10 @@
         <v>5</v>
       </c>
       <c r="N652" t="n">
-        <v>4223.6597938144</v>
+        <v>4202</v>
       </c>
       <c r="O652" t="n">
-        <v>21118.298969072</v>
+        <v>21010</v>
       </c>
       <c r="P652" t="n">
         <v>7900</v>
@@ -32017,10 +32017,10 @@
         <v>187</v>
       </c>
       <c r="N712" t="n">
-        <v>1946.0906677937</v>
+        <v>1907.3944716822</v>
       </c>
       <c r="O712" t="n">
-        <v>363918.9548774219</v>
+        <v>356682.7662045714</v>
       </c>
       <c r="P712" t="n">
         <v>2500</v>
@@ -32063,10 +32063,10 @@
         <v>118</v>
       </c>
       <c r="N713" t="n">
-        <v>1796.7129837251</v>
+        <v>1771.091283906</v>
       </c>
       <c r="O713" t="n">
-        <v>212012.1320795618</v>
+        <v>208988.771500908</v>
       </c>
       <c r="P713" t="n">
         <v>2500</v>
@@ -32109,10 +32109,10 @@
         <v>227</v>
       </c>
       <c r="N714" t="n">
-        <v>2095.5452849741</v>
+        <v>2079.3842227979</v>
       </c>
       <c r="O714" t="n">
-        <v>475688.7796891207</v>
+        <v>472020.2185751233</v>
       </c>
       <c r="P714" t="n">
         <v>2900</v>
@@ -32155,10 +32155,10 @@
         <v>230</v>
       </c>
       <c r="N715" t="n">
-        <v>1828.4692441176</v>
+        <v>1803.0149852941</v>
       </c>
       <c r="O715" t="n">
-        <v>420547.926147048</v>
+        <v>414693.446617643</v>
       </c>
       <c r="P715" t="n">
         <v>2500</v>
@@ -32247,10 +32247,10 @@
         <v>302</v>
       </c>
       <c r="N717" t="n">
-        <v>2137.4820360902</v>
+        <v>2122.1641172932</v>
       </c>
       <c r="O717" t="n">
-        <v>645519.5748992404</v>
+        <v>640893.5634225464</v>
       </c>
       <c r="P717" t="n">
         <v>2900</v>
@@ -32385,10 +32385,10 @@
         <v>132</v>
       </c>
       <c r="N720" t="n">
-        <v>3276.0008772707</v>
+        <v>3224.5679308817</v>
       </c>
       <c r="O720" t="n">
-        <v>432432.1157997324</v>
+        <v>425642.9668763844</v>
       </c>
       <c r="P720" t="n">
         <v>4500</v>
@@ -32800,10 +32800,10 @@
         <v>3</v>
       </c>
       <c r="N729" t="n">
-        <v>5414.576625</v>
+        <v>5347.73</v>
       </c>
       <c r="O729" t="n">
-        <v>16243.729875</v>
+        <v>16043.19</v>
       </c>
       <c r="P729" t="n">
         <v>9500</v>
@@ -33122,10 +33122,10 @@
         <v>30</v>
       </c>
       <c r="N736" t="n">
-        <v>3051.52</v>
+        <v>2980</v>
       </c>
       <c r="O736" t="n">
-        <v>91545.60000000001</v>
+        <v>89400</v>
       </c>
       <c r="P736" t="n">
         <v>4800</v>
@@ -34391,10 +34391,10 @@
         <v>14</v>
       </c>
       <c r="N763" t="n">
-        <v>2769.7168108108</v>
+        <v>2682.71</v>
       </c>
       <c r="O763" t="n">
-        <v>38776.03535135119</v>
+        <v>37557.94</v>
       </c>
       <c r="P763" t="n">
         <v>10900</v>
@@ -36118,10 +36118,10 @@
         <v>9</v>
       </c>
       <c r="N800" t="n">
-        <v>2483.1635416667</v>
+        <v>2270.3210416667</v>
       </c>
       <c r="O800" t="n">
-        <v>22348.4718750003</v>
+        <v>20432.8893750003</v>
       </c>
       <c r="P800" t="n">
         <v>3900</v>
@@ -38109,10 +38109,10 @@
         <v>664</v>
       </c>
       <c r="N843" t="n">
-        <v>704.1779547101401</v>
+        <v>703.79545471015</v>
       </c>
       <c r="O843" t="n">
-        <v>467574.161927533</v>
+        <v>467320.1819275396</v>
       </c>
       <c r="P843" t="n">
         <v>900</v>
@@ -38345,10 +38345,10 @@
         <v>2</v>
       </c>
       <c r="N848" t="n">
-        <v>3216.9665454545</v>
+        <v>3182.2510909091</v>
       </c>
       <c r="O848" t="n">
-        <v>6433.933090909</v>
+        <v>6364.5021818182</v>
       </c>
       <c r="P848" t="n">
         <v>6900</v>
@@ -47060,10 +47060,10 @@
         <v>38</v>
       </c>
       <c r="N1030" t="n">
-        <v>713.93197013211</v>
+        <v>711.48</v>
       </c>
       <c r="O1030" t="n">
-        <v>27129.41486502018</v>
+        <v>27036.24</v>
       </c>
       <c r="P1030" t="n">
         <v>2500</v>
@@ -49253,10 +49253,10 @@
         <v>1</v>
       </c>
       <c r="N1075" t="n">
-        <v>2251.9952</v>
+        <v>2010.71</v>
       </c>
       <c r="O1075" t="n">
-        <v>2251.9952</v>
+        <v>2010.71</v>
       </c>
       <c r="P1075" t="n">
         <v>7200</v>
@@ -50267,10 +50267,10 @@
         <v>51</v>
       </c>
       <c r="N1097" t="n">
-        <v>3192.6751439214</v>
+        <v>3181.9</v>
       </c>
       <c r="O1097" t="n">
-        <v>162826.4323399914</v>
+        <v>162276.9</v>
       </c>
       <c r="P1097" t="n">
         <v>5100</v>
@@ -50401,10 +50401,10 @@
         <v>3</v>
       </c>
       <c r="N1100" t="n">
-        <v>2540.4017582418</v>
+        <v>2523.3377514793</v>
       </c>
       <c r="O1100" t="n">
-        <v>7621.2052747254</v>
+        <v>7570.0132544379</v>
       </c>
       <c r="P1100" t="n">
         <v>2800</v>
@@ -50632,10 +50632,10 @@
         <v>41</v>
       </c>
       <c r="N1105" t="n">
-        <v>707.12182981928</v>
+        <v>705.52801204819</v>
       </c>
       <c r="O1105" t="n">
-        <v>28991.99502259048</v>
+        <v>28926.64849397579</v>
       </c>
       <c r="P1105" t="n">
         <v>1500</v>
@@ -55816,10 +55816,10 @@
         <v>3</v>
       </c>
       <c r="N1218" t="n">
-        <v>1338.6403076923</v>
+        <v>1160.1556923077</v>
       </c>
       <c r="O1218" t="n">
-        <v>4015.9209230769</v>
+        <v>3480.4670769231</v>
       </c>
       <c r="P1218" t="n">
         <v>1600</v>
@@ -59063,10 +59063,10 @@
         <v>5</v>
       </c>
       <c r="N1288" t="n">
-        <v>614.59626373626</v>
+        <v>576.58</v>
       </c>
       <c r="O1288" t="n">
-        <v>3072.9813186813</v>
+        <v>2882.9</v>
       </c>
       <c r="P1288" t="n">
         <v>5900</v>
@@ -60386,10 +60386,10 @@
         <v>13</v>
       </c>
       <c r="N1316" t="n">
-        <v>229.9076771366</v>
+        <v>227.41596785975</v>
       </c>
       <c r="O1316" t="n">
-        <v>2988.7998027758</v>
+        <v>2956.40758217675</v>
       </c>
       <c r="P1316" t="n">
         <v>1200</v>

--- a/bodegas/02.xlsx
+++ b/bodegas/02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-07</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-08</t>
         </is>
       </c>
     </row>

--- a/bodegas/02.xlsx
+++ b/bodegas/02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-09</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-10</t>
         </is>
       </c>
     </row>

--- a/bodegas/02.xlsx
+++ b/bodegas/02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-14</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-15</t>
         </is>
       </c>
     </row>
@@ -1519,13 +1519,13 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>14</v>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -1895,22 +1895,22 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M37" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N37" t="n">
         <v>2413.0010615711</v>
       </c>
       <c r="O37" t="n">
-        <v>28956.0127388532</v>
+        <v>24130.010615711</v>
       </c>
       <c r="P37" t="n">
         <v>4700</v>
       </c>
       <c r="Q37" t="n">
-        <v>56400</v>
+        <v>47000</v>
       </c>
     </row>
     <row r="38">
@@ -2162,13 +2162,13 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>22</v>
@@ -2282,13 +2282,13 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
         <v>2</v>
@@ -5645,13 +5645,13 @@
         </is>
       </c>
       <c r="J125" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="K125" t="n">
         <v>0</v>
       </c>
       <c r="L125" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
         <v>14</v>
@@ -5985,13 +5985,13 @@
         </is>
       </c>
       <c r="J133" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K133" t="n">
         <v>0</v>
       </c>
       <c r="L133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
         <v>11</v>
@@ -6537,13 +6537,13 @@
         </is>
       </c>
       <c r="J146" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K146" t="n">
         <v>0</v>
       </c>
       <c r="L146" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M146" t="n">
         <v>7</v>
@@ -8787,13 +8787,13 @@
         </is>
       </c>
       <c r="J196" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="K196" t="n">
         <v>0</v>
       </c>
       <c r="L196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M196" t="n">
         <v>210</v>
@@ -10507,13 +10507,13 @@
         </is>
       </c>
       <c r="J234" t="n">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="K234" t="n">
         <v>0</v>
       </c>
       <c r="L234" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M234" t="n">
         <v>614</v>
@@ -11591,13 +11591,13 @@
         </is>
       </c>
       <c r="J259" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="K259" t="n">
         <v>0</v>
       </c>
       <c r="L259" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M259" t="n">
         <v>54</v>
@@ -11729,13 +11729,13 @@
         </is>
       </c>
       <c r="J262" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K262" t="n">
         <v>0</v>
       </c>
       <c r="L262" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M262" t="n">
         <v>42</v>
@@ -11824,13 +11824,13 @@
         </is>
       </c>
       <c r="J264" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K264" t="n">
         <v>0</v>
       </c>
       <c r="L264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M264" t="n">
         <v>5</v>
@@ -12057,13 +12057,13 @@
         </is>
       </c>
       <c r="J269" t="n">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="K269" t="n">
         <v>0</v>
       </c>
       <c r="L269" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M269" t="n">
         <v>165</v>
@@ -12459,13 +12459,13 @@
         </is>
       </c>
       <c r="J278" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K278" t="n">
         <v>0</v>
       </c>
       <c r="L278" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M278" t="n">
         <v>234</v>
@@ -13184,13 +13184,13 @@
         </is>
       </c>
       <c r="J294" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K294" t="n">
         <v>0</v>
       </c>
       <c r="L294" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M294" t="n">
         <v>100</v>
@@ -13225,13 +13225,13 @@
         </is>
       </c>
       <c r="J295" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="K295" t="n">
         <v>0</v>
       </c>
       <c r="L295" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M295" t="n">
         <v>11</v>
@@ -13271,13 +13271,13 @@
         </is>
       </c>
       <c r="J296" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K296" t="n">
         <v>0</v>
       </c>
       <c r="L296" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M296" t="n">
         <v>8</v>
@@ -13947,13 +13947,13 @@
         </is>
       </c>
       <c r="J311" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="K311" t="n">
         <v>0</v>
       </c>
       <c r="L311" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M311" t="n">
         <v>57</v>
@@ -14039,13 +14039,13 @@
         </is>
       </c>
       <c r="J313" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K313" t="n">
         <v>0</v>
       </c>
       <c r="L313" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M313" t="n">
         <v>4</v>
@@ -14934,13 +14934,13 @@
         </is>
       </c>
       <c r="J333" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K333" t="n">
         <v>0</v>
       </c>
       <c r="L333" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M333" t="n">
         <v>43</v>
@@ -15029,13 +15029,13 @@
         </is>
       </c>
       <c r="J335" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K335" t="n">
         <v>0</v>
       </c>
       <c r="L335" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M335" t="n">
         <v>50</v>
@@ -15119,13 +15119,13 @@
         </is>
       </c>
       <c r="J337" t="n">
-        <v>229</v>
+        <v>198</v>
       </c>
       <c r="K337" t="n">
         <v>0</v>
       </c>
       <c r="L337" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="M337" t="n">
         <v>198</v>
@@ -15293,13 +15293,13 @@
         </is>
       </c>
       <c r="J341" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="K341" t="n">
         <v>0</v>
       </c>
       <c r="L341" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M341" t="n">
         <v>29</v>
@@ -15872,13 +15872,13 @@
         </is>
       </c>
       <c r="J354" t="n">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="K354" t="n">
         <v>0</v>
       </c>
       <c r="L354" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M354" t="n">
         <v>98</v>
@@ -16465,13 +16465,13 @@
         </is>
       </c>
       <c r="J367" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K367" t="n">
         <v>0</v>
       </c>
       <c r="L367" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M367" t="n">
         <v>18</v>
@@ -16557,13 +16557,13 @@
         </is>
       </c>
       <c r="J369" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K369" t="n">
         <v>0</v>
       </c>
       <c r="L369" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M369" t="n">
         <v>6</v>
@@ -17008,13 +17008,13 @@
         </is>
       </c>
       <c r="J379" t="n">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="K379" t="n">
         <v>0</v>
       </c>
       <c r="L379" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M379" t="n">
         <v>268</v>
@@ -17146,13 +17146,13 @@
         </is>
       </c>
       <c r="J382" t="n">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="K382" t="n">
         <v>0</v>
       </c>
       <c r="L382" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M382" t="n">
         <v>234</v>
@@ -17192,13 +17192,13 @@
         </is>
       </c>
       <c r="J383" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K383" t="n">
         <v>0</v>
       </c>
       <c r="L383" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M383" t="n">
         <v>43</v>
@@ -17238,13 +17238,13 @@
         </is>
       </c>
       <c r="J384" t="n">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="K384" t="n">
         <v>0</v>
       </c>
       <c r="L384" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M384" t="n">
         <v>442</v>
@@ -17284,13 +17284,13 @@
         </is>
       </c>
       <c r="J385" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="K385" t="n">
         <v>0</v>
       </c>
       <c r="L385" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M385" t="n">
         <v>57</v>
@@ -17862,13 +17862,13 @@
         </is>
       </c>
       <c r="J398" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="K398" t="n">
         <v>0</v>
       </c>
       <c r="L398" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M398" t="n">
         <v>38</v>
@@ -19801,13 +19801,13 @@
         </is>
       </c>
       <c r="J442" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K442" t="n">
         <v>0</v>
       </c>
       <c r="L442" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M442" t="n">
         <v>95</v>
@@ -20434,10 +20434,10 @@
         </is>
       </c>
       <c r="J457" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K457" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L457" t="n">
         <v>0</v>
@@ -20608,13 +20608,13 @@
         </is>
       </c>
       <c r="J461" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K461" t="n">
         <v>0</v>
       </c>
       <c r="L461" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M461" t="n">
         <v>93</v>
@@ -20747,13 +20747,13 @@
         </is>
       </c>
       <c r="J464" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K464" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L464" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M464" t="n">
         <v>6</v>
@@ -21648,13 +21648,13 @@
         </is>
       </c>
       <c r="J485" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K485" t="n">
         <v>0</v>
       </c>
       <c r="L485" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M485" t="n">
         <v>1</v>
@@ -24111,13 +24111,13 @@
         </is>
       </c>
       <c r="J541" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K541" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L541" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M541" t="n">
         <v>19</v>
@@ -24157,13 +24157,13 @@
         </is>
       </c>
       <c r="J542" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="K542" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L542" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M542" t="n">
         <v>19</v>
@@ -24203,13 +24203,13 @@
         </is>
       </c>
       <c r="J543" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K543" t="n">
         <v>0</v>
       </c>
       <c r="L543" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M543" t="n">
         <v>4</v>
@@ -24341,10 +24341,10 @@
         </is>
       </c>
       <c r="J546" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="K546" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L546" t="n">
         <v>0</v>
@@ -24387,13 +24387,13 @@
         </is>
       </c>
       <c r="J547" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="K547" t="n">
         <v>0</v>
       </c>
       <c r="L547" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M547" t="n">
         <v>14</v>
@@ -24433,13 +24433,13 @@
         </is>
       </c>
       <c r="J548" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K548" t="n">
         <v>0</v>
       </c>
       <c r="L548" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M548" t="n">
         <v>20</v>
@@ -24479,13 +24479,13 @@
         </is>
       </c>
       <c r="J549" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K549" t="n">
         <v>0</v>
       </c>
       <c r="L549" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M549" t="n">
         <v>18</v>
@@ -24525,13 +24525,13 @@
         </is>
       </c>
       <c r="J550" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="K550" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L550" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M550" t="n">
         <v>23</v>
@@ -24571,13 +24571,13 @@
         </is>
       </c>
       <c r="J551" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K551" t="n">
         <v>0</v>
       </c>
       <c r="L551" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M551" t="n">
         <v>18</v>
@@ -24801,13 +24801,13 @@
         </is>
       </c>
       <c r="J556" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="K556" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L556" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M556" t="n">
         <v>21</v>
@@ -25358,13 +25358,13 @@
         </is>
       </c>
       <c r="J568" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K568" t="n">
         <v>0</v>
       </c>
       <c r="L568" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M568" t="n">
         <v>4</v>
@@ -25404,13 +25404,13 @@
         </is>
       </c>
       <c r="J569" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K569" t="n">
         <v>0</v>
       </c>
       <c r="L569" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M569" t="n">
         <v>36</v>
@@ -25440,10 +25440,10 @@
         </is>
       </c>
       <c r="J570" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K570" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L570" t="n">
         <v>0</v>
@@ -25486,13 +25486,13 @@
         </is>
       </c>
       <c r="J571" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K571" t="n">
         <v>0</v>
       </c>
       <c r="L571" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M571" t="n">
         <v>3</v>
@@ -27620,22 +27620,22 @@
         <v>0</v>
       </c>
       <c r="L617" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M617" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N617" t="n">
         <v>10385</v>
       </c>
       <c r="O617" t="n">
-        <v>166160</v>
+        <v>155775</v>
       </c>
       <c r="P617" t="n">
         <v>16900</v>
       </c>
       <c r="Q617" t="n">
-        <v>270400</v>
+        <v>253500</v>
       </c>
     </row>
     <row r="618">
@@ -27798,13 +27798,13 @@
         </is>
       </c>
       <c r="J621" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K621" t="n">
         <v>0</v>
       </c>
       <c r="L621" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M621" t="n">
         <v>7</v>
@@ -28950,13 +28950,13 @@
         </is>
       </c>
       <c r="J646" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K646" t="n">
         <v>0</v>
       </c>
       <c r="L646" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M646" t="n">
         <v>24</v>
@@ -30192,10 +30192,10 @@
         </is>
       </c>
       <c r="J673" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K673" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L673" t="n">
         <v>0</v>
@@ -31476,13 +31476,13 @@
         </is>
       </c>
       <c r="J701" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K701" t="n">
         <v>0</v>
       </c>
       <c r="L701" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M701" t="n">
         <v>32</v>
@@ -32077,13 +32077,13 @@
         </is>
       </c>
       <c r="J714" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K714" t="n">
         <v>0</v>
       </c>
       <c r="L714" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M714" t="n">
         <v>106</v>
@@ -32123,13 +32123,13 @@
         </is>
       </c>
       <c r="J715" t="n">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="K715" t="n">
         <v>0</v>
       </c>
       <c r="L715" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M715" t="n">
         <v>166</v>
@@ -32215,13 +32215,13 @@
         </is>
       </c>
       <c r="J717" t="n">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="K717" t="n">
         <v>0</v>
       </c>
       <c r="L717" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M717" t="n">
         <v>225</v>
@@ -32261,13 +32261,13 @@
         </is>
       </c>
       <c r="J718" t="n">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="K718" t="n">
         <v>0</v>
       </c>
       <c r="L718" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M718" t="n">
         <v>227</v>
@@ -32307,13 +32307,13 @@
         </is>
       </c>
       <c r="J719" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="K719" t="n">
         <v>0</v>
       </c>
       <c r="L719" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M719" t="n">
         <v>47</v>
@@ -32399,13 +32399,13 @@
         </is>
       </c>
       <c r="J721" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="K721" t="n">
         <v>0</v>
       </c>
       <c r="L721" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M721" t="n">
         <v>209</v>
@@ -32445,13 +32445,13 @@
         </is>
       </c>
       <c r="J722" t="n">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="K722" t="n">
         <v>0</v>
       </c>
       <c r="L722" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M722" t="n">
         <v>222</v>
@@ -32491,13 +32491,13 @@
         </is>
       </c>
       <c r="J723" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="K723" t="n">
         <v>0</v>
       </c>
       <c r="L723" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M723" t="n">
         <v>129</v>
@@ -32678,13 +32678,13 @@
         </is>
       </c>
       <c r="J727" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="K727" t="n">
         <v>0</v>
       </c>
       <c r="L727" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M727" t="n">
         <v>94</v>
@@ -32724,13 +32724,13 @@
         </is>
       </c>
       <c r="J728" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="K728" t="n">
         <v>0</v>
       </c>
       <c r="L728" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M728" t="n">
         <v>124</v>
@@ -32770,13 +32770,13 @@
         </is>
       </c>
       <c r="J729" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K729" t="n">
         <v>0</v>
       </c>
       <c r="L729" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M729" t="n">
         <v>77</v>
@@ -32816,13 +32816,13 @@
         </is>
       </c>
       <c r="J730" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="K730" t="n">
         <v>0</v>
       </c>
       <c r="L730" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M730" t="n">
         <v>103</v>
@@ -32862,13 +32862,13 @@
         </is>
       </c>
       <c r="J731" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K731" t="n">
         <v>0</v>
       </c>
       <c r="L731" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M731" t="n">
         <v>14</v>
@@ -32952,13 +32952,13 @@
         </is>
       </c>
       <c r="J733" t="n">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="K733" t="n">
         <v>0</v>
       </c>
       <c r="L733" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M733" t="n">
         <v>126</v>
@@ -33044,13 +33044,13 @@
         </is>
       </c>
       <c r="J735" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="K735" t="n">
         <v>0</v>
       </c>
       <c r="L735" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M735" t="n">
         <v>31</v>
@@ -33090,13 +33090,13 @@
         </is>
       </c>
       <c r="J736" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K736" t="n">
         <v>0</v>
       </c>
       <c r="L736" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M736" t="n">
         <v>19</v>
@@ -33274,13 +33274,13 @@
         </is>
       </c>
       <c r="J740" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K740" t="n">
         <v>0</v>
       </c>
       <c r="L740" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M740" t="n">
         <v>6</v>
@@ -33407,13 +33407,13 @@
         </is>
       </c>
       <c r="J743" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K743" t="n">
         <v>0</v>
       </c>
       <c r="L743" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M743" t="n">
         <v>3</v>
@@ -33453,13 +33453,13 @@
         </is>
       </c>
       <c r="J744" t="n">
-        <v>529</v>
+        <v>505</v>
       </c>
       <c r="K744" t="n">
         <v>0</v>
       </c>
       <c r="L744" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M744" t="n">
         <v>505</v>
@@ -35190,13 +35190,13 @@
         </is>
       </c>
       <c r="J781" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K781" t="n">
         <v>0</v>
       </c>
       <c r="L781" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M781" t="n">
         <v>8</v>
@@ -36077,13 +36077,13 @@
         </is>
       </c>
       <c r="J800" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K800" t="n">
         <v>0</v>
       </c>
       <c r="L800" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M800" t="n">
         <v>6</v>
@@ -36273,13 +36273,13 @@
         </is>
       </c>
       <c r="J804" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K804" t="n">
         <v>0</v>
       </c>
       <c r="L804" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M804" t="n">
         <v>2</v>
@@ -37064,28 +37064,28 @@
         </is>
       </c>
       <c r="J821" t="n">
-        <v>20</v>
+        <v>1150</v>
       </c>
       <c r="K821" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="L821" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="M821" t="n">
-        <v>1150</v>
+        <v>1100</v>
       </c>
       <c r="N821" t="n">
         <v>177.65</v>
       </c>
       <c r="O821" t="n">
-        <v>204297.5</v>
+        <v>195415</v>
       </c>
       <c r="P821" t="n">
         <v>300</v>
       </c>
       <c r="Q821" t="n">
-        <v>345000</v>
+        <v>330000</v>
       </c>
     </row>
     <row r="822">
@@ -37379,28 +37379,28 @@
         </is>
       </c>
       <c r="J828" t="n">
-        <v>883</v>
+        <v>849</v>
       </c>
       <c r="K828" t="n">
         <v>0</v>
       </c>
       <c r="L828" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="M828" t="n">
-        <v>849</v>
+        <v>843</v>
       </c>
       <c r="N828" t="n">
         <v>517.28815469086</v>
       </c>
       <c r="O828" t="n">
-        <v>439177.6433325401</v>
+        <v>436073.914404395</v>
       </c>
       <c r="P828" t="n">
         <v>900</v>
       </c>
       <c r="Q828" t="n">
-        <v>764100</v>
+        <v>758700</v>
       </c>
     </row>
     <row r="829">
@@ -37984,13 +37984,13 @@
         </is>
       </c>
       <c r="J841" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K841" t="n">
         <v>0</v>
       </c>
       <c r="L841" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M841" t="n">
         <v>74</v>
@@ -38215,13 +38215,13 @@
         </is>
       </c>
       <c r="J846" t="n">
-        <v>518</v>
+        <v>469</v>
       </c>
       <c r="K846" t="n">
         <v>0</v>
       </c>
       <c r="L846" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M846" t="n">
         <v>469</v>
@@ -41342,10 +41342,10 @@
         </is>
       </c>
       <c r="J912" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K912" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L912" t="n">
         <v>0</v>
@@ -42065,13 +42065,13 @@
         </is>
       </c>
       <c r="J927" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K927" t="n">
         <v>0</v>
       </c>
       <c r="L927" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M927" t="n">
         <v>3</v>
@@ -42111,13 +42111,13 @@
         </is>
       </c>
       <c r="J928" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K928" t="n">
         <v>0</v>
       </c>
       <c r="L928" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M928" t="n">
         <v>9</v>
@@ -42347,13 +42347,13 @@
         </is>
       </c>
       <c r="J933" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K933" t="n">
         <v>0</v>
       </c>
       <c r="L933" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M933" t="n">
         <v>1</v>
@@ -42396,10 +42396,10 @@
         </is>
       </c>
       <c r="J934" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K934" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L934" t="n">
         <v>0</v>
@@ -44766,13 +44766,13 @@
         </is>
       </c>
       <c r="J983" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K983" t="n">
         <v>0</v>
       </c>
       <c r="L983" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M983" t="n">
         <v>4</v>
@@ -47806,13 +47806,13 @@
         </is>
       </c>
       <c r="J1046" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K1046" t="n">
         <v>0</v>
       </c>
       <c r="L1046" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1046" t="n">
         <v>3</v>
@@ -47855,13 +47855,13 @@
         </is>
       </c>
       <c r="J1047" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K1047" t="n">
         <v>0</v>
       </c>
       <c r="L1047" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1047" t="n">
         <v>5</v>
@@ -48823,13 +48823,13 @@
         </is>
       </c>
       <c r="J1067" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="K1067" t="n">
         <v>0</v>
       </c>
       <c r="L1067" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M1067" t="n">
         <v>125</v>
@@ -49068,13 +49068,13 @@
         </is>
       </c>
       <c r="J1072" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K1072" t="n">
         <v>0</v>
       </c>
       <c r="L1072" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1072" t="n">
         <v>12</v>
@@ -49117,10 +49117,10 @@
         </is>
       </c>
       <c r="J1073" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="K1073" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L1073" t="n">
         <v>0</v>
@@ -50185,13 +50185,13 @@
         </is>
       </c>
       <c r="J1096" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="K1096" t="n">
         <v>0</v>
       </c>
       <c r="L1096" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M1096" t="n">
         <v>44</v>
@@ -54591,13 +54591,13 @@
         </is>
       </c>
       <c r="J1192" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K1192" t="n">
         <v>0</v>
       </c>
       <c r="L1192" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1192" t="n">
         <v>7</v>
@@ -54995,13 +54995,13 @@
         </is>
       </c>
       <c r="J1201" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K1201" t="n">
         <v>0</v>
       </c>
       <c r="L1201" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1201" t="n">
         <v>67</v>
@@ -59359,13 +59359,13 @@
         </is>
       </c>
       <c r="J1295" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K1295" t="n">
         <v>0</v>
       </c>
       <c r="L1295" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M1295" t="n">
         <v>9</v>
@@ -59456,13 +59456,13 @@
         </is>
       </c>
       <c r="J1297" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K1297" t="n">
         <v>0</v>
       </c>
       <c r="L1297" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1297" t="n">
         <v>2</v>
@@ -59548,13 +59548,13 @@
         </is>
       </c>
       <c r="J1299" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K1299" t="n">
         <v>0</v>
       </c>
       <c r="L1299" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1299" t="n">
         <v>2</v>

--- a/bodegas/02.xlsx
+++ b/bodegas/02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-16</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-17</t>
         </is>
       </c>
     </row>

--- a/bodegas/02.xlsx
+++ b/bodegas/02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-17</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-18</t>
         </is>
       </c>
     </row>
@@ -29047,22 +29047,22 @@
         <v>0</v>
       </c>
       <c r="L648" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M648" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N648" t="n">
         <v>52443</v>
       </c>
       <c r="O648" t="n">
-        <v>1415961</v>
+        <v>1363518</v>
       </c>
       <c r="P648" t="n">
         <v>83900</v>
       </c>
       <c r="Q648" t="n">
-        <v>2265300</v>
+        <v>2181400</v>
       </c>
     </row>
     <row r="649">

--- a/bodegas/02.xlsx
+++ b/bodegas/02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-23</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-24</t>
         </is>
       </c>
     </row>

--- a/bodegas/02.xlsx
+++ b/bodegas/02.xlsx
@@ -856,10 +856,10 @@
         <v>403</v>
       </c>
       <c r="N11" t="n">
-        <v>1811.307219032</v>
+        <v>1811.307345576</v>
       </c>
       <c r="O11" t="n">
-        <v>729956.809269896</v>
+        <v>729956.860267128</v>
       </c>
       <c r="P11" t="n">
         <v>2600</v>
@@ -934,10 +934,10 @@
         <v>7</v>
       </c>
       <c r="N13" t="n">
-        <v>3376.7464660832</v>
+        <v>3376.7464651163</v>
       </c>
       <c r="O13" t="n">
-        <v>23637.2252625824</v>
+        <v>23637.2252558141</v>
       </c>
       <c r="P13" t="n">
         <v>4500</v>
@@ -1531,10 +1531,10 @@
         <v>14</v>
       </c>
       <c r="N28" t="n">
-        <v>6272.8547682119</v>
+        <v>6272.8547761194</v>
       </c>
       <c r="O28" t="n">
-        <v>87819.96675496659</v>
+        <v>87819.96686567161</v>
       </c>
       <c r="P28" t="n">
         <v>7900</v>
@@ -1779,10 +1779,10 @@
         <v>8</v>
       </c>
       <c r="N34" t="n">
-        <v>22510.483333333</v>
+        <v>22510.483207547</v>
       </c>
       <c r="O34" t="n">
-        <v>180083.866666664</v>
+        <v>180083.865660376</v>
       </c>
       <c r="P34" t="n">
         <v>44900</v>
@@ -3431,10 +3431,10 @@
         <v>1</v>
       </c>
       <c r="N73" t="n">
-        <v>30708.848333333</v>
+        <v>30708.828</v>
       </c>
       <c r="O73" t="n">
-        <v>30708.848333333</v>
+        <v>30708.828</v>
       </c>
       <c r="P73" t="n">
         <v>53500</v>
@@ -4546,22 +4546,22 @@
         <v>0</v>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M100" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>61666.874092141</v>
+        <v>61666.874114441</v>
       </c>
       <c r="O100" t="n">
-        <v>123333.748184282</v>
+        <v>0</v>
       </c>
       <c r="P100" t="n">
         <v>98900</v>
       </c>
       <c r="Q100" t="n">
-        <v>197800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -5908,22 +5908,22 @@
         <v>0</v>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M131" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="N131" t="n">
         <v>2791.02</v>
       </c>
       <c r="O131" t="n">
-        <v>44656.32</v>
+        <v>11164.08</v>
       </c>
       <c r="P131" t="n">
         <v>3900</v>
       </c>
       <c r="Q131" t="n">
-        <v>62400</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="132">
@@ -6064,22 +6064,22 @@
         <v>0</v>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M135" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="N135" t="n">
         <v>4378</v>
       </c>
       <c r="O135" t="n">
-        <v>52536</v>
+        <v>17512</v>
       </c>
       <c r="P135" t="n">
         <v>3900</v>
       </c>
       <c r="Q135" t="n">
-        <v>46800</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="136">
@@ -10129,10 +10129,10 @@
         <v>16</v>
       </c>
       <c r="N225" t="n">
-        <v>4937.3101635688</v>
+        <v>4937.3101636905</v>
       </c>
       <c r="O225" t="n">
-        <v>78996.9626171008</v>
+        <v>78996.962619048</v>
       </c>
       <c r="P225" t="n">
         <v>7500</v>
@@ -10425,22 +10425,22 @@
         <v>0</v>
       </c>
       <c r="L232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M232" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N232" t="n">
         <v>14233.54</v>
       </c>
       <c r="O232" t="n">
-        <v>85401.24000000001</v>
+        <v>71167.70000000001</v>
       </c>
       <c r="P232" t="n">
         <v>10000</v>
       </c>
       <c r="Q232" t="n">
-        <v>60000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="233">
@@ -10475,10 +10475,10 @@
         <v>171</v>
       </c>
       <c r="N233" t="n">
-        <v>1098.0595661432</v>
+        <v>1098.0597873486</v>
       </c>
       <c r="O233" t="n">
-        <v>187768.1858104872</v>
+        <v>187768.2236366106</v>
       </c>
       <c r="P233" t="n">
         <v>1500</v>
@@ -11199,22 +11199,22 @@
         <v>0</v>
       </c>
       <c r="L250" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M250" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="N250" t="n">
         <v>2804.33</v>
       </c>
       <c r="O250" t="n">
-        <v>154238.15</v>
+        <v>143020.83</v>
       </c>
       <c r="P250" t="n">
         <v>4900</v>
       </c>
       <c r="Q250" t="n">
-        <v>269500</v>
+        <v>249900</v>
       </c>
     </row>
     <row r="251">
@@ -11553,22 +11553,22 @@
         <v>0</v>
       </c>
       <c r="L258" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M258" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N258" t="n">
-        <v>2582.2557353886</v>
+        <v>2582.2557142857</v>
       </c>
       <c r="O258" t="n">
-        <v>30987.0688246632</v>
+        <v>25822.557142857</v>
       </c>
       <c r="P258" t="n">
         <v>4500</v>
       </c>
       <c r="Q258" t="n">
-        <v>54000</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="259">
@@ -11651,10 +11651,10 @@
         <v>33</v>
       </c>
       <c r="N260" t="n">
-        <v>5216.8961202577</v>
+        <v>5216.8961124659</v>
       </c>
       <c r="O260" t="n">
-        <v>172157.5719685041</v>
+        <v>172157.5717113747</v>
       </c>
       <c r="P260" t="n">
         <v>8500</v>
@@ -11743,10 +11743,10 @@
         <v>34</v>
       </c>
       <c r="N262" t="n">
-        <v>2033.5474193548</v>
+        <v>2033.5471351351</v>
       </c>
       <c r="O262" t="n">
-        <v>69140.61225806321</v>
+        <v>69140.60259459339</v>
       </c>
       <c r="P262" t="n">
         <v>4100</v>
@@ -11979,10 +11979,10 @@
         <v>279</v>
       </c>
       <c r="N267" t="n">
-        <v>3158.8608260699</v>
+        <v>3158.8608262318</v>
       </c>
       <c r="O267" t="n">
-        <v>881322.1704735021</v>
+        <v>881322.1705186721</v>
       </c>
       <c r="P267" t="n">
         <v>5600</v>
@@ -12071,10 +12071,10 @@
         <v>11</v>
       </c>
       <c r="N269" t="n">
-        <v>3841.6247928994</v>
+        <v>3841.6248214286</v>
       </c>
       <c r="O269" t="n">
-        <v>42257.8727218934</v>
+        <v>42257.87303571461</v>
       </c>
       <c r="P269" t="n">
         <v>6900</v>
@@ -12239,25 +12239,25 @@
         <v>23</v>
       </c>
       <c r="K273" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L273" t="n">
         <v>0</v>
       </c>
       <c r="M273" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="N273" t="n">
         <v>3230.0672177419</v>
       </c>
       <c r="O273" t="n">
-        <v>74291.5460080637</v>
+        <v>171193.5625403207</v>
       </c>
       <c r="P273" t="n">
         <v>6200</v>
       </c>
       <c r="Q273" t="n">
-        <v>142600</v>
+        <v>328600</v>
       </c>
     </row>
     <row r="274">
@@ -12375,22 +12375,22 @@
         <v>0</v>
       </c>
       <c r="L276" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M276" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="N276" t="n">
         <v>2341</v>
       </c>
       <c r="O276" t="n">
-        <v>74912</v>
+        <v>70230</v>
       </c>
       <c r="P276" t="n">
         <v>3900</v>
       </c>
       <c r="Q276" t="n">
-        <v>124800</v>
+        <v>117000</v>
       </c>
     </row>
     <row r="277">
@@ -12421,22 +12421,22 @@
         <v>0</v>
       </c>
       <c r="L277" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M277" t="n">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="N277" t="n">
         <v>1337.34</v>
       </c>
       <c r="O277" t="n">
-        <v>292877.46</v>
+        <v>288865.44</v>
       </c>
       <c r="P277" t="n">
         <v>2500</v>
       </c>
       <c r="Q277" t="n">
-        <v>547500</v>
+        <v>540000</v>
       </c>
     </row>
     <row r="278">
@@ -13187,22 +13187,22 @@
         <v>0</v>
       </c>
       <c r="L294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M294" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N294" t="n">
         <v>1057.08</v>
       </c>
       <c r="O294" t="n">
-        <v>2114.16</v>
+        <v>1057.08</v>
       </c>
       <c r="P294" t="n">
         <v>2800</v>
       </c>
       <c r="Q294" t="n">
-        <v>5600</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="295">
@@ -13239,10 +13239,10 @@
         <v>20</v>
       </c>
       <c r="N295" t="n">
-        <v>4890.9300487805</v>
+        <v>4890.93004884</v>
       </c>
       <c r="O295" t="n">
-        <v>97818.60097561001</v>
+        <v>97818.60097680001</v>
       </c>
       <c r="P295" t="n">
         <v>8200</v>
@@ -13692,10 +13692,10 @@
         <v>1</v>
       </c>
       <c r="N305" t="n">
-        <v>3594.2540186916</v>
+        <v>3594.254</v>
       </c>
       <c r="O305" t="n">
-        <v>3594.2540186916</v>
+        <v>3594.254</v>
       </c>
       <c r="P305" t="n">
         <v>6500</v>
@@ -13955,22 +13955,22 @@
         <v>0</v>
       </c>
       <c r="L311" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M311" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="N311" t="n">
-        <v>3240.8500325733</v>
+        <v>3240.850037037</v>
       </c>
       <c r="O311" t="n">
-        <v>158801.6515960917</v>
+        <v>152319.951740739</v>
       </c>
       <c r="P311" t="n">
         <v>5200</v>
       </c>
       <c r="Q311" t="n">
-        <v>254800</v>
+        <v>244400</v>
       </c>
     </row>
     <row r="312">
@@ -14091,22 +14091,22 @@
         <v>0</v>
       </c>
       <c r="L314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M314" t="n">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="N314" t="n">
         <v>2090.85</v>
       </c>
       <c r="O314" t="n">
-        <v>503894.85</v>
+        <v>501804</v>
       </c>
       <c r="P314" t="n">
         <v>2900</v>
       </c>
       <c r="Q314" t="n">
-        <v>698900</v>
+        <v>696000</v>
       </c>
     </row>
     <row r="315">
@@ -14997,10 +14997,10 @@
         <v>35</v>
       </c>
       <c r="N334" t="n">
-        <v>3041.660013245</v>
+        <v>3041.6600132802</v>
       </c>
       <c r="O334" t="n">
-        <v>106458.100463575</v>
+        <v>106458.100464807</v>
       </c>
       <c r="P334" t="n">
         <v>5500</v>
@@ -15124,25 +15124,25 @@
         <v>109</v>
       </c>
       <c r="K337" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L337" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M337" t="n">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="N337" t="n">
-        <v>1592.566762142</v>
+        <v>1592.5667254408</v>
       </c>
       <c r="O337" t="n">
-        <v>173589.777073478</v>
+        <v>208626.2410327448</v>
       </c>
       <c r="P337" t="n">
         <v>3900</v>
       </c>
       <c r="Q337" t="n">
-        <v>425100</v>
+        <v>510900</v>
       </c>
     </row>
     <row r="338">
@@ -15209,22 +15209,22 @@
         <v>0</v>
       </c>
       <c r="L339" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M339" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N339" t="n">
         <v>2224.56</v>
       </c>
       <c r="O339" t="n">
-        <v>57838.56</v>
+        <v>51164.88</v>
       </c>
       <c r="P339" t="n">
         <v>3900</v>
       </c>
       <c r="Q339" t="n">
-        <v>101400</v>
+        <v>89700</v>
       </c>
     </row>
     <row r="340">
@@ -15921,22 +15921,22 @@
         <v>0</v>
       </c>
       <c r="L355" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M355" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="N355" t="n">
         <v>1387.55</v>
       </c>
       <c r="O355" t="n">
-        <v>113779.1</v>
+        <v>111004</v>
       </c>
       <c r="P355" t="n">
         <v>2300</v>
       </c>
       <c r="Q355" t="n">
-        <v>188600</v>
+        <v>184000</v>
       </c>
     </row>
     <row r="356">
@@ -16608,22 +16608,22 @@
         <v>0</v>
       </c>
       <c r="L370" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M370" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N370" t="n">
         <v>11921.4</v>
       </c>
       <c r="O370" t="n">
-        <v>166899.6</v>
+        <v>154978.2</v>
       </c>
       <c r="P370" t="n">
         <v>19900</v>
       </c>
       <c r="Q370" t="n">
-        <v>278600</v>
+        <v>258700</v>
       </c>
     </row>
     <row r="371">
@@ -17059,22 +17059,22 @@
         <v>0</v>
       </c>
       <c r="L380" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M380" t="n">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="N380" t="n">
-        <v>1630.9235901027</v>
+        <v>1630.9236367936</v>
       </c>
       <c r="O380" t="n">
-        <v>415885.5154761885</v>
+        <v>386528.9019200832</v>
       </c>
       <c r="P380" t="n">
         <v>2500</v>
       </c>
       <c r="Q380" t="n">
-        <v>637500</v>
+        <v>592500</v>
       </c>
     </row>
     <row r="381">
@@ -17157,10 +17157,10 @@
         <v>30</v>
       </c>
       <c r="N382" t="n">
-        <v>1690.5972035794</v>
+        <v>1690.5971524664</v>
       </c>
       <c r="O382" t="n">
-        <v>50717.916107382</v>
+        <v>50717.91457399201</v>
       </c>
       <c r="P382" t="n">
         <v>2900</v>
@@ -17197,22 +17197,22 @@
         <v>0</v>
       </c>
       <c r="L383" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M383" t="n">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="N383" t="n">
-        <v>1550.1936753491</v>
+        <v>1550.1936973199</v>
       </c>
       <c r="O383" t="n">
-        <v>336392.0275507547</v>
+        <v>328641.0638318188</v>
       </c>
       <c r="P383" t="n">
         <v>2500</v>
       </c>
       <c r="Q383" t="n">
-        <v>542500</v>
+        <v>530000</v>
       </c>
     </row>
     <row r="384">
@@ -17243,22 +17243,22 @@
         <v>0</v>
       </c>
       <c r="L384" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M384" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="N384" t="n">
-        <v>1579.3905526316</v>
+        <v>1579.3904266667</v>
       </c>
       <c r="O384" t="n">
-        <v>52119.8882368428</v>
+        <v>44222.9319466676</v>
       </c>
       <c r="P384" t="n">
         <v>2900</v>
       </c>
       <c r="Q384" t="n">
-        <v>95700</v>
+        <v>81200</v>
       </c>
     </row>
     <row r="385">
@@ -17289,22 +17289,22 @@
         <v>0</v>
       </c>
       <c r="L385" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M385" t="n">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="N385" t="n">
-        <v>2403.5119996136</v>
+        <v>2403.5120742613</v>
       </c>
       <c r="O385" t="n">
-        <v>641737.7038968311</v>
+        <v>615299.0910108928</v>
       </c>
       <c r="P385" t="n">
         <v>3500</v>
       </c>
       <c r="Q385" t="n">
-        <v>934500</v>
+        <v>896000</v>
       </c>
     </row>
     <row r="386">
@@ -17335,22 +17335,22 @@
         <v>0</v>
       </c>
       <c r="L386" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M386" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N386" t="n">
-        <v>2521.52825</v>
+        <v>2530.9356343284</v>
       </c>
       <c r="O386" t="n">
-        <v>5043.0565</v>
+        <v>2530.9356343284</v>
       </c>
       <c r="P386" t="n">
         <v>3900</v>
       </c>
       <c r="Q386" t="n">
-        <v>7800</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="387">
@@ -19445,10 +19445,10 @@
         <v>7</v>
       </c>
       <c r="N433" t="n">
-        <v>4196.8725291181</v>
+        <v>4196.8725298197</v>
       </c>
       <c r="O433" t="n">
-        <v>29378.1077038267</v>
+        <v>29378.1077087379</v>
       </c>
       <c r="P433" t="n">
         <v>5900</v>
@@ -19527,10 +19527,10 @@
         <v>6</v>
       </c>
       <c r="N435" t="n">
-        <v>7537.4721969697</v>
+        <v>7537.4722307692</v>
       </c>
       <c r="O435" t="n">
-        <v>45224.83318181821</v>
+        <v>45224.8333846152</v>
       </c>
       <c r="P435" t="n">
         <v>8900</v>
@@ -19688,22 +19688,22 @@
         <v>0</v>
       </c>
       <c r="L439" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M439" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N439" t="n">
-        <v>5449.5305128205</v>
+        <v>5449.5305217391</v>
       </c>
       <c r="O439" t="n">
-        <v>65394.366153846</v>
+        <v>54495.305217391</v>
       </c>
       <c r="P439" t="n">
         <v>6200</v>
       </c>
       <c r="Q439" t="n">
-        <v>74400</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="440">
@@ -19811,22 +19811,22 @@
         <v>0</v>
       </c>
       <c r="L442" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M442" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="N442" t="n">
         <v>2517.22</v>
       </c>
       <c r="O442" t="n">
-        <v>93137.14</v>
+        <v>85585.48</v>
       </c>
       <c r="P442" t="n">
         <v>4200</v>
       </c>
       <c r="Q442" t="n">
-        <v>155400</v>
+        <v>142800</v>
       </c>
     </row>
     <row r="443">
@@ -19858,10 +19858,10 @@
         <v>95</v>
       </c>
       <c r="N443" t="n">
-        <v>2029.8738129131</v>
+        <v>2029.8738600103</v>
       </c>
       <c r="O443" t="n">
-        <v>192838.0122267445</v>
+        <v>192838.0167009785</v>
       </c>
       <c r="P443" t="n">
         <v>3600</v>
@@ -20673,10 +20673,10 @@
         <v>1</v>
       </c>
       <c r="N462" t="n">
-        <v>4285.1955097614</v>
+        <v>4285.1955337691</v>
       </c>
       <c r="O462" t="n">
-        <v>4285.1955097614</v>
+        <v>4285.1955337691</v>
       </c>
       <c r="P462" t="n">
         <v>6900</v>
@@ -21049,22 +21049,22 @@
         <v>0</v>
       </c>
       <c r="L471" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M471" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N471" t="n">
         <v>3591.13</v>
       </c>
       <c r="O471" t="n">
-        <v>82595.99000000001</v>
+        <v>79004.86</v>
       </c>
       <c r="P471" t="n">
         <v>6300</v>
       </c>
       <c r="Q471" t="n">
-        <v>144900</v>
+        <v>138600</v>
       </c>
     </row>
     <row r="472">
@@ -21884,10 +21884,10 @@
         <v>16</v>
       </c>
       <c r="N490" t="n">
-        <v>1561.0003205128</v>
+        <v>1561.0009152542</v>
       </c>
       <c r="O490" t="n">
-        <v>24976.0051282048</v>
+        <v>24976.0146440672</v>
       </c>
       <c r="P490" t="n">
         <v>2900</v>
@@ -22801,22 +22801,22 @@
         <v>0</v>
       </c>
       <c r="L511" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M511" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N511" t="n">
-        <v>12956</v>
+        <v>0</v>
       </c>
       <c r="O511" t="n">
-        <v>12956</v>
+        <v>0</v>
       </c>
       <c r="P511" t="n">
         <v>22100</v>
       </c>
       <c r="Q511" t="n">
-        <v>22100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="512">
@@ -23192,10 +23192,10 @@
         <v>114</v>
       </c>
       <c r="N520" t="n">
-        <v>548.14720461095</v>
+        <v>548.1471884058</v>
       </c>
       <c r="O520" t="n">
-        <v>62488.7813256483</v>
+        <v>62488.7794782612</v>
       </c>
       <c r="P520" t="n">
         <v>2000</v>
@@ -23668,22 +23668,22 @@
         <v>0</v>
       </c>
       <c r="L531" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M531" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N531" t="n">
         <v>6240.75</v>
       </c>
       <c r="O531" t="n">
-        <v>93611.25</v>
+        <v>87370.5</v>
       </c>
       <c r="P531" t="n">
         <v>13900</v>
       </c>
       <c r="Q531" t="n">
-        <v>208500</v>
+        <v>194600</v>
       </c>
     </row>
     <row r="532">
@@ -24029,22 +24029,22 @@
         <v>0</v>
       </c>
       <c r="L539" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M539" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N539" t="n">
         <v>2634.61</v>
       </c>
       <c r="O539" t="n">
-        <v>44788.37</v>
+        <v>39519.15</v>
       </c>
       <c r="P539" t="n">
         <v>4200</v>
       </c>
       <c r="Q539" t="n">
-        <v>71400</v>
+        <v>63000</v>
       </c>
     </row>
     <row r="540">
@@ -24719,22 +24719,22 @@
         <v>0</v>
       </c>
       <c r="L554" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M554" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N554" t="n">
         <v>10977.27</v>
       </c>
       <c r="O554" t="n">
-        <v>32931.81</v>
+        <v>21954.54</v>
       </c>
       <c r="P554" t="n">
         <v>17900</v>
       </c>
       <c r="Q554" t="n">
-        <v>53700</v>
+        <v>35800</v>
       </c>
     </row>
     <row r="555">
@@ -25502,10 +25502,10 @@
         <v>128</v>
       </c>
       <c r="N571" t="n">
-        <v>1778.4726299141</v>
+        <v>1778.4726458554</v>
       </c>
       <c r="O571" t="n">
-        <v>227644.4966290048</v>
+        <v>227644.4986694912</v>
       </c>
       <c r="P571" t="n">
         <v>4900</v>
@@ -27304,22 +27304,22 @@
         <v>0</v>
       </c>
       <c r="L610" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M610" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N610" t="n">
         <v>12709</v>
       </c>
       <c r="O610" t="n">
-        <v>88963</v>
+        <v>76254</v>
       </c>
       <c r="P610" t="n">
         <v>20500</v>
       </c>
       <c r="Q610" t="n">
-        <v>143500</v>
+        <v>123000</v>
       </c>
     </row>
     <row r="611">
@@ -27532,22 +27532,22 @@
         <v>0</v>
       </c>
       <c r="L615" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M615" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N615" t="n">
         <v>4136</v>
       </c>
       <c r="O615" t="n">
-        <v>37224</v>
+        <v>33088</v>
       </c>
       <c r="P615" t="n">
         <v>6900</v>
       </c>
       <c r="Q615" t="n">
-        <v>62100</v>
+        <v>55200</v>
       </c>
     </row>
     <row r="616">
@@ -27716,22 +27716,22 @@
         <v>0</v>
       </c>
       <c r="L619" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M619" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N619" t="n">
         <v>13019</v>
       </c>
       <c r="O619" t="n">
-        <v>820197</v>
+        <v>807178</v>
       </c>
       <c r="P619" t="n">
         <v>20900</v>
       </c>
       <c r="Q619" t="n">
-        <v>1316700</v>
+        <v>1295800</v>
       </c>
     </row>
     <row r="620">
@@ -28080,22 +28080,22 @@
         <v>0</v>
       </c>
       <c r="L627" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M627" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="N627" t="n">
-        <v>2328.1187114504</v>
+        <v>2328.1187098747</v>
       </c>
       <c r="O627" t="n">
-        <v>249108.7021251928</v>
+        <v>239796.2271170941</v>
       </c>
       <c r="P627" t="n">
         <v>4500</v>
       </c>
       <c r="Q627" t="n">
-        <v>481500</v>
+        <v>463500</v>
       </c>
     </row>
     <row r="628">
@@ -29555,22 +29555,22 @@
         <v>0</v>
       </c>
       <c r="L659" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M659" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N659" t="n">
         <v>6268</v>
       </c>
       <c r="O659" t="n">
-        <v>351008</v>
+        <v>344740</v>
       </c>
       <c r="P659" t="n">
         <v>10900</v>
       </c>
       <c r="Q659" t="n">
-        <v>610400</v>
+        <v>599500</v>
       </c>
     </row>
     <row r="660">
@@ -30061,22 +30061,22 @@
         <v>0</v>
       </c>
       <c r="L670" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M670" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N670" t="n">
         <v>5682</v>
       </c>
       <c r="O670" t="n">
-        <v>28410</v>
+        <v>22728</v>
       </c>
       <c r="P670" t="n">
         <v>9900</v>
       </c>
       <c r="Q670" t="n">
-        <v>49500</v>
+        <v>39600</v>
       </c>
     </row>
     <row r="671">
@@ -30435,10 +30435,10 @@
         <v>31</v>
       </c>
       <c r="N678" t="n">
-        <v>17075.989523151</v>
+        <v>17075.989522822</v>
       </c>
       <c r="O678" t="n">
-        <v>529355.6752176811</v>
+        <v>529355.6752074821</v>
       </c>
       <c r="P678" t="n">
         <v>27500</v>
@@ -30698,22 +30698,22 @@
         <v>0</v>
       </c>
       <c r="L684" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M684" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N684" t="n">
         <v>59834</v>
       </c>
       <c r="O684" t="n">
-        <v>2034356</v>
+        <v>1914688</v>
       </c>
       <c r="P684" t="n">
         <v>7900</v>
       </c>
       <c r="Q684" t="n">
-        <v>268600</v>
+        <v>252800</v>
       </c>
     </row>
     <row r="685">
@@ -31250,22 +31250,22 @@
         <v>0</v>
       </c>
       <c r="L696" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M696" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N696" t="n">
         <v>3639.35</v>
       </c>
       <c r="O696" t="n">
-        <v>123737.9</v>
+        <v>116459.2</v>
       </c>
       <c r="P696" t="n">
         <v>7500</v>
       </c>
       <c r="Q696" t="n">
-        <v>255000</v>
+        <v>240000</v>
       </c>
     </row>
     <row r="697">
@@ -31296,22 +31296,22 @@
         <v>0</v>
       </c>
       <c r="L697" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M697" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N697" t="n">
         <v>1326</v>
       </c>
       <c r="O697" t="n">
-        <v>37128</v>
+        <v>34476</v>
       </c>
       <c r="P697" t="n">
         <v>2500</v>
       </c>
       <c r="Q697" t="n">
-        <v>70000</v>
+        <v>65000</v>
       </c>
     </row>
     <row r="698">
@@ -31811,10 +31811,10 @@
         <v>70</v>
       </c>
       <c r="N708" t="n">
-        <v>1516.0387982037</v>
+        <v>1516.0387951453</v>
       </c>
       <c r="O708" t="n">
-        <v>106122.715874259</v>
+        <v>106122.715660171</v>
       </c>
       <c r="P708" t="n">
         <v>2300</v>
@@ -31894,25 +31894,25 @@
         <v>82</v>
       </c>
       <c r="K710" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="L710" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M710" t="n">
-        <v>82</v>
+        <v>129</v>
       </c>
       <c r="N710" t="n">
-        <v>2458.5131328074</v>
+        <v>2458.5130759032</v>
       </c>
       <c r="O710" t="n">
-        <v>201598.0768902068</v>
+        <v>317148.1867915128</v>
       </c>
       <c r="P710" t="n">
         <v>3500</v>
       </c>
       <c r="Q710" t="n">
-        <v>287000</v>
+        <v>451500</v>
       </c>
     </row>
     <row r="711">
@@ -32041,10 +32041,10 @@
         <v>225</v>
       </c>
       <c r="N713" t="n">
-        <v>2079.3840254521</v>
+        <v>2079.3839709361</v>
       </c>
       <c r="O713" t="n">
-        <v>467861.4057267225</v>
+        <v>467861.3934606225</v>
       </c>
       <c r="P713" t="n">
         <v>2900</v>
@@ -32087,10 +32087,10 @@
         <v>188</v>
       </c>
       <c r="N714" t="n">
-        <v>1803.0156051587</v>
+        <v>1803.0156237558</v>
       </c>
       <c r="O714" t="n">
-        <v>338966.9337698356</v>
+        <v>338966.9372660904</v>
       </c>
       <c r="P714" t="n">
         <v>2500</v>
@@ -32124,25 +32124,25 @@
         <v>23</v>
       </c>
       <c r="K715" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L715" t="n">
         <v>0</v>
       </c>
       <c r="M715" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="N715" t="n">
-        <v>3306.5951153324</v>
+        <v>3306.5946745562</v>
       </c>
       <c r="O715" t="n">
-        <v>76051.6876526452</v>
+        <v>115730.813609467</v>
       </c>
       <c r="P715" t="n">
         <v>4900</v>
       </c>
       <c r="Q715" t="n">
-        <v>112700</v>
+        <v>171500</v>
       </c>
     </row>
     <row r="716">
@@ -32173,22 +32173,22 @@
         <v>0</v>
       </c>
       <c r="L716" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M716" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="N716" t="n">
-        <v>2122.1638529227</v>
+        <v>2122.1638509903</v>
       </c>
       <c r="O716" t="n">
-        <v>630282.6643180419</v>
+        <v>628160.4998931288</v>
       </c>
       <c r="P716" t="n">
         <v>2900</v>
       </c>
       <c r="Q716" t="n">
-        <v>861300</v>
+        <v>858400</v>
       </c>
     </row>
     <row r="717">
@@ -32216,25 +32216,25 @@
         <v>168</v>
       </c>
       <c r="K717" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="L717" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M717" t="n">
-        <v>168</v>
+        <v>211</v>
       </c>
       <c r="N717" t="n">
-        <v>2108.7920330806</v>
+        <v>2108.792083045</v>
       </c>
       <c r="O717" t="n">
-        <v>354277.0615575408</v>
+        <v>444955.129522495</v>
       </c>
       <c r="P717" t="n">
         <v>2900</v>
       </c>
       <c r="Q717" t="n">
-        <v>487200</v>
+        <v>611900</v>
       </c>
     </row>
     <row r="718">
@@ -32262,25 +32262,25 @@
         <v>183</v>
       </c>
       <c r="K718" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L718" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M718" t="n">
-        <v>183</v>
+        <v>272</v>
       </c>
       <c r="N718" t="n">
-        <v>2056.0831723454</v>
+        <v>2056.0829891304</v>
       </c>
       <c r="O718" t="n">
-        <v>376263.2205392082</v>
+        <v>559254.5730434689</v>
       </c>
       <c r="P718" t="n">
         <v>2900</v>
       </c>
       <c r="Q718" t="n">
-        <v>530700</v>
+        <v>788800</v>
       </c>
     </row>
     <row r="719">
@@ -32308,25 +32308,25 @@
         <v>123</v>
       </c>
       <c r="K719" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="L719" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M719" t="n">
-        <v>123</v>
+        <v>157</v>
       </c>
       <c r="N719" t="n">
-        <v>3224.5688003933</v>
+        <v>3224.5688090551</v>
       </c>
       <c r="O719" t="n">
-        <v>396621.9624483759</v>
+        <v>506257.3030216506</v>
       </c>
       <c r="P719" t="n">
         <v>4500</v>
       </c>
       <c r="Q719" t="n">
-        <v>553500</v>
+        <v>706500</v>
       </c>
     </row>
     <row r="720">
@@ -32354,25 +32354,25 @@
         <v>128</v>
       </c>
       <c r="K720" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="L720" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M720" t="n">
-        <v>128</v>
+        <v>172</v>
       </c>
       <c r="N720" t="n">
-        <v>1655.9308592201</v>
+        <v>1655.9308045213</v>
       </c>
       <c r="O720" t="n">
-        <v>211959.1499801728</v>
+        <v>284820.0983776636</v>
       </c>
       <c r="P720" t="n">
         <v>2500</v>
       </c>
       <c r="Q720" t="n">
-        <v>320000</v>
+        <v>430000</v>
       </c>
     </row>
     <row r="721">
@@ -32642,10 +32642,10 @@
         <v>53</v>
       </c>
       <c r="N726" t="n">
-        <v>1592.2786119257</v>
+        <v>1592.2787749004</v>
       </c>
       <c r="O726" t="n">
-        <v>84390.7664320621</v>
+        <v>84390.7750697212</v>
       </c>
       <c r="P726" t="n">
         <v>2500</v>
@@ -32818,22 +32818,22 @@
         <v>0</v>
       </c>
       <c r="L730" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M730" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="N730" t="n">
-        <v>1906.1836708861</v>
+        <v>1906.1834782609</v>
       </c>
       <c r="O730" t="n">
-        <v>32405.1224050637</v>
+        <v>26686.5686956526</v>
       </c>
       <c r="P730" t="n">
         <v>2900</v>
       </c>
       <c r="Q730" t="n">
-        <v>49300</v>
+        <v>40600</v>
       </c>
     </row>
     <row r="731">
@@ -32864,22 +32864,22 @@
         <v>0</v>
       </c>
       <c r="L731" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M731" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N731" t="n">
-        <v>3033.7172791519</v>
+        <v>3033.7169285714</v>
       </c>
       <c r="O731" t="n">
-        <v>12134.8691166076</v>
+        <v>3033.7169285714</v>
       </c>
       <c r="P731" t="n">
         <v>4500</v>
       </c>
       <c r="Q731" t="n">
-        <v>18000</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="732">
@@ -32916,10 +32916,10 @@
         <v>4</v>
       </c>
       <c r="N732" t="n">
-        <v>2546.9839186296</v>
+        <v>2546.9838660907</v>
       </c>
       <c r="O732" t="n">
-        <v>10187.9356745184</v>
+        <v>10187.9354643628</v>
       </c>
       <c r="P732" t="n">
         <v>3900</v>
@@ -32956,22 +32956,22 @@
         <v>0</v>
       </c>
       <c r="L733" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M733" t="n">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="N733" t="n">
-        <v>1259.2745472973</v>
+        <v>1259.274561681</v>
       </c>
       <c r="O733" t="n">
-        <v>674971.1573513527</v>
+        <v>667415.51769093</v>
       </c>
       <c r="P733" t="n">
         <v>1900</v>
       </c>
       <c r="Q733" t="n">
-        <v>1018400</v>
+        <v>1007000</v>
       </c>
     </row>
     <row r="734">
@@ -33187,10 +33187,10 @@
         <v>3</v>
       </c>
       <c r="N738" t="n">
-        <v>2556.7459385666</v>
+        <v>2556.7460207612</v>
       </c>
       <c r="O738" t="n">
-        <v>7670.2378156998</v>
+        <v>7670.238062283599</v>
       </c>
       <c r="P738" t="n">
         <v>3900</v>
@@ -33227,22 +33227,22 @@
         <v>0</v>
       </c>
       <c r="L739" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M739" t="n">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="N739" t="n">
         <v>1801</v>
       </c>
       <c r="O739" t="n">
-        <v>644758</v>
+        <v>641156</v>
       </c>
       <c r="P739" t="n">
         <v>2900</v>
       </c>
       <c r="Q739" t="n">
-        <v>1038200</v>
+        <v>1032400</v>
       </c>
     </row>
     <row r="740">
@@ -34734,22 +34734,22 @@
         <v>0</v>
       </c>
       <c r="L771" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M771" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="N771" t="n">
         <v>1245.62</v>
       </c>
       <c r="O771" t="n">
-        <v>33631.74</v>
+        <v>31140.5</v>
       </c>
       <c r="P771" t="n">
         <v>4000</v>
       </c>
       <c r="Q771" t="n">
-        <v>108000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="772">
@@ -35614,22 +35614,22 @@
         <v>0</v>
       </c>
       <c r="L790" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M790" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="N790" t="n">
         <v>7559.75</v>
       </c>
       <c r="O790" t="n">
-        <v>143635.25</v>
+        <v>120956</v>
       </c>
       <c r="P790" t="n">
         <v>7900</v>
       </c>
       <c r="Q790" t="n">
-        <v>150100</v>
+        <v>126400</v>
       </c>
     </row>
     <row r="791">
@@ -36794,22 +36794,22 @@
         <v>0</v>
       </c>
       <c r="L815" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M815" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="N815" t="n">
         <v>1326</v>
       </c>
       <c r="O815" t="n">
-        <v>76908</v>
+        <v>74256</v>
       </c>
       <c r="P815" t="n">
         <v>2900</v>
       </c>
       <c r="Q815" t="n">
-        <v>168200</v>
+        <v>162400</v>
       </c>
     </row>
     <row r="816">
@@ -37109,22 +37109,22 @@
         <v>0</v>
       </c>
       <c r="L822" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="M822" t="n">
-        <v>503</v>
+        <v>432</v>
       </c>
       <c r="N822" t="n">
-        <v>517.2898138359</v>
+        <v>517.28990087531</v>
       </c>
       <c r="O822" t="n">
-        <v>260196.7763594577</v>
+        <v>223469.2371781339</v>
       </c>
       <c r="P822" t="n">
         <v>900</v>
       </c>
       <c r="Q822" t="n">
-        <v>452700</v>
+        <v>388800</v>
       </c>
     </row>
     <row r="823">
@@ -37714,22 +37714,22 @@
         <v>0</v>
       </c>
       <c r="L835" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M835" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N835" t="n">
-        <v>3110.8415227818</v>
+        <v>3110.8414032101</v>
       </c>
       <c r="O835" t="n">
-        <v>130655.3439568356</v>
+        <v>127544.4975316141</v>
       </c>
       <c r="P835" t="n">
         <v>4500</v>
       </c>
       <c r="Q835" t="n">
-        <v>189000</v>
+        <v>184500</v>
       </c>
     </row>
     <row r="836">
@@ -37951,10 +37951,10 @@
         <v>212</v>
       </c>
       <c r="N840" t="n">
-        <v>703.795175</v>
+        <v>703.79516919374</v>
       </c>
       <c r="O840" t="n">
-        <v>149204.5771</v>
+        <v>149204.5758690729</v>
       </c>
       <c r="P840" t="n">
         <v>900</v>
@@ -38412,22 +38412,22 @@
         <v>0</v>
       </c>
       <c r="L850" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M850" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N850" t="n">
         <v>7570.87</v>
       </c>
       <c r="O850" t="n">
-        <v>37854.35</v>
+        <v>30283.48</v>
       </c>
       <c r="P850" t="n">
         <v>9500</v>
       </c>
       <c r="Q850" t="n">
-        <v>47500</v>
+        <v>38000</v>
       </c>
     </row>
     <row r="851">
@@ -39436,10 +39436,10 @@
         <v>42</v>
       </c>
       <c r="N872" t="n">
-        <v>1595.5123423818</v>
+        <v>1595.5119633274</v>
       </c>
       <c r="O872" t="n">
-        <v>67011.5183800356</v>
+        <v>67011.5024597508</v>
       </c>
       <c r="P872" t="n">
         <v>2500</v>
@@ -40496,22 +40496,22 @@
         <v>0</v>
       </c>
       <c r="L894" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M894" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N894" t="n">
         <v>10548.76</v>
       </c>
       <c r="O894" t="n">
-        <v>21097.52</v>
+        <v>10548.76</v>
       </c>
       <c r="P894" t="n">
         <v>35900</v>
       </c>
       <c r="Q894" t="n">
-        <v>71800</v>
+        <v>35900</v>
       </c>
     </row>
     <row r="895">
@@ -43541,22 +43541,22 @@
         <v>0</v>
       </c>
       <c r="L957" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M957" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N957" t="n">
         <v>2320.4</v>
       </c>
       <c r="O957" t="n">
-        <v>99777.2</v>
+        <v>97456.8</v>
       </c>
       <c r="P957" t="n">
         <v>4600</v>
       </c>
       <c r="Q957" t="n">
-        <v>197800</v>
+        <v>193200</v>
       </c>
     </row>
     <row r="958">
@@ -45664,22 +45664,22 @@
         <v>0</v>
       </c>
       <c r="L1001" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1001" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N1001" t="n">
         <v>11939.92</v>
       </c>
       <c r="O1001" t="n">
-        <v>35819.76</v>
+        <v>23879.84</v>
       </c>
       <c r="P1001" t="n">
         <v>25900</v>
       </c>
       <c r="Q1001" t="n">
-        <v>77700</v>
+        <v>51800</v>
       </c>
     </row>
     <row r="1002">
@@ -47153,10 +47153,10 @@
         <v>265</v>
       </c>
       <c r="N1032" t="n">
-        <v>7046.9398281418</v>
+        <v>7046.93982792</v>
       </c>
       <c r="O1032" t="n">
-        <v>1867439.054457577</v>
+        <v>1867439.0543988</v>
       </c>
       <c r="P1032" t="n">
         <v>9900</v>
@@ -47974,22 +47974,22 @@
         <v>0</v>
       </c>
       <c r="L1049" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1049" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N1049" t="n">
-        <v>919.27</v>
+        <v>919.2666666666699</v>
       </c>
       <c r="O1049" t="n">
-        <v>2757.81</v>
+        <v>1838.53333333334</v>
       </c>
       <c r="P1049" t="n">
         <v>2400</v>
       </c>
       <c r="Q1049" t="n">
-        <v>7200</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="1050">
@@ -48265,22 +48265,22 @@
         <v>0</v>
       </c>
       <c r="L1055" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1055" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N1055" t="n">
         <v>619.01</v>
       </c>
       <c r="O1055" t="n">
-        <v>3095.05</v>
+        <v>2476.04</v>
       </c>
       <c r="P1055" t="n">
         <v>3500</v>
       </c>
       <c r="Q1055" t="n">
-        <v>17500</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="1056">
@@ -48406,22 +48406,22 @@
         <v>0</v>
       </c>
       <c r="L1058" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1058" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="N1058" t="n">
         <v>1338.14</v>
       </c>
       <c r="O1058" t="n">
-        <v>139166.56</v>
+        <v>135152.14</v>
       </c>
       <c r="P1058" t="n">
         <v>2500</v>
       </c>
       <c r="Q1058" t="n">
-        <v>260000</v>
+        <v>252500</v>
       </c>
     </row>
     <row r="1059">
@@ -48951,10 +48951,10 @@
         <v>73</v>
       </c>
       <c r="N1069" t="n">
-        <v>430.6099761621</v>
+        <v>430.60997607656</v>
       </c>
       <c r="O1069" t="n">
-        <v>31434.5282598333</v>
+        <v>31434.52825358888</v>
       </c>
       <c r="P1069" t="n">
         <v>2200</v>
@@ -49000,10 +49000,10 @@
         <v>37</v>
       </c>
       <c r="N1070" t="n">
-        <v>465.87094835681</v>
+        <v>465.87095553453</v>
       </c>
       <c r="O1070" t="n">
-        <v>17237.22508920197</v>
+        <v>17237.22535477761</v>
       </c>
       <c r="P1070" t="n">
         <v>2500</v>
@@ -49622,22 +49622,22 @@
         <v>0</v>
       </c>
       <c r="L1084" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M1084" t="n">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="N1084" t="n">
         <v>1176.57</v>
       </c>
       <c r="O1084" t="n">
-        <v>230607.72</v>
+        <v>216488.88</v>
       </c>
       <c r="P1084" t="n">
         <v>1900</v>
       </c>
       <c r="Q1084" t="n">
-        <v>372400</v>
+        <v>349600</v>
       </c>
     </row>
     <row r="1085">
@@ -50047,10 +50047,10 @@
         <v>10</v>
       </c>
       <c r="N1093" t="n">
-        <v>22951.704812903</v>
+        <v>22951.704799483</v>
       </c>
       <c r="O1093" t="n">
-        <v>229517.04812903</v>
+        <v>229517.04799483</v>
       </c>
       <c r="P1093" t="n">
         <v>37900</v>
@@ -53816,22 +53816,22 @@
         <v>0</v>
       </c>
       <c r="L1175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1175" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N1175" t="n">
         <v>15482.98</v>
       </c>
       <c r="O1175" t="n">
-        <v>46448.94</v>
+        <v>30965.96</v>
       </c>
       <c r="P1175" t="n">
         <v>18500</v>
       </c>
       <c r="Q1175" t="n">
-        <v>55500</v>
+        <v>37000</v>
       </c>
     </row>
     <row r="1176">
@@ -54348,22 +54348,22 @@
         <v>0</v>
       </c>
       <c r="L1187" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1187" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N1187" t="n">
         <v>3885.95</v>
       </c>
       <c r="O1187" t="n">
-        <v>38859.5</v>
+        <v>34973.55</v>
       </c>
       <c r="P1187" t="n">
         <v>6700</v>
       </c>
       <c r="Q1187" t="n">
-        <v>67000</v>
+        <v>60300</v>
       </c>
     </row>
     <row r="1188">
@@ -55777,22 +55777,22 @@
         <v>0</v>
       </c>
       <c r="L1218" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M1218" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N1218" t="n">
         <v>7480</v>
       </c>
       <c r="O1218" t="n">
-        <v>777920</v>
+        <v>748000</v>
       </c>
       <c r="P1218" t="n">
         <v>9500</v>
       </c>
       <c r="Q1218" t="n">
-        <v>988000</v>
+        <v>950000</v>
       </c>
     </row>
     <row r="1219">
@@ -55823,22 +55823,22 @@
         <v>0</v>
       </c>
       <c r="L1219" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M1219" t="n">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="N1219" t="n">
         <v>6336</v>
       </c>
       <c r="O1219" t="n">
-        <v>849024</v>
+        <v>747648</v>
       </c>
       <c r="P1219" t="n">
         <v>7500</v>
       </c>
       <c r="Q1219" t="n">
-        <v>1005000</v>
+        <v>885000</v>
       </c>
     </row>
     <row r="1220">
@@ -55869,22 +55869,22 @@
         <v>0</v>
       </c>
       <c r="L1220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1220" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N1220" t="n">
         <v>5280</v>
       </c>
       <c r="O1220" t="n">
-        <v>21120</v>
+        <v>15840</v>
       </c>
       <c r="P1220" t="n">
         <v>6900</v>
       </c>
       <c r="Q1220" t="n">
-        <v>27600</v>
+        <v>20700</v>
       </c>
     </row>
     <row r="1221">
@@ -55915,22 +55915,22 @@
         <v>0</v>
       </c>
       <c r="L1221" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1221" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N1221" t="n">
         <v>5280</v>
       </c>
       <c r="O1221" t="n">
-        <v>26400</v>
+        <v>21120</v>
       </c>
       <c r="P1221" t="n">
         <v>6900</v>
       </c>
       <c r="Q1221" t="n">
-        <v>34500</v>
+        <v>27600</v>
       </c>
     </row>
     <row r="1222">
@@ -56007,22 +56007,22 @@
         <v>0</v>
       </c>
       <c r="L1223" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1223" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="N1223" t="n">
         <v>3872</v>
       </c>
       <c r="O1223" t="n">
-        <v>278784</v>
+        <v>271040</v>
       </c>
       <c r="P1223" t="n">
         <v>4900</v>
       </c>
       <c r="Q1223" t="n">
-        <v>352800</v>
+        <v>343000</v>
       </c>
     </row>
     <row r="1224">
@@ -56145,22 +56145,22 @@
         <v>0</v>
       </c>
       <c r="L1226" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1226" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N1226" t="n">
         <v>3520</v>
       </c>
       <c r="O1226" t="n">
-        <v>154880</v>
+        <v>147840</v>
       </c>
       <c r="P1226" t="n">
         <v>4500</v>
       </c>
       <c r="Q1226" t="n">
-        <v>198000</v>
+        <v>189000</v>
       </c>
     </row>
     <row r="1227">
@@ -56191,22 +56191,22 @@
         <v>0</v>
       </c>
       <c r="L1227" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M1227" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="N1227" t="n">
         <v>9240</v>
       </c>
       <c r="O1227" t="n">
-        <v>304920</v>
+        <v>258720</v>
       </c>
       <c r="P1227" t="n">
         <v>11500</v>
       </c>
       <c r="Q1227" t="n">
-        <v>379500</v>
+        <v>322000</v>
       </c>
     </row>
     <row r="1228">
@@ -63633,10 +63633,10 @@
         <v>24</v>
       </c>
       <c r="N1387" t="n">
-        <v>4687.9742393162</v>
+        <v>4687.9742611684</v>
       </c>
       <c r="O1387" t="n">
-        <v>112511.3817435888</v>
+        <v>112511.3822680416</v>
       </c>
       <c r="P1387" t="n">
         <v>5900</v>
@@ -63679,10 +63679,10 @@
         <v>20</v>
       </c>
       <c r="N1388" t="n">
-        <v>4171.6687</v>
+        <v>4171.6686912752</v>
       </c>
       <c r="O1388" t="n">
-        <v>83433.37400000001</v>
+        <v>83433.37382550401</v>
       </c>
       <c r="P1388" t="n">
         <v>5500</v>
@@ -67688,22 +67688,22 @@
         <v>0</v>
       </c>
       <c r="L1476" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1476" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N1476" t="n">
         <v>855.85</v>
       </c>
       <c r="O1476" t="n">
-        <v>45360.05</v>
+        <v>44504.2</v>
       </c>
       <c r="P1476" t="n">
         <v>3500</v>
       </c>
       <c r="Q1476" t="n">
-        <v>185500</v>
+        <v>182000</v>
       </c>
     </row>
     <row r="1477">
@@ -68148,22 +68148,22 @@
         <v>0</v>
       </c>
       <c r="L1486" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1486" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N1486" t="n">
-        <v>4158.2961111111</v>
+        <v>4158.296</v>
       </c>
       <c r="O1486" t="n">
-        <v>12474.8883333333</v>
+        <v>8316.592000000001</v>
       </c>
       <c r="P1486" t="n">
         <v>13800</v>
       </c>
       <c r="Q1486" t="n">
-        <v>41400</v>
+        <v>27600</v>
       </c>
     </row>
     <row r="1487">

--- a/bodegas/02.xlsx
+++ b/bodegas/02.xlsx
@@ -856,10 +856,10 @@
         <v>403</v>
       </c>
       <c r="N11" t="n">
-        <v>1811.307345576</v>
+        <v>1811.3074074074</v>
       </c>
       <c r="O11" t="n">
-        <v>729956.860267128</v>
+        <v>729956.8851851822</v>
       </c>
       <c r="P11" t="n">
         <v>2600</v>
@@ -1609,10 +1609,10 @@
         <v>14</v>
       </c>
       <c r="N30" t="n">
-        <v>3926.8370969414</v>
+        <v>3926.8370954357</v>
       </c>
       <c r="O30" t="n">
-        <v>54975.7193571796</v>
+        <v>54975.7193360998</v>
       </c>
       <c r="P30" t="n">
         <v>4800</v>
@@ -2202,22 +2202,22 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N45" t="n">
         <v>21333.69</v>
       </c>
       <c r="O45" t="n">
-        <v>192003.21</v>
+        <v>170669.52</v>
       </c>
       <c r="P45" t="n">
         <v>30000</v>
       </c>
       <c r="Q45" t="n">
-        <v>270000</v>
+        <v>240000</v>
       </c>
     </row>
     <row r="46">
@@ -3473,10 +3473,10 @@
         <v>21</v>
       </c>
       <c r="N74" t="n">
-        <v>15711.965922747</v>
+        <v>15711.965905172</v>
       </c>
       <c r="O74" t="n">
-        <v>329951.284377687</v>
+        <v>329951.284008612</v>
       </c>
       <c r="P74" t="n">
         <v>28500</v>
@@ -10469,22 +10469,22 @@
         <v>0</v>
       </c>
       <c r="L233" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M233" t="n">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="N233" t="n">
-        <v>1098.0597873486</v>
+        <v>1098.0598890693</v>
       </c>
       <c r="O233" t="n">
-        <v>187768.2236366106</v>
+        <v>175689.582251088</v>
       </c>
       <c r="P233" t="n">
         <v>1500</v>
       </c>
       <c r="Q233" t="n">
-        <v>256500</v>
+        <v>240000</v>
       </c>
     </row>
     <row r="234">
@@ -11979,10 +11979,10 @@
         <v>279</v>
       </c>
       <c r="N267" t="n">
-        <v>3158.8608262318</v>
+        <v>3160.2538267431</v>
       </c>
       <c r="O267" t="n">
-        <v>881322.1705186721</v>
+        <v>881710.8176613249</v>
       </c>
       <c r="P267" t="n">
         <v>5600</v>
@@ -12071,10 +12071,10 @@
         <v>11</v>
       </c>
       <c r="N269" t="n">
-        <v>3841.6248214286</v>
+        <v>3856.9300996016</v>
       </c>
       <c r="O269" t="n">
-        <v>42257.87303571461</v>
+        <v>42426.2310956176</v>
       </c>
       <c r="P269" t="n">
         <v>6900</v>
@@ -12421,22 +12421,22 @@
         <v>0</v>
       </c>
       <c r="L277" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M277" t="n">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="N277" t="n">
         <v>1337.34</v>
       </c>
       <c r="O277" t="n">
-        <v>288865.44</v>
+        <v>283516.08</v>
       </c>
       <c r="P277" t="n">
         <v>2500</v>
       </c>
       <c r="Q277" t="n">
-        <v>540000</v>
+        <v>530000</v>
       </c>
     </row>
     <row r="278">
@@ -12703,22 +12703,22 @@
         <v>0</v>
       </c>
       <c r="L283" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M283" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N283" t="n">
         <v>9664</v>
       </c>
       <c r="O283" t="n">
-        <v>48320</v>
+        <v>38656</v>
       </c>
       <c r="P283" t="n">
         <v>15900</v>
       </c>
       <c r="Q283" t="n">
-        <v>79500</v>
+        <v>63600</v>
       </c>
     </row>
     <row r="284">
@@ -13692,10 +13692,10 @@
         <v>11</v>
       </c>
       <c r="N305" t="n">
-        <v>3594.254</v>
+        <v>3594.2539962477</v>
       </c>
       <c r="O305" t="n">
-        <v>39536.794</v>
+        <v>39536.7939587247</v>
       </c>
       <c r="P305" t="n">
         <v>6500</v>
@@ -14097,10 +14097,10 @@
         <v>240</v>
       </c>
       <c r="N314" t="n">
-        <v>2090.85</v>
+        <v>2091.1308394896</v>
       </c>
       <c r="O314" t="n">
-        <v>501804</v>
+        <v>501871.401477504</v>
       </c>
       <c r="P314" t="n">
         <v>2900</v>
@@ -15043,10 +15043,10 @@
         <v>54</v>
       </c>
       <c r="N335" t="n">
-        <v>4372.2107903559</v>
+        <v>4372.2107904123</v>
       </c>
       <c r="O335" t="n">
-        <v>236099.3826792186</v>
+        <v>236099.3826822642</v>
       </c>
       <c r="P335" t="n">
         <v>7500</v>
@@ -15127,22 +15127,22 @@
         <v>0</v>
       </c>
       <c r="L337" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M337" t="n">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="N337" t="n">
-        <v>1592.5667254408</v>
+        <v>1600.6713740458</v>
       </c>
       <c r="O337" t="n">
-        <v>208626.2410327448</v>
+        <v>200083.921755725</v>
       </c>
       <c r="P337" t="n">
         <v>3900</v>
       </c>
       <c r="Q337" t="n">
-        <v>510900</v>
+        <v>487500</v>
       </c>
     </row>
     <row r="338">
@@ -15209,22 +15209,22 @@
         <v>0</v>
       </c>
       <c r="L339" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M339" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N339" t="n">
         <v>2224.56</v>
       </c>
       <c r="O339" t="n">
-        <v>51164.88</v>
+        <v>48940.32</v>
       </c>
       <c r="P339" t="n">
         <v>3900</v>
       </c>
       <c r="Q339" t="n">
-        <v>89700</v>
+        <v>85800</v>
       </c>
     </row>
     <row r="340">
@@ -16240,22 +16240,22 @@
         <v>0</v>
       </c>
       <c r="L362" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M362" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N362" t="n">
         <v>16897</v>
       </c>
       <c r="O362" t="n">
-        <v>337940</v>
+        <v>321043</v>
       </c>
       <c r="P362" t="n">
         <v>27900</v>
       </c>
       <c r="Q362" t="n">
-        <v>558000</v>
+        <v>530100</v>
       </c>
     </row>
     <row r="363">
@@ -16522,10 +16522,10 @@
         <v>9</v>
       </c>
       <c r="N368" t="n">
-        <v>3761.6</v>
+        <v>3775.3787545788</v>
       </c>
       <c r="O368" t="n">
-        <v>33854.4</v>
+        <v>33978.4087912092</v>
       </c>
       <c r="P368" t="n">
         <v>6900</v>
@@ -17059,22 +17059,22 @@
         <v>0</v>
       </c>
       <c r="L380" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M380" t="n">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="N380" t="n">
-        <v>1630.9236471425</v>
+        <v>1630.9236566809</v>
       </c>
       <c r="O380" t="n">
-        <v>383267.0570784875</v>
+        <v>366957.8227532025</v>
       </c>
       <c r="P380" t="n">
         <v>2500</v>
       </c>
       <c r="Q380" t="n">
-        <v>587500</v>
+        <v>562500</v>
       </c>
     </row>
     <row r="381">
@@ -17157,10 +17157,10 @@
         <v>30</v>
       </c>
       <c r="N382" t="n">
-        <v>1690.5969977427</v>
+        <v>1690.5969630746</v>
       </c>
       <c r="O382" t="n">
-        <v>50717.909932281</v>
+        <v>50717.908892238</v>
       </c>
       <c r="P382" t="n">
         <v>2900</v>
@@ -17197,22 +17197,22 @@
         <v>0</v>
       </c>
       <c r="L383" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M383" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="N383" t="n">
-        <v>1550.1936995315</v>
+        <v>1550.1937050719</v>
       </c>
       <c r="O383" t="n">
-        <v>328641.064300678</v>
+        <v>327090.8717701709</v>
       </c>
       <c r="P383" t="n">
         <v>2500</v>
       </c>
       <c r="Q383" t="n">
-        <v>530000</v>
+        <v>527500</v>
       </c>
     </row>
     <row r="384">
@@ -17249,10 +17249,10 @@
         <v>28</v>
       </c>
       <c r="N384" t="n">
-        <v>1579.3904266667</v>
+        <v>1579.3903753351</v>
       </c>
       <c r="O384" t="n">
-        <v>44222.9319466676</v>
+        <v>44222.9305093828</v>
       </c>
       <c r="P384" t="n">
         <v>2900</v>
@@ -17289,22 +17289,22 @@
         <v>0</v>
       </c>
       <c r="L385" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M385" t="n">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="N385" t="n">
-        <v>2403.5121001364</v>
+        <v>2403.5121166602</v>
       </c>
       <c r="O385" t="n">
-        <v>615299.0976349184</v>
+        <v>605685.0533983704</v>
       </c>
       <c r="P385" t="n">
         <v>3500</v>
       </c>
       <c r="Q385" t="n">
-        <v>896000</v>
+        <v>882000</v>
       </c>
     </row>
     <row r="386">
@@ -20147,22 +20147,22 @@
         <v>0</v>
       </c>
       <c r="L450" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M450" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N450" t="n">
-        <v>2680.739695084</v>
+        <v>2680.7396948941</v>
       </c>
       <c r="O450" t="n">
-        <v>26807.39695084</v>
+        <v>24126.6572540469</v>
       </c>
       <c r="P450" t="n">
         <v>4900</v>
       </c>
       <c r="Q450" t="n">
-        <v>49000</v>
+        <v>44100</v>
       </c>
     </row>
     <row r="451">
@@ -21884,10 +21884,10 @@
         <v>16</v>
       </c>
       <c r="N490" t="n">
-        <v>1561.0009337861</v>
+        <v>1561.000952381</v>
       </c>
       <c r="O490" t="n">
-        <v>24976.0149405776</v>
+        <v>24976.015238096</v>
       </c>
       <c r="P490" t="n">
         <v>2900</v>
@@ -23988,22 +23988,22 @@
         <v>0</v>
       </c>
       <c r="L538" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M538" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N538" t="n">
         <v>2634.61</v>
       </c>
       <c r="O538" t="n">
-        <v>39519.15</v>
+        <v>36884.54</v>
       </c>
       <c r="P538" t="n">
         <v>4200</v>
       </c>
       <c r="Q538" t="n">
-        <v>63000</v>
+        <v>58800</v>
       </c>
     </row>
     <row r="539">
@@ -24080,22 +24080,22 @@
         <v>0</v>
       </c>
       <c r="L540" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M540" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N540" t="n">
         <v>5410.72</v>
       </c>
       <c r="O540" t="n">
-        <v>16232.16</v>
+        <v>10821.44</v>
       </c>
       <c r="P540" t="n">
         <v>8700</v>
       </c>
       <c r="Q540" t="n">
-        <v>26100</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="541">
@@ -28738,10 +28738,10 @@
         <v>36</v>
       </c>
       <c r="N641" t="n">
-        <v>4907.822092257</v>
+        <v>4956.8186522463</v>
       </c>
       <c r="O641" t="n">
-        <v>176681.595321252</v>
+        <v>178445.4714808668</v>
       </c>
       <c r="P641" t="n">
         <v>8200</v>
@@ -30565,22 +30565,22 @@
         <v>0</v>
       </c>
       <c r="L681" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M681" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N681" t="n">
         <v>11015</v>
       </c>
       <c r="O681" t="n">
-        <v>132180</v>
+        <v>121165</v>
       </c>
       <c r="P681" t="n">
         <v>17900</v>
       </c>
       <c r="Q681" t="n">
-        <v>214800</v>
+        <v>196900</v>
       </c>
     </row>
     <row r="682">
@@ -31994,22 +31994,22 @@
         <v>0</v>
       </c>
       <c r="L712" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M712" t="n">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="N712" t="n">
-        <v>1803.0156237558</v>
+        <v>1803.0156368474</v>
       </c>
       <c r="O712" t="n">
-        <v>338966.9372660904</v>
+        <v>328148.8459062268</v>
       </c>
       <c r="P712" t="n">
         <v>2500</v>
       </c>
       <c r="Q712" t="n">
-        <v>470000</v>
+        <v>455000</v>
       </c>
     </row>
     <row r="713">
@@ -32046,10 +32046,10 @@
         <v>35</v>
       </c>
       <c r="N713" t="n">
-        <v>3306.5946745562</v>
+        <v>3306.5946666667</v>
       </c>
       <c r="O713" t="n">
-        <v>115730.813609467</v>
+        <v>115730.8133333345</v>
       </c>
       <c r="P713" t="n">
         <v>4900</v>
@@ -32184,10 +32184,10 @@
         <v>272</v>
       </c>
       <c r="N716" t="n">
-        <v>2056.0829843644</v>
+        <v>2056.0829819789</v>
       </c>
       <c r="O716" t="n">
-        <v>559254.5717471169</v>
+        <v>559254.5710982608</v>
       </c>
       <c r="P716" t="n">
         <v>2900</v>
@@ -32270,22 +32270,22 @@
         <v>0</v>
       </c>
       <c r="L718" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M718" t="n">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="N718" t="n">
-        <v>1655.9308045213</v>
+        <v>1655.9307861426</v>
       </c>
       <c r="O718" t="n">
-        <v>284820.0983776636</v>
+        <v>274884.5104996716</v>
       </c>
       <c r="P718" t="n">
         <v>2500</v>
       </c>
       <c r="Q718" t="n">
-        <v>430000</v>
+        <v>415000</v>
       </c>
     </row>
     <row r="719">
@@ -32555,10 +32555,10 @@
         <v>51</v>
       </c>
       <c r="N724" t="n">
-        <v>1592.27881</v>
+        <v>1592.2788188188</v>
       </c>
       <c r="O724" t="n">
-        <v>81206.21931</v>
+        <v>81206.21975975879</v>
       </c>
       <c r="P724" t="n">
         <v>2500</v>
@@ -32737,10 +32737,10 @@
         <v>10</v>
       </c>
       <c r="N728" t="n">
-        <v>1906.1829245283</v>
+        <v>1906.1827536232</v>
       </c>
       <c r="O728" t="n">
-        <v>19061.829245283</v>
+        <v>19061.827536232</v>
       </c>
       <c r="P728" t="n">
         <v>2900</v>
@@ -32783,10 +32783,10 @@
         <v>1</v>
       </c>
       <c r="N729" t="n">
-        <v>3033.7169285714</v>
+        <v>3033.7165703971</v>
       </c>
       <c r="O729" t="n">
-        <v>3033.7169285714</v>
+        <v>3033.7165703971</v>
       </c>
       <c r="P729" t="n">
         <v>4500</v>
@@ -34555,22 +34555,22 @@
         <v>0</v>
       </c>
       <c r="L767" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M767" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N767" t="n">
         <v>3930.38</v>
       </c>
       <c r="O767" t="n">
-        <v>31443.04</v>
+        <v>27512.66</v>
       </c>
       <c r="P767" t="n">
         <v>7500</v>
       </c>
       <c r="Q767" t="n">
-        <v>60000</v>
+        <v>52500</v>
       </c>
     </row>
     <row r="768">
@@ -34883,10 +34883,10 @@
         <v>8</v>
       </c>
       <c r="N774" t="n">
-        <v>3629.36</v>
+        <v>3642.7032352941</v>
       </c>
       <c r="O774" t="n">
-        <v>29034.88</v>
+        <v>29141.6258823528</v>
       </c>
       <c r="P774" t="n">
         <v>3900</v>
@@ -35481,22 +35481,22 @@
         <v>0</v>
       </c>
       <c r="L787" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M787" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="N787" t="n">
         <v>7103.81</v>
       </c>
       <c r="O787" t="n">
-        <v>333879.07</v>
+        <v>305463.83</v>
       </c>
       <c r="P787" t="n">
         <v>8900</v>
       </c>
       <c r="Q787" t="n">
-        <v>418300</v>
+        <v>382700</v>
       </c>
     </row>
     <row r="788">
@@ -35868,10 +35868,10 @@
         <v>15</v>
       </c>
       <c r="N795" t="n">
-        <v>6090.22</v>
+        <v>6160.2225287356</v>
       </c>
       <c r="O795" t="n">
-        <v>91353.3</v>
+        <v>92403.337931034</v>
       </c>
       <c r="P795" t="n">
         <v>8500</v>
@@ -37028,10 +37028,10 @@
         <v>1547</v>
       </c>
       <c r="N820" t="n">
-        <v>517.2899423715</v>
+        <v>517.28997081144</v>
       </c>
       <c r="O820" t="n">
-        <v>800247.5408487106</v>
+        <v>800247.5848452976</v>
       </c>
       <c r="P820" t="n">
         <v>900</v>
@@ -37633,10 +37633,10 @@
         <v>41</v>
       </c>
       <c r="N833" t="n">
-        <v>3110.8413822526</v>
+        <v>3110.8413717354</v>
       </c>
       <c r="O833" t="n">
-        <v>127544.4966723566</v>
+        <v>127544.4962411514</v>
       </c>
       <c r="P833" t="n">
         <v>4500</v>
@@ -37858,22 +37858,22 @@
         <v>0</v>
       </c>
       <c r="L838" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M838" t="n">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="N838" t="n">
-        <v>703.79516599434</v>
+        <v>703.79516401441</v>
       </c>
       <c r="O838" t="n">
-        <v>149204.5751908001</v>
+        <v>142166.6231309108</v>
       </c>
       <c r="P838" t="n">
         <v>900</v>
       </c>
       <c r="Q838" t="n">
-        <v>190800</v>
+        <v>181800</v>
       </c>
     </row>
     <row r="839">
@@ -38515,10 +38515,10 @@
         <v>7</v>
       </c>
       <c r="N852" t="n">
-        <v>2501.3849767442</v>
+        <v>2501.384953271</v>
       </c>
       <c r="O852" t="n">
-        <v>17509.6948372094</v>
+        <v>17509.694672897</v>
       </c>
       <c r="P852" t="n">
         <v>4100</v>
@@ -40219,10 +40219,10 @@
         <v>33</v>
       </c>
       <c r="N888" t="n">
-        <v>2098.4050144928</v>
+        <v>2110.6406122449</v>
       </c>
       <c r="O888" t="n">
-        <v>69247.36547826241</v>
+        <v>69651.14020408169</v>
       </c>
       <c r="P888" t="n">
         <v>9500</v>
@@ -43019,10 +43019,10 @@
         <v>13</v>
       </c>
       <c r="N946" t="n">
-        <v>2992.5689285714</v>
+        <v>3065.5584146341</v>
       </c>
       <c r="O946" t="n">
-        <v>38903.3960714282</v>
+        <v>39852.2593902433</v>
       </c>
       <c r="P946" t="n">
         <v>6000</v>
@@ -48040,10 +48040,10 @@
         <v>49</v>
       </c>
       <c r="N1050" t="n">
-        <v>665.32359209922</v>
+        <v>665.32360534809</v>
       </c>
       <c r="O1050" t="n">
-        <v>32600.85601286178</v>
+        <v>32600.85666205641</v>
       </c>
       <c r="P1050" t="n">
         <v>2900</v>
@@ -49500,10 +49500,10 @@
         <v>108</v>
       </c>
       <c r="N1081" t="n">
-        <v>1008.8168311195</v>
+        <v>1008.8166794626</v>
       </c>
       <c r="O1081" t="n">
-        <v>108952.217760906</v>
+        <v>108952.2013819608</v>
       </c>
       <c r="P1081" t="n">
         <v>1500</v>
@@ -49535,22 +49535,22 @@
         <v>0</v>
       </c>
       <c r="L1082" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M1082" t="n">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="N1082" t="n">
         <v>1176.57</v>
       </c>
       <c r="O1082" t="n">
-        <v>210606.03</v>
+        <v>195310.62</v>
       </c>
       <c r="P1082" t="n">
         <v>1900</v>
       </c>
       <c r="Q1082" t="n">
-        <v>340100</v>
+        <v>315400</v>
       </c>
     </row>
     <row r="1083">
@@ -50291,22 +50291,22 @@
         <v>0</v>
       </c>
       <c r="L1098" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1098" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N1098" t="n">
-        <v>2367.1669565217</v>
+        <v>2367.1668181818</v>
       </c>
       <c r="O1098" t="n">
-        <v>35507.5043478255</v>
+        <v>33140.3354545452</v>
       </c>
       <c r="P1098" t="n">
         <v>2900</v>
       </c>
       <c r="Q1098" t="n">
-        <v>43500</v>
+        <v>40600</v>
       </c>
     </row>
     <row r="1099">
@@ -55736,22 +55736,22 @@
         <v>0</v>
       </c>
       <c r="L1217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1217" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N1217" t="n">
         <v>6336</v>
       </c>
       <c r="O1217" t="n">
-        <v>734976</v>
+        <v>728640</v>
       </c>
       <c r="P1217" t="n">
         <v>7500</v>
       </c>
       <c r="Q1217" t="n">
-        <v>870000</v>
+        <v>862500</v>
       </c>
     </row>
     <row r="1218">
@@ -55788,10 +55788,10 @@
         <v>3</v>
       </c>
       <c r="N1218" t="n">
-        <v>5280</v>
+        <v>5305.2631578947</v>
       </c>
       <c r="O1218" t="n">
-        <v>15840</v>
+        <v>15915.7894736841</v>
       </c>
       <c r="P1218" t="n">
         <v>6900</v>
@@ -55834,10 +55834,10 @@
         <v>4</v>
       </c>
       <c r="N1219" t="n">
-        <v>5280</v>
+        <v>5301.8181818182</v>
       </c>
       <c r="O1219" t="n">
-        <v>21120</v>
+        <v>21207.2727272728</v>
       </c>
       <c r="P1219" t="n">
         <v>6900</v>
@@ -55874,22 +55874,22 @@
         <v>0</v>
       </c>
       <c r="L1220" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1220" t="n">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="N1220" t="n">
         <v>1584</v>
       </c>
       <c r="O1220" t="n">
-        <v>191664</v>
+        <v>186912</v>
       </c>
       <c r="P1220" t="n">
         <v>2000</v>
       </c>
       <c r="Q1220" t="n">
-        <v>242000</v>
+        <v>236000</v>
       </c>
     </row>
     <row r="1221">
@@ -59556,10 +59556,10 @@
         <v>2</v>
       </c>
       <c r="N1299" t="n">
-        <v>1319.360887574</v>
+        <v>1327.2142261905</v>
       </c>
       <c r="O1299" t="n">
-        <v>2638.721775148</v>
+        <v>2654.428452381</v>
       </c>
       <c r="P1299" t="n">
         <v>3500</v>
@@ -63500,10 +63500,10 @@
         <v>20</v>
       </c>
       <c r="N1384" t="n">
-        <v>2539.5715559441</v>
+        <v>2539.5715696649</v>
       </c>
       <c r="O1384" t="n">
-        <v>50791.431118882</v>
+        <v>50791.431393298</v>
       </c>
       <c r="P1384" t="n">
         <v>3500</v>
@@ -63546,10 +63546,10 @@
         <v>24</v>
       </c>
       <c r="N1385" t="n">
-        <v>4687.9742611684</v>
+        <v>4687.9742758621</v>
       </c>
       <c r="O1385" t="n">
-        <v>112511.3822680416</v>
+        <v>112511.3826206904</v>
       </c>
       <c r="P1385" t="n">
         <v>5900</v>
@@ -63592,10 +63592,10 @@
         <v>20</v>
       </c>
       <c r="N1386" t="n">
-        <v>4171.6686912752</v>
+        <v>4171.6686824324</v>
       </c>
       <c r="O1386" t="n">
-        <v>83433.37382550401</v>
+        <v>83433.37364864799</v>
       </c>
       <c r="P1386" t="n">
         <v>5500</v>
@@ -68061,22 +68061,22 @@
         <v>0</v>
       </c>
       <c r="L1484" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1484" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N1484" t="n">
-        <v>4158.296</v>
+        <v>4158.2958823529</v>
       </c>
       <c r="O1484" t="n">
-        <v>8316.592000000001</v>
+        <v>4158.2958823529</v>
       </c>
       <c r="P1484" t="n">
         <v>13800</v>
       </c>
       <c r="Q1484" t="n">
-        <v>27600</v>
+        <v>13800</v>
       </c>
     </row>
     <row r="1485">
@@ -70691,22 +70691,22 @@
         <v>0</v>
       </c>
       <c r="L1544" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1544" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N1544" t="n">
-        <v>2403.9772262774</v>
+        <v>2403.9772058824</v>
       </c>
       <c r="O1544" t="n">
-        <v>64907.3851094898</v>
+        <v>62503.40735294241</v>
       </c>
       <c r="P1544" t="n">
         <v>3000</v>
       </c>
       <c r="Q1544" t="n">
-        <v>81000</v>
+        <v>78000</v>
       </c>
     </row>
   </sheetData>

--- a/bodegas/02.xlsx
+++ b/bodegas/02.xlsx
@@ -28745,10 +28745,10 @@
         <v>36</v>
       </c>
       <c r="N641" t="n">
-        <v>4956.8186522463</v>
+        <v>4907.8221131448</v>
       </c>
       <c r="O641" t="n">
-        <v>178445.4714808668</v>
+        <v>176681.5960732128</v>
       </c>
       <c r="P641" t="n">
         <v>8200</v>
@@ -34841,10 +34841,10 @@
         <v>8</v>
       </c>
       <c r="N773" t="n">
-        <v>3642.7032352941</v>
+        <v>3629.36</v>
       </c>
       <c r="O773" t="n">
-        <v>29141.6258823528</v>
+        <v>29034.88</v>
       </c>
       <c r="P773" t="n">
         <v>3900</v>
@@ -35826,10 +35826,10 @@
         <v>15</v>
       </c>
       <c r="N794" t="n">
-        <v>6160.2225287356</v>
+        <v>6090.22</v>
       </c>
       <c r="O794" t="n">
-        <v>92403.337931034</v>
+        <v>91353.3</v>
       </c>
       <c r="P794" t="n">
         <v>8500</v>
@@ -45054,10 +45054,10 @@
         <v>5</v>
       </c>
       <c r="N988" t="n">
-        <v>33063.39</v>
+        <v>22042.26</v>
       </c>
       <c r="O988" t="n">
-        <v>165316.95</v>
+        <v>110211.3</v>
       </c>
       <c r="P988" t="n">
         <v>56000</v>
@@ -59465,10 +59465,10 @@
         <v>2</v>
       </c>
       <c r="N1297" t="n">
-        <v>1327.2142261905</v>
+        <v>1319.3608928571</v>
       </c>
       <c r="O1297" t="n">
-        <v>2654.428452381</v>
+        <v>2638.7217857142</v>
       </c>
       <c r="P1297" t="n">
         <v>3500</v>

--- a/bodegas/02.xlsx
+++ b/bodegas/02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-30</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-31</t>
         </is>
       </c>
     </row>

--- a/bodegas/02.xlsx
+++ b/bodegas/02.xlsx
@@ -3434,10 +3434,10 @@
         <v>21</v>
       </c>
       <c r="N73" t="n">
-        <v>15711.965869565</v>
+        <v>15711.965851528</v>
       </c>
       <c r="O73" t="n">
-        <v>329951.283260865</v>
+        <v>329951.282882088</v>
       </c>
       <c r="P73" t="n">
         <v>28500</v>
@@ -11986,10 +11986,10 @@
         <v>279</v>
       </c>
       <c r="N267" t="n">
-        <v>3158.8608271635</v>
+        <v>3158.8608272041</v>
       </c>
       <c r="O267" t="n">
-        <v>881322.1707786164</v>
+        <v>881322.1707899439</v>
       </c>
       <c r="P267" t="n">
         <v>5600</v>
@@ -13693,22 +13693,22 @@
         <v>0</v>
       </c>
       <c r="L305" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M305" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N305" t="n">
-        <v>3594.2539622642</v>
+        <v>3594.2539546599</v>
       </c>
       <c r="O305" t="n">
-        <v>39536.7935849062</v>
+        <v>32348.2855919391</v>
       </c>
       <c r="P305" t="n">
         <v>6500</v>
       </c>
       <c r="Q305" t="n">
-        <v>71500</v>
+        <v>58500</v>
       </c>
     </row>
     <row r="306">
@@ -13968,10 +13968,10 @@
         <v>39</v>
       </c>
       <c r="N311" t="n">
-        <v>3240.850037594</v>
+        <v>3240.8500375235</v>
       </c>
       <c r="O311" t="n">
-        <v>126393.151466166</v>
+        <v>126393.1514634165</v>
       </c>
       <c r="P311" t="n">
         <v>5200</v>
@@ -14723,22 +14723,22 @@
         <v>0</v>
       </c>
       <c r="L328" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M328" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N328" t="n">
         <v>15851.61</v>
       </c>
       <c r="O328" t="n">
-        <v>253625.76</v>
+        <v>221922.54</v>
       </c>
       <c r="P328" t="n">
         <v>23900</v>
       </c>
       <c r="Q328" t="n">
-        <v>382400</v>
+        <v>334600</v>
       </c>
     </row>
     <row r="329">
@@ -17601,10 +17601,10 @@
         <v>268</v>
       </c>
       <c r="N392" t="n">
-        <v>893.67886945501</v>
+        <v>893.67886888156</v>
       </c>
       <c r="O392" t="n">
-        <v>239505.9370139427</v>
+        <v>239505.9368602581</v>
       </c>
       <c r="P392" t="n">
         <v>1200</v>
@@ -20021,22 +20021,22 @@
         <v>0</v>
       </c>
       <c r="L447" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M447" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N447" t="n">
         <v>15355</v>
       </c>
       <c r="O447" t="n">
-        <v>61420</v>
+        <v>46065</v>
       </c>
       <c r="P447" t="n">
         <v>17900</v>
       </c>
       <c r="Q447" t="n">
-        <v>71600</v>
+        <v>53700</v>
       </c>
     </row>
     <row r="448">
@@ -27452,22 +27452,22 @@
         <v>0</v>
       </c>
       <c r="L613" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M613" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N613" t="n">
         <v>10385</v>
       </c>
       <c r="O613" t="n">
-        <v>83080</v>
+        <v>51925</v>
       </c>
       <c r="P613" t="n">
         <v>16900</v>
       </c>
       <c r="Q613" t="n">
-        <v>135200</v>
+        <v>84500</v>
       </c>
     </row>
     <row r="614">
@@ -31823,10 +31823,10 @@
         <v>164</v>
       </c>
       <c r="N708" t="n">
-        <v>1907.3929677419</v>
+        <v>1907.3929220779</v>
       </c>
       <c r="O708" t="n">
-        <v>312812.4467096716</v>
+        <v>312812.4392207756</v>
       </c>
       <c r="P708" t="n">
         <v>2500</v>
@@ -31961,10 +31961,10 @@
         <v>182</v>
       </c>
       <c r="N711" t="n">
-        <v>1803.0157013118</v>
+        <v>1803.0157128413</v>
       </c>
       <c r="O711" t="n">
-        <v>328148.8576387476</v>
+        <v>328148.8597371166</v>
       </c>
       <c r="P711" t="n">
         <v>2500</v>
@@ -32099,10 +32099,10 @@
         <v>203</v>
       </c>
       <c r="N714" t="n">
-        <v>2108.7924270463</v>
+        <v>2108.7924803431</v>
       </c>
       <c r="O714" t="n">
-        <v>428084.8626903989</v>
+        <v>428084.8735096493</v>
       </c>
       <c r="P714" t="n">
         <v>2900</v>
@@ -32145,10 +32145,10 @@
         <v>248</v>
       </c>
       <c r="N715" t="n">
-        <v>2056.0829120879</v>
+        <v>2056.0828974535</v>
       </c>
       <c r="O715" t="n">
-        <v>509908.5621977992</v>
+        <v>509908.558568468</v>
       </c>
       <c r="P715" t="n">
         <v>2900</v>
@@ -32516,10 +32516,10 @@
         <v>28</v>
       </c>
       <c r="N723" t="n">
-        <v>1592.2799548023</v>
+        <v>1592.2799660633</v>
       </c>
       <c r="O723" t="n">
-        <v>44583.8387344644</v>
+        <v>44583.8390497724</v>
       </c>
       <c r="P723" t="n">
         <v>2500</v>
@@ -33055,22 +33055,22 @@
         <v>0</v>
       </c>
       <c r="L735" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M735" t="n">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="N735" t="n">
         <v>1801</v>
       </c>
       <c r="O735" t="n">
-        <v>585325</v>
+        <v>563713</v>
       </c>
       <c r="P735" t="n">
         <v>2900</v>
       </c>
       <c r="Q735" t="n">
-        <v>942500</v>
+        <v>907700</v>
       </c>
     </row>
     <row r="736">
@@ -37724,22 +37724,22 @@
         <v>0</v>
       </c>
       <c r="L835" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M835" t="n">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="N835" t="n">
-        <v>703.79511760843</v>
+        <v>703.79511689575</v>
       </c>
       <c r="O835" t="n">
-        <v>100642.7018180055</v>
+        <v>92197.16031334325</v>
       </c>
       <c r="P835" t="n">
         <v>900</v>
       </c>
       <c r="Q835" t="n">
-        <v>128700</v>
+        <v>117900</v>
       </c>
     </row>
     <row r="836">
@@ -45002,22 +45002,22 @@
         <v>0</v>
       </c>
       <c r="L987" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M987" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N987" t="n">
         <v>5876.81</v>
       </c>
       <c r="O987" t="n">
-        <v>29384.05</v>
+        <v>17630.43</v>
       </c>
       <c r="P987" t="n">
         <v>22900</v>
       </c>
       <c r="Q987" t="n">
-        <v>114500</v>
+        <v>68700</v>
       </c>
     </row>
     <row r="988">
@@ -49673,22 +49673,22 @@
         <v>0</v>
       </c>
       <c r="L1085" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1085" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N1085" t="n">
-        <v>22951.704792746</v>
+        <v>22951.704785992</v>
       </c>
       <c r="O1085" t="n">
-        <v>436082.391062174</v>
+        <v>413130.6861478559</v>
       </c>
       <c r="P1085" t="n">
         <v>37900</v>
       </c>
       <c r="Q1085" t="n">
-        <v>720100</v>
+        <v>682200</v>
       </c>
     </row>
     <row r="1086">

--- a/bodegas/02.xlsx
+++ b/bodegas/02.xlsx
@@ -3434,10 +3434,10 @@
         <v>21</v>
       </c>
       <c r="N73" t="n">
-        <v>15711.965814978</v>
+        <v>15711.96579646</v>
       </c>
       <c r="O73" t="n">
-        <v>329951.282114538</v>
+        <v>329951.28172566</v>
       </c>
       <c r="P73" t="n">
         <v>28500</v>
@@ -11403,10 +11403,10 @@
         <v>25</v>
       </c>
       <c r="N254" t="n">
-        <v>2582.2555555556</v>
+        <v>2582.2555535714</v>
       </c>
       <c r="O254" t="n">
-        <v>64556.38888889</v>
+        <v>64556.388839285</v>
       </c>
       <c r="P254" t="n">
         <v>4500</v>
@@ -32074,10 +32074,10 @@
         <v>164</v>
       </c>
       <c r="N713" t="n">
-        <v>1655.9307118872</v>
+        <v>1655.9306993948</v>
       </c>
       <c r="O713" t="n">
-        <v>271572.6367495008</v>
+        <v>271572.6347007472</v>
       </c>
       <c r="P713" t="n">
         <v>2500</v>
@@ -32353,10 +32353,10 @@
         <v>18</v>
       </c>
       <c r="N719" t="n">
-        <v>1592.2805889423</v>
+        <v>1592.2806787879</v>
       </c>
       <c r="O719" t="n">
-        <v>28661.0506009614</v>
+        <v>28661.0522181822</v>
       </c>
       <c r="P719" t="n">
         <v>2500</v>
@@ -32489,10 +32489,10 @@
         <v>89</v>
       </c>
       <c r="N722" t="n">
-        <v>2311.9153823529</v>
+        <v>2311.9150892857</v>
       </c>
       <c r="O722" t="n">
-        <v>205760.4690294081</v>
+        <v>205760.4429464273</v>
       </c>
       <c r="P722" t="n">
         <v>3500</v>
@@ -32535,10 +32535,10 @@
         <v>5</v>
       </c>
       <c r="N723" t="n">
-        <v>1906.1813793103</v>
+        <v>1906.1812280702</v>
       </c>
       <c r="O723" t="n">
-        <v>9530.9068965515</v>
+        <v>9530.906140351</v>
       </c>
       <c r="P723" t="n">
         <v>2900</v>
@@ -32673,10 +32673,10 @@
         <v>530</v>
       </c>
       <c r="N726" t="n">
-        <v>1259.2746360505</v>
+        <v>1259.2746413793</v>
       </c>
       <c r="O726" t="n">
-        <v>667415.557106765</v>
+        <v>667415.559931029</v>
       </c>
       <c r="P726" t="n">
         <v>1900</v>
@@ -37336,10 +37336,10 @@
         <v>33</v>
       </c>
       <c r="N826" t="n">
-        <v>3110.8404252438</v>
+        <v>3110.840414859</v>
       </c>
       <c r="O826" t="n">
-        <v>102657.7340330454</v>
+        <v>102657.733690347</v>
       </c>
       <c r="P826" t="n">
         <v>4500</v>
@@ -39052,10 +39052,10 @@
         <v>42</v>
       </c>
       <c r="N863" t="n">
-        <v>1595.5116515014</v>
+        <v>1595.5116012774</v>
       </c>
       <c r="O863" t="n">
-        <v>67011.48936305879</v>
+        <v>67011.48725365079</v>
       </c>
       <c r="P863" t="n">
         <v>2500</v>

--- a/bodegas/02.xlsx
+++ b/bodegas/02.xlsx
@@ -11314,22 +11314,22 @@
         <v>0</v>
       </c>
       <c r="L252" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M252" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="N252" t="n">
-        <v>2582.255546613</v>
+        <v>2582.2555436242</v>
       </c>
       <c r="O252" t="n">
-        <v>64556.38866532501</v>
+        <v>56809.6219597324</v>
       </c>
       <c r="P252" t="n">
         <v>4500</v>
       </c>
       <c r="Q252" t="n">
-        <v>112500</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="253">
@@ -16958,22 +16958,22 @@
         <v>0</v>
       </c>
       <c r="L377" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M377" t="n">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="N377" t="n">
-        <v>1550.1938919769</v>
+        <v>1550.1938936103</v>
       </c>
       <c r="O377" t="n">
-        <v>257332.1860681654</v>
+        <v>251131.4107648686</v>
       </c>
       <c r="P377" t="n">
         <v>2500</v>
       </c>
       <c r="Q377" t="n">
-        <v>415000</v>
+        <v>405000</v>
       </c>
     </row>
     <row r="378">
@@ -21379,10 +21379,10 @@
         <v>5</v>
       </c>
       <c r="N478" t="n">
-        <v>8332.779621212099</v>
+        <v>8332.779620253201</v>
       </c>
       <c r="O478" t="n">
-        <v>41663.8981060605</v>
+        <v>41663.89810126601</v>
       </c>
       <c r="P478" t="n">
         <v>14900</v>
@@ -29976,10 +29976,10 @@
         <v>30</v>
       </c>
       <c r="N667" t="n">
-        <v>17075.989522491</v>
+        <v>17075.989522161</v>
       </c>
       <c r="O667" t="n">
-        <v>512279.68567473</v>
+        <v>512279.68566483</v>
       </c>
       <c r="P667" t="n">
         <v>27500</v>
@@ -32177,22 +32177,22 @@
         <v>0</v>
       </c>
       <c r="L715" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M715" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="N715" t="n">
-        <v>1592.2810401003</v>
+        <v>1592.2811378003</v>
       </c>
       <c r="O715" t="n">
-        <v>14330.5293609027</v>
+        <v>3184.5622756006</v>
       </c>
       <c r="P715" t="n">
         <v>2500</v>
       </c>
       <c r="Q715" t="n">
-        <v>22500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="716">
@@ -36555,22 +36555,22 @@
         <v>0</v>
       </c>
       <c r="L809" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M809" t="n">
-        <v>1355</v>
+        <v>1345</v>
       </c>
       <c r="N809" t="n">
-        <v>517.29096206919</v>
+        <v>517.29097263266</v>
       </c>
       <c r="O809" t="n">
-        <v>700929.2536037524</v>
+        <v>695756.3581909277</v>
       </c>
       <c r="P809" t="n">
         <v>900</v>
       </c>
       <c r="Q809" t="n">
-        <v>1219500</v>
+        <v>1210500</v>
       </c>
     </row>
     <row r="810">
@@ -55168,22 +55168,22 @@
         <v>0</v>
       </c>
       <c r="L1204" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M1204" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="N1204" t="n">
         <v>1584</v>
       </c>
       <c r="O1204" t="n">
-        <v>104544</v>
+        <v>95040</v>
       </c>
       <c r="P1204" t="n">
         <v>2000</v>
       </c>
       <c r="Q1204" t="n">
-        <v>132000</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="1205">

--- a/bodegas/02.xlsx
+++ b/bodegas/02.xlsx
@@ -10494,22 +10494,22 @@
         <v>0</v>
       </c>
       <c r="L233" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M233" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="N233" t="n">
         <v>2600</v>
       </c>
       <c r="O233" t="n">
-        <v>41600</v>
+        <v>18200</v>
       </c>
       <c r="P233" t="n">
         <v>4900</v>
       </c>
       <c r="Q233" t="n">
-        <v>78400</v>
+        <v>34300</v>
       </c>
     </row>
     <row r="234">
@@ -12055,10 +12055,10 @@
         <v>47</v>
       </c>
       <c r="N268" t="n">
-        <v>3230.0670575693</v>
+        <v>3230.0670386266</v>
       </c>
       <c r="O268" t="n">
-        <v>151813.1517057571</v>
+        <v>151813.1508154502</v>
       </c>
       <c r="P268" t="n">
         <v>6200</v>
@@ -12605,22 +12605,22 @@
         <v>0</v>
       </c>
       <c r="L280" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M280" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="N280" t="n">
-        <v>5002</v>
+        <v>5013.3940774487</v>
       </c>
       <c r="O280" t="n">
-        <v>150060</v>
+        <v>130348.2460136662</v>
       </c>
       <c r="P280" t="n">
         <v>8400</v>
       </c>
       <c r="Q280" t="n">
-        <v>252000</v>
+        <v>218400</v>
       </c>
     </row>
     <row r="281">
@@ -13046,10 +13046,10 @@
         <v>26</v>
       </c>
       <c r="N290" t="n">
-        <v>4890.9300493218</v>
+        <v>4890.9300493827</v>
       </c>
       <c r="O290" t="n">
-        <v>127164.1812823668</v>
+        <v>127164.1812839502</v>
       </c>
       <c r="P290" t="n">
         <v>8200</v>
@@ -13852,22 +13852,22 @@
         <v>0</v>
       </c>
       <c r="L308" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M308" t="n">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="N308" t="n">
-        <v>2090.85</v>
+        <v>2092.643951094</v>
       </c>
       <c r="O308" t="n">
-        <v>422351.7</v>
+        <v>397602.35070786</v>
       </c>
       <c r="P308" t="n">
         <v>2900</v>
       </c>
       <c r="Q308" t="n">
-        <v>585800</v>
+        <v>551000</v>
       </c>
     </row>
     <row r="309">
@@ -14027,22 +14027,22 @@
         <v>0</v>
       </c>
       <c r="L312" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M312" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="N312" t="n">
         <v>2769.98</v>
       </c>
       <c r="O312" t="n">
-        <v>66479.52</v>
+        <v>33239.76</v>
       </c>
       <c r="P312" t="n">
         <v>3500</v>
       </c>
       <c r="Q312" t="n">
-        <v>84000</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="313">
@@ -14804,10 +14804,10 @@
         <v>48</v>
       </c>
       <c r="N329" t="n">
-        <v>4372.2107917679</v>
+        <v>4372.2107918811</v>
       </c>
       <c r="O329" t="n">
-        <v>209866.1180048592</v>
+        <v>209866.1180102928</v>
       </c>
       <c r="P329" t="n">
         <v>7500</v>
@@ -14888,22 +14888,22 @@
         <v>0</v>
       </c>
       <c r="L331" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="M331" t="n">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="N331" t="n">
-        <v>1592.5662209302</v>
+        <v>1617.3578206079</v>
       </c>
       <c r="O331" t="n">
-        <v>173589.7180813918</v>
+        <v>142327.4882134952</v>
       </c>
       <c r="P331" t="n">
         <v>3900</v>
       </c>
       <c r="Q331" t="n">
-        <v>425100</v>
+        <v>343200</v>
       </c>
     </row>
     <row r="332">
@@ -15236,22 +15236,22 @@
         <v>0</v>
       </c>
       <c r="L339" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M339" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N339" t="n">
         <v>6242.93</v>
       </c>
       <c r="O339" t="n">
-        <v>181044.97</v>
+        <v>131101.53</v>
       </c>
       <c r="P339" t="n">
         <v>10400</v>
       </c>
       <c r="Q339" t="n">
-        <v>301600</v>
+        <v>218400</v>
       </c>
     </row>
     <row r="340">
@@ -16228,22 +16228,22 @@
         <v>0</v>
       </c>
       <c r="L361" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M361" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="N361" t="n">
         <v>5853</v>
       </c>
       <c r="O361" t="n">
-        <v>134619</v>
+        <v>93648</v>
       </c>
       <c r="P361" t="n">
         <v>9900</v>
       </c>
       <c r="Q361" t="n">
-        <v>227700</v>
+        <v>158400</v>
       </c>
     </row>
     <row r="362">
@@ -16826,10 +16826,10 @@
         <v>203</v>
       </c>
       <c r="N374" t="n">
-        <v>1630.9238760081</v>
+        <v>1630.9238867829</v>
       </c>
       <c r="O374" t="n">
-        <v>331077.5468296443</v>
+        <v>331077.5490169287</v>
       </c>
       <c r="P374" t="n">
         <v>2500</v>
@@ -16964,10 +16964,10 @@
         <v>155</v>
       </c>
       <c r="N377" t="n">
-        <v>1550.1939063158</v>
+        <v>1550.1939133186</v>
       </c>
       <c r="O377" t="n">
-        <v>240280.055478949</v>
+        <v>240280.056564383</v>
       </c>
       <c r="P377" t="n">
         <v>2500</v>
@@ -17056,10 +17056,10 @@
         <v>220</v>
       </c>
       <c r="N379" t="n">
-        <v>2403.5134379057</v>
+        <v>2403.513461205</v>
       </c>
       <c r="O379" t="n">
-        <v>528772.9563392539</v>
+        <v>528772.9614651001</v>
       </c>
       <c r="P379" t="n">
         <v>3500</v>
@@ -19526,22 +19526,22 @@
         <v>0</v>
       </c>
       <c r="L435" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M435" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="N435" t="n">
-        <v>2517.22</v>
+        <v>2541.6788178138</v>
       </c>
       <c r="O435" t="n">
-        <v>75516.59999999999</v>
+        <v>45750.2187206484</v>
       </c>
       <c r="P435" t="n">
         <v>4200</v>
       </c>
       <c r="Q435" t="n">
-        <v>126000</v>
+        <v>75600</v>
       </c>
     </row>
     <row r="436">
@@ -24071,22 +24071,22 @@
         <v>0</v>
       </c>
       <c r="L539" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M539" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N539" t="n">
-        <v>5218.1705692109</v>
+        <v>5218.1705706874</v>
       </c>
       <c r="O539" t="n">
-        <v>83490.7291073744</v>
+        <v>73054.3879896236</v>
       </c>
       <c r="P539" t="n">
         <v>8500</v>
       </c>
       <c r="Q539" t="n">
-        <v>136000</v>
+        <v>119000</v>
       </c>
     </row>
     <row r="540">
@@ -24117,22 +24117,22 @@
         <v>0</v>
       </c>
       <c r="L540" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M540" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="N540" t="n">
-        <v>1595.0093202147</v>
+        <v>1595.0093078324</v>
       </c>
       <c r="O540" t="n">
-        <v>20735.1211627911</v>
+        <v>4785.0279234972</v>
       </c>
       <c r="P540" t="n">
         <v>2600</v>
       </c>
       <c r="Q540" t="n">
-        <v>33800</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="541">
@@ -31387,22 +31387,22 @@
         <v>0</v>
       </c>
       <c r="L698" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M698" t="n">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="N698" t="n">
-        <v>1516.0387891009</v>
+        <v>1517.8304441599</v>
       </c>
       <c r="O698" t="n">
-        <v>104606.6764479621</v>
+        <v>86516.3353171143</v>
       </c>
       <c r="P698" t="n">
         <v>2300</v>
       </c>
       <c r="Q698" t="n">
-        <v>158700</v>
+        <v>131100</v>
       </c>
     </row>
     <row r="699">
@@ -31669,10 +31669,10 @@
         <v>182</v>
       </c>
       <c r="N704" t="n">
-        <v>1803.0158874609</v>
+        <v>1803.0158936022</v>
       </c>
       <c r="O704" t="n">
-        <v>328148.8915178838</v>
+        <v>328148.8926356004</v>
       </c>
       <c r="P704" t="n">
         <v>2500</v>
@@ -32224,10 +32224,10 @@
         <v>1</v>
       </c>
       <c r="N716" t="n">
-        <v>1592.2815314136</v>
+        <v>1592.2816534392</v>
       </c>
       <c r="O716" t="n">
-        <v>1592.2815314136</v>
+        <v>1592.2816534392</v>
       </c>
       <c r="P716" t="n">
         <v>2500</v>
@@ -36596,22 +36596,22 @@
         <v>0</v>
       </c>
       <c r="L810" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M810" t="n">
-        <v>1260</v>
+        <v>1236</v>
       </c>
       <c r="N810" t="n">
-        <v>517.29128286432</v>
+        <v>518.11303680169</v>
       </c>
       <c r="O810" t="n">
-        <v>651787.0164090432</v>
+        <v>640387.7134868888</v>
       </c>
       <c r="P810" t="n">
         <v>900</v>
       </c>
       <c r="Q810" t="n">
-        <v>1134000</v>
+        <v>1112400</v>
       </c>
     </row>
     <row r="811">
@@ -37432,22 +37432,22 @@
         <v>0</v>
       </c>
       <c r="L828" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M828" t="n">
-        <v>279</v>
+        <v>231</v>
       </c>
       <c r="N828" t="n">
-        <v>703.79502188713</v>
+        <v>703.79501848956</v>
       </c>
       <c r="O828" t="n">
-        <v>196358.8111065093</v>
+        <v>162576.6492710884</v>
       </c>
       <c r="P828" t="n">
         <v>900</v>
       </c>
       <c r="Q828" t="n">
-        <v>251100</v>
+        <v>207900</v>
       </c>
     </row>
     <row r="829">
@@ -48867,22 +48867,22 @@
         <v>0</v>
       </c>
       <c r="L1067" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M1067" t="n">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="N1067" t="n">
         <v>1176.57</v>
       </c>
       <c r="O1067" t="n">
-        <v>156483.81</v>
+        <v>142364.97</v>
       </c>
       <c r="P1067" t="n">
         <v>1900</v>
       </c>
       <c r="Q1067" t="n">
-        <v>252700</v>
+        <v>229900</v>
       </c>
     </row>
     <row r="1068">
@@ -55068,22 +55068,22 @@
         <v>0</v>
       </c>
       <c r="L1202" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M1202" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="N1202" t="n">
         <v>5280</v>
       </c>
       <c r="O1202" t="n">
-        <v>79200</v>
+        <v>15840</v>
       </c>
       <c r="P1202" t="n">
         <v>6900</v>
       </c>
       <c r="Q1202" t="n">
-        <v>103500</v>
+        <v>20700</v>
       </c>
     </row>
     <row r="1203">
@@ -55114,22 +55114,22 @@
         <v>0</v>
       </c>
       <c r="L1203" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M1203" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="N1203" t="n">
         <v>5280</v>
       </c>
       <c r="O1203" t="n">
-        <v>89760</v>
+        <v>26400</v>
       </c>
       <c r="P1203" t="n">
         <v>6900</v>
       </c>
       <c r="Q1203" t="n">
-        <v>117300</v>
+        <v>34500</v>
       </c>
     </row>
     <row r="1204">
@@ -55344,22 +55344,22 @@
         <v>0</v>
       </c>
       <c r="L1208" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M1208" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="N1208" t="n">
-        <v>3520</v>
+        <v>3571.512195122</v>
       </c>
       <c r="O1208" t="n">
-        <v>197120</v>
+        <v>178575.6097561</v>
       </c>
       <c r="P1208" t="n">
         <v>4500</v>
       </c>
       <c r="Q1208" t="n">
-        <v>252000</v>
+        <v>225000</v>
       </c>
     </row>
     <row r="1209">

--- a/bodegas/02.xlsx
+++ b/bodegas/02.xlsx
@@ -11366,10 +11366,10 @@
         <v>37</v>
       </c>
       <c r="N253" t="n">
-        <v>2582.2555145238</v>
+        <v>2582.2555084555</v>
       </c>
       <c r="O253" t="n">
-        <v>95543.45403738059</v>
+        <v>95543.45381285351</v>
       </c>
       <c r="P253" t="n">
         <v>4500</v>
@@ -11924,10 +11924,10 @@
         <v>11</v>
       </c>
       <c r="N265" t="n">
-        <v>3841.62486</v>
+        <v>3841.6248746239</v>
       </c>
       <c r="O265" t="n">
-        <v>42257.87346</v>
+        <v>42257.8736208629</v>
       </c>
       <c r="P265" t="n">
         <v>6900</v>
@@ -16916,10 +16916,10 @@
         <v>203</v>
       </c>
       <c r="N376" t="n">
-        <v>1630.9239095069</v>
+        <v>1630.9239154786</v>
       </c>
       <c r="O376" t="n">
-        <v>331077.5536299007</v>
+        <v>331077.5548421558</v>
       </c>
       <c r="P376" t="n">
         <v>2500</v>
@@ -17146,10 +17146,10 @@
         <v>175</v>
       </c>
       <c r="N381" t="n">
-        <v>2403.5136926808</v>
+        <v>2403.513738111</v>
       </c>
       <c r="O381" t="n">
-        <v>420614.89621914</v>
+        <v>420614.904169425</v>
       </c>
       <c r="P381" t="n">
         <v>3500</v>
@@ -32360,10 +32360,10 @@
         <v>1</v>
       </c>
       <c r="N719" t="n">
-        <v>1592.2817466667</v>
+        <v>1592.281793842</v>
       </c>
       <c r="O719" t="n">
-        <v>1592.2817466667</v>
+        <v>1592.281793842</v>
       </c>
       <c r="P719" t="n">
         <v>2500</v>
@@ -32588,10 +32588,10 @@
         <v>1</v>
       </c>
       <c r="N724" t="n">
-        <v>3033.7037</v>
+        <v>3033.7022680412</v>
       </c>
       <c r="O724" t="n">
-        <v>3033.7037</v>
+        <v>3033.7022680412</v>
       </c>
       <c r="P724" t="n">
         <v>4500</v>
@@ -37574,10 +37574,10 @@
         <v>167</v>
       </c>
       <c r="N831" t="n">
-        <v>703.79500857932</v>
+        <v>703.79500789654</v>
       </c>
       <c r="O831" t="n">
-        <v>117533.7664327464</v>
+        <v>117533.7663187222</v>
       </c>
       <c r="P831" t="n">
         <v>900</v>

--- a/bodegas/02.xlsx
+++ b/bodegas/02.xlsx
@@ -771,10 +771,10 @@
         <v>6</v>
       </c>
       <c r="N9" t="n">
-        <v>27035.809018568</v>
+        <v>27000</v>
       </c>
       <c r="O9" t="n">
-        <v>162214.854111408</v>
+        <v>162000</v>
       </c>
       <c r="P9" t="n">
         <v>20000</v>
@@ -2936,10 +2936,10 @@
         <v>2</v>
       </c>
       <c r="N62" t="n">
-        <v>30074.074074074</v>
+        <v>29000</v>
       </c>
       <c r="O62" t="n">
-        <v>60148.148148148</v>
+        <v>58000</v>
       </c>
       <c r="P62" t="n">
         <v>34800</v>
@@ -10715,10 +10715,10 @@
         <v>13</v>
       </c>
       <c r="N238" t="n">
-        <v>17234.854035088</v>
+        <v>17207.41</v>
       </c>
       <c r="O238" t="n">
-        <v>224053.102456144</v>
+        <v>223696.33</v>
       </c>
       <c r="P238" t="n">
         <v>20000</v>
@@ -12565,10 +12565,10 @@
         <v>2</v>
       </c>
       <c r="N279" t="n">
-        <v>8807.6968085106</v>
+        <v>8796</v>
       </c>
       <c r="O279" t="n">
-        <v>17615.3936170212</v>
+        <v>17592</v>
       </c>
       <c r="P279" t="n">
         <v>14900</v>
@@ -14082,10 +14082,10 @@
         <v>7</v>
       </c>
       <c r="N313" t="n">
-        <v>2667.0463248919</v>
+        <v>2665.4</v>
       </c>
       <c r="O313" t="n">
-        <v>18669.3242742433</v>
+        <v>18657.8</v>
       </c>
       <c r="P313" t="n">
         <v>20900</v>
@@ -14763,10 +14763,10 @@
         <v>49</v>
       </c>
       <c r="N328" t="n">
-        <v>4372.5234503719</v>
+        <v>4372.2107923341</v>
       </c>
       <c r="O328" t="n">
-        <v>214253.6490682231</v>
+        <v>214238.3288243709</v>
       </c>
       <c r="P328" t="n">
         <v>7500</v>
@@ -15471,10 +15471,10 @@
         <v>29</v>
       </c>
       <c r="N344" t="n">
-        <v>17473.953844316</v>
+        <v>17472.91</v>
       </c>
       <c r="O344" t="n">
-        <v>506744.6614851641</v>
+        <v>506714.39</v>
       </c>
       <c r="P344" t="n">
         <v>2900</v>
@@ -15559,10 +15559,10 @@
         <v>43</v>
       </c>
       <c r="N346" t="n">
-        <v>1530.7162764218</v>
+        <v>1530.63</v>
       </c>
       <c r="O346" t="n">
-        <v>65820.79988613741</v>
+        <v>65817.09000000001</v>
       </c>
       <c r="P346" t="n">
         <v>2900</v>
@@ -22168,10 +22168,10 @@
         <v>9</v>
       </c>
       <c r="N496" t="n">
-        <v>7982.1180305344</v>
+        <v>7969.9501679389</v>
       </c>
       <c r="O496" t="n">
-        <v>71839.06227480959</v>
+        <v>71729.5515114501</v>
       </c>
       <c r="P496" t="n">
         <v>12900</v>
@@ -24453,10 +24453,10 @@
         <v>9</v>
       </c>
       <c r="N547" t="n">
-        <v>14447.670588235</v>
+        <v>14380</v>
       </c>
       <c r="O547" t="n">
-        <v>130029.035294115</v>
+        <v>129420</v>
       </c>
       <c r="P547" t="n">
         <v>23000</v>
@@ -27909,10 +27909,10 @@
         <v>48</v>
       </c>
       <c r="N622" t="n">
-        <v>50584.365236051</v>
+        <v>50153.86</v>
       </c>
       <c r="O622" t="n">
-        <v>2428049.531330448</v>
+        <v>2407385.28</v>
       </c>
       <c r="P622" t="n">
         <v>11500</v>
@@ -30294,10 +30294,10 @@
         <v>64</v>
       </c>
       <c r="N674" t="n">
-        <v>59958.524453694</v>
+        <v>59834</v>
       </c>
       <c r="O674" t="n">
-        <v>3837345.565036416</v>
+        <v>3829376</v>
       </c>
       <c r="P674" t="n">
         <v>7900</v>
@@ -31076,10 +31076,10 @@
         <v>30</v>
       </c>
       <c r="N691" t="n">
-        <v>3821.6520477816</v>
+        <v>3821</v>
       </c>
       <c r="O691" t="n">
-        <v>114649.561433448</v>
+        <v>114630</v>
       </c>
       <c r="P691" t="n">
         <v>5900</v>
@@ -31306,10 +31306,10 @@
         <v>50</v>
       </c>
       <c r="N696" t="n">
-        <v>5486.9301397206</v>
+        <v>5476</v>
       </c>
       <c r="O696" t="n">
-        <v>274346.50698603</v>
+        <v>273800</v>
       </c>
       <c r="P696" t="n">
         <v>8900</v>
@@ -32322,10 +32322,10 @@
         <v>5</v>
       </c>
       <c r="N718" t="n">
-        <v>5372.836713615</v>
+        <v>5347.73</v>
       </c>
       <c r="O718" t="n">
-        <v>26864.183568075</v>
+        <v>26738.65</v>
       </c>
       <c r="P718" t="n">
         <v>9500</v>
@@ -32916,10 +32916,10 @@
         <v>3</v>
       </c>
       <c r="N731" t="n">
-        <v>18654.637168142</v>
+        <v>18491</v>
       </c>
       <c r="O731" t="n">
-        <v>55963.911504426</v>
+        <v>55473</v>
       </c>
       <c r="P731" t="n">
         <v>13500</v>
@@ -45686,10 +45686,10 @@
         <v>11</v>
       </c>
       <c r="N1000" t="n">
-        <v>5235.0773519164</v>
+        <v>5216.9</v>
       </c>
       <c r="O1000" t="n">
-        <v>57585.8508710804</v>
+        <v>57385.89999999999</v>
       </c>
       <c r="P1000" t="n">
         <v>20500</v>
@@ -46412,10 +46412,10 @@
         <v>261</v>
       </c>
       <c r="N1015" t="n">
-        <v>7049.9805782093</v>
+        <v>7046.9398274002</v>
       </c>
       <c r="O1015" t="n">
-        <v>1840044.930912627</v>
+        <v>1839251.294951452</v>
       </c>
       <c r="P1015" t="n">
         <v>9900</v>

--- a/bodegas/02.xlsx
+++ b/bodegas/02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-06</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-07</t>
         </is>
       </c>
     </row>

--- a/bodegas/02.xlsx
+++ b/bodegas/02.xlsx
@@ -1570,10 +1570,10 @@
         <v>10</v>
       </c>
       <c r="N29" t="n">
-        <v>12357.960422535</v>
+        <v>12357.960425532</v>
       </c>
       <c r="O29" t="n">
-        <v>123579.60422535</v>
+        <v>123579.60425532</v>
       </c>
       <c r="P29" t="n">
         <v>15900</v>
@@ -1732,10 +1732,10 @@
         <v>5</v>
       </c>
       <c r="N33" t="n">
-        <v>11491.097222222</v>
+        <v>11491.09755814</v>
       </c>
       <c r="O33" t="n">
-        <v>57455.48611111</v>
+        <v>57455.4877907</v>
       </c>
       <c r="P33" t="n">
         <v>23000</v>
@@ -3434,10 +3434,10 @@
         <v>21</v>
       </c>
       <c r="N73" t="n">
-        <v>15711.96562212</v>
+        <v>15711.965560748</v>
       </c>
       <c r="O73" t="n">
-        <v>329951.27806452</v>
+        <v>329951.276775708</v>
       </c>
       <c r="P73" t="n">
         <v>28500</v>
@@ -3769,10 +3769,10 @@
         <v>8</v>
       </c>
       <c r="N81" t="n">
-        <v>22267.5525</v>
+        <v>22267.552777778</v>
       </c>
       <c r="O81" t="n">
-        <v>178140.42</v>
+        <v>178140.422222224</v>
       </c>
       <c r="P81" t="n">
         <v>46300</v>
@@ -4396,10 +4396,10 @@
         <v>3</v>
       </c>
       <c r="N96" t="n">
-        <v>61666.874148352</v>
+        <v>61666.87415978</v>
       </c>
       <c r="O96" t="n">
-        <v>185000.622445056</v>
+        <v>185000.62247934</v>
       </c>
       <c r="P96" t="n">
         <v>98900</v>
@@ -8646,22 +8646,22 @@
         <v>0</v>
       </c>
       <c r="L192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M192" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N192" t="n">
         <v>1368.1</v>
       </c>
       <c r="O192" t="n">
-        <v>272251.9</v>
+        <v>270883.8</v>
       </c>
       <c r="P192" t="n">
         <v>1900</v>
       </c>
       <c r="Q192" t="n">
-        <v>378100</v>
+        <v>376200</v>
       </c>
     </row>
     <row r="193">
@@ -11366,10 +11366,10 @@
         <v>32</v>
       </c>
       <c r="N253" t="n">
-        <v>2582.2554768392</v>
+        <v>2582.2554727273</v>
       </c>
       <c r="O253" t="n">
-        <v>82632.1752588544</v>
+        <v>82632.1751272736</v>
       </c>
       <c r="P253" t="n">
         <v>4500</v>
@@ -12228,22 +12228,22 @@
         <v>0</v>
       </c>
       <c r="L272" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M272" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="N272" t="n">
         <v>1337.34</v>
       </c>
       <c r="O272" t="n">
-        <v>270142.68</v>
+        <v>267468</v>
       </c>
       <c r="P272" t="n">
         <v>2500</v>
       </c>
       <c r="Q272" t="n">
-        <v>505000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="273">
@@ -13458,10 +13458,10 @@
         <v>10</v>
       </c>
       <c r="N299" t="n">
-        <v>3594.253608522</v>
+        <v>3594.2536</v>
       </c>
       <c r="O299" t="n">
-        <v>35942.53608522</v>
+        <v>35942.536</v>
       </c>
       <c r="P299" t="n">
         <v>6500</v>
@@ -13773,10 +13773,10 @@
         <v>8</v>
       </c>
       <c r="N306" t="n">
-        <v>14822.378837068</v>
+        <v>14822.378836364</v>
       </c>
       <c r="O306" t="n">
-        <v>118579.030696544</v>
+        <v>118579.030690912</v>
       </c>
       <c r="P306" t="n">
         <v>24900</v>
@@ -13811,22 +13811,22 @@
         <v>0</v>
       </c>
       <c r="L307" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M307" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="N307" t="n">
         <v>2090.85</v>
       </c>
       <c r="O307" t="n">
-        <v>263447.1</v>
+        <v>255083.7</v>
       </c>
       <c r="P307" t="n">
         <v>2900</v>
       </c>
       <c r="Q307" t="n">
-        <v>365400</v>
+        <v>353800</v>
       </c>
     </row>
     <row r="308">
@@ -14847,22 +14847,22 @@
         <v>0</v>
       </c>
       <c r="L330" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M330" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="N330" t="n">
-        <v>1592.5660665658</v>
+        <v>1592.5660516325</v>
       </c>
       <c r="O330" t="n">
-        <v>136960.6817246588</v>
+        <v>128997.8501822325</v>
       </c>
       <c r="P330" t="n">
         <v>3900</v>
       </c>
       <c r="Q330" t="n">
-        <v>335400</v>
+        <v>315900</v>
       </c>
     </row>
     <row r="331">
@@ -16921,10 +16921,10 @@
         <v>29</v>
       </c>
       <c r="N376" t="n">
-        <v>1690.5922846782</v>
+        <v>1690.591979835</v>
       </c>
       <c r="O376" t="n">
-        <v>49027.1762556678</v>
+        <v>49027.167415215</v>
       </c>
       <c r="P376" t="n">
         <v>2900</v>
@@ -16967,10 +16967,10 @@
         <v>139</v>
       </c>
       <c r="N377" t="n">
-        <v>1550.1940319426</v>
+        <v>1550.1940372063</v>
       </c>
       <c r="O377" t="n">
-        <v>215476.9704400214</v>
+        <v>215476.9711716757</v>
       </c>
       <c r="P377" t="n">
         <v>2500</v>
@@ -17053,22 +17053,22 @@
         <v>0</v>
       </c>
       <c r="L379" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M379" t="n">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="N379" t="n">
-        <v>2403.5140171519</v>
+        <v>2403.5141965714</v>
       </c>
       <c r="O379" t="n">
-        <v>386965.7567614559</v>
+        <v>338895.5017165674</v>
       </c>
       <c r="P379" t="n">
         <v>3500</v>
       </c>
       <c r="Q379" t="n">
-        <v>563500</v>
+        <v>493500</v>
       </c>
     </row>
     <row r="380">
@@ -19535,10 +19535,10 @@
         <v>89</v>
       </c>
       <c r="N435" t="n">
-        <v>2029.8739872408</v>
+        <v>2029.8739957379</v>
       </c>
       <c r="O435" t="n">
-        <v>180658.7848644312</v>
+        <v>180658.7856206731</v>
       </c>
       <c r="P435" t="n">
         <v>3600</v>
@@ -20350,10 +20350,10 @@
         <v>1</v>
       </c>
       <c r="N454" t="n">
-        <v>4285.1958525346</v>
+        <v>4285.1958592849</v>
       </c>
       <c r="O454" t="n">
-        <v>4285.1958525346</v>
+        <v>4285.1958592849</v>
       </c>
       <c r="P454" t="n">
         <v>6900</v>
@@ -25086,22 +25086,22 @@
         <v>0</v>
       </c>
       <c r="L561" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M561" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N561" t="n">
-        <v>1778.4726973583</v>
+        <v>1778.472697775</v>
       </c>
       <c r="O561" t="n">
-        <v>131606.9796045142</v>
+        <v>129828.506937575</v>
       </c>
       <c r="P561" t="n">
         <v>4900</v>
       </c>
       <c r="Q561" t="n">
-        <v>362600</v>
+        <v>357700</v>
       </c>
     </row>
     <row r="562">
@@ -28415,10 +28415,10 @@
         <v>64</v>
       </c>
       <c r="N633" t="n">
-        <v>4907.8223782772</v>
+        <v>4907.8223917137</v>
       </c>
       <c r="O633" t="n">
-        <v>314100.6322097408</v>
+        <v>314100.6330696768</v>
       </c>
       <c r="P633" t="n">
         <v>8200</v>
@@ -30025,10 +30025,10 @@
         <v>30</v>
       </c>
       <c r="N668" t="n">
-        <v>17075.98952183</v>
+        <v>17075.989521166</v>
       </c>
       <c r="O668" t="n">
-        <v>512279.6856549</v>
+        <v>512279.68563498</v>
       </c>
       <c r="P668" t="n">
         <v>27500</v>
@@ -31861,10 +31861,10 @@
         <v>246</v>
       </c>
       <c r="N708" t="n">
-        <v>2056.082714437</v>
+        <v>2056.08270929</v>
       </c>
       <c r="O708" t="n">
-        <v>505796.347751502</v>
+        <v>505796.34648534</v>
       </c>
       <c r="P708" t="n">
         <v>2900</v>
@@ -31907,10 +31907,10 @@
         <v>168</v>
       </c>
       <c r="N709" t="n">
-        <v>3224.5689724311</v>
+        <v>3224.568981435</v>
       </c>
       <c r="O709" t="n">
-        <v>541727.5873684249</v>
+        <v>541727.5888810799</v>
       </c>
       <c r="P709" t="n">
         <v>4500</v>
@@ -32232,10 +32232,10 @@
         <v>1</v>
       </c>
       <c r="N716" t="n">
-        <v>1592.2820519836</v>
+        <v>1592.2820684932</v>
       </c>
       <c r="O716" t="n">
-        <v>1592.2820519836</v>
+        <v>1592.2820684932</v>
       </c>
       <c r="P716" t="n">
         <v>2500</v>
@@ -32362,22 +32362,22 @@
         <v>0</v>
       </c>
       <c r="L719" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M719" t="n">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="N719" t="n">
-        <v>2311.912006689</v>
+        <v>2311.9102135231</v>
       </c>
       <c r="O719" t="n">
-        <v>175705.312508364</v>
+        <v>134090.7923843398</v>
       </c>
       <c r="P719" t="n">
         <v>3500</v>
       </c>
       <c r="Q719" t="n">
-        <v>266000</v>
+        <v>203000</v>
       </c>
     </row>
     <row r="720">
@@ -33999,22 +33999,22 @@
         <v>0</v>
       </c>
       <c r="L754" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M754" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N754" t="n">
         <v>1306.5</v>
       </c>
       <c r="O754" t="n">
-        <v>3919.5</v>
+        <v>2613</v>
       </c>
       <c r="P754" t="n">
         <v>2000</v>
       </c>
       <c r="Q754" t="n">
-        <v>6000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="755">
@@ -36653,22 +36653,22 @@
         <v>0</v>
       </c>
       <c r="L811" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="M811" t="n">
-        <v>935</v>
+        <v>914</v>
       </c>
       <c r="N811" t="n">
-        <v>517.2923857868</v>
+        <v>517.29240467717</v>
       </c>
       <c r="O811" t="n">
-        <v>483668.380710658</v>
+        <v>472805.2578749334</v>
       </c>
       <c r="P811" t="n">
         <v>900</v>
       </c>
       <c r="Q811" t="n">
-        <v>841500</v>
+        <v>822600</v>
       </c>
     </row>
     <row r="812">
@@ -37264,10 +37264,10 @@
         <v>19</v>
       </c>
       <c r="N824" t="n">
-        <v>3110.8400113026</v>
+        <v>3110.8399744753</v>
       </c>
       <c r="O824" t="n">
-        <v>59105.9602147494</v>
+        <v>59105.9595150307</v>
       </c>
       <c r="P824" t="n">
         <v>4500</v>
@@ -47665,22 +47665,22 @@
         <v>0</v>
       </c>
       <c r="L1041" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1041" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="N1041" t="n">
         <v>1338.14</v>
       </c>
       <c r="O1041" t="n">
-        <v>128461.44</v>
+        <v>124447.02</v>
       </c>
       <c r="P1041" t="n">
         <v>2500</v>
       </c>
       <c r="Q1041" t="n">
-        <v>240000</v>
+        <v>232500</v>
       </c>
     </row>
     <row r="1042">
@@ -47714,22 +47714,22 @@
         <v>0</v>
       </c>
       <c r="L1042" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1042" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="N1042" t="n">
-        <v>366.39975903614</v>
+        <v>366.39975609756</v>
       </c>
       <c r="O1042" t="n">
-        <v>26380.78265060208</v>
+        <v>26014.38268292676</v>
       </c>
       <c r="P1042" t="n">
         <v>2900</v>
       </c>
       <c r="Q1042" t="n">
-        <v>208800</v>
+        <v>205900</v>
       </c>
     </row>
     <row r="1043">
@@ -48881,22 +48881,22 @@
         <v>0</v>
       </c>
       <c r="L1067" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="M1067" t="n">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="N1067" t="n">
         <v>1176.57</v>
       </c>
       <c r="O1067" t="n">
-        <v>114127.29</v>
+        <v>83536.47</v>
       </c>
       <c r="P1067" t="n">
         <v>1900</v>
       </c>
       <c r="Q1067" t="n">
-        <v>184300</v>
+        <v>134900</v>
       </c>
     </row>
     <row r="1068">
@@ -55036,22 +55036,22 @@
         <v>0</v>
       </c>
       <c r="L1201" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1201" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N1201" t="n">
         <v>7480</v>
       </c>
       <c r="O1201" t="n">
-        <v>463760</v>
+        <v>456280</v>
       </c>
       <c r="P1201" t="n">
         <v>9500</v>
       </c>
       <c r="Q1201" t="n">
-        <v>589000</v>
+        <v>579500</v>
       </c>
     </row>
     <row r="1202">
@@ -55174,22 +55174,22 @@
         <v>0</v>
       </c>
       <c r="L1204" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="M1204" t="n">
-        <v>130</v>
+        <v>46</v>
       </c>
       <c r="N1204" t="n">
         <v>1584</v>
       </c>
       <c r="O1204" t="n">
-        <v>205920</v>
+        <v>72864</v>
       </c>
       <c r="P1204" t="n">
         <v>2000</v>
       </c>
       <c r="Q1204" t="n">
-        <v>260000</v>
+        <v>92000</v>
       </c>
     </row>
     <row r="1205">
@@ -55358,22 +55358,22 @@
         <v>0</v>
       </c>
       <c r="L1208" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M1208" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="N1208" t="n">
         <v>3520</v>
       </c>
       <c r="O1208" t="n">
-        <v>91520</v>
+        <v>35200</v>
       </c>
       <c r="P1208" t="n">
         <v>4500</v>
       </c>
       <c r="Q1208" t="n">
-        <v>117000</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="1209">

--- a/bodegas/02.xlsx
+++ b/bodegas/02.xlsx
@@ -11366,10 +11366,10 @@
         <v>32</v>
       </c>
       <c r="N253" t="n">
-        <v>2582.2554675768</v>
+        <v>2582.2554613807</v>
       </c>
       <c r="O253" t="n">
-        <v>82632.1749624576</v>
+        <v>82632.1747641824</v>
       </c>
       <c r="P253" t="n">
         <v>4500</v>
@@ -12467,10 +12467,10 @@
         <v>4</v>
       </c>
       <c r="N277" t="n">
-        <v>7507.39</v>
+        <v>7518.1997768179</v>
       </c>
       <c r="O277" t="n">
-        <v>30029.56</v>
+        <v>30072.7991072716</v>
       </c>
       <c r="P277" t="n">
         <v>13500</v>
@@ -12565,10 +12565,10 @@
         <v>2</v>
       </c>
       <c r="N279" t="n">
-        <v>8796</v>
+        <v>8831.230974632799</v>
       </c>
       <c r="O279" t="n">
-        <v>17592</v>
+        <v>17662.4619492656</v>
       </c>
       <c r="P279" t="n">
         <v>14900</v>
@@ -14488,10 +14488,10 @@
         <v>11</v>
       </c>
       <c r="N322" t="n">
-        <v>15851.61</v>
+        <v>15976.425826772</v>
       </c>
       <c r="O322" t="n">
-        <v>174367.71</v>
+        <v>175740.684094492</v>
       </c>
       <c r="P322" t="n">
         <v>23900</v>
@@ -16967,10 +16967,10 @@
         <v>125</v>
       </c>
       <c r="N377" t="n">
-        <v>1550.1940686328</v>
+        <v>1550.1940704179</v>
       </c>
       <c r="O377" t="n">
-        <v>193774.2585791</v>
+        <v>193774.2588022375</v>
       </c>
       <c r="P377" t="n">
         <v>2500</v>
@@ -17059,10 +17059,10 @@
         <v>137</v>
       </c>
       <c r="N379" t="n">
-        <v>2403.5142945915</v>
+        <v>2403.514304468</v>
       </c>
       <c r="O379" t="n">
-        <v>329281.4583590355</v>
+        <v>329281.459712116</v>
       </c>
       <c r="P379" t="n">
         <v>3500</v>
@@ -25086,22 +25086,22 @@
         <v>0</v>
       </c>
       <c r="L561" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M561" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N561" t="n">
-        <v>1778.4727006961</v>
+        <v>1778.4727011139</v>
       </c>
       <c r="O561" t="n">
-        <v>126271.5617494231</v>
+        <v>124493.089077973</v>
       </c>
       <c r="P561" t="n">
         <v>4900</v>
       </c>
       <c r="Q561" t="n">
-        <v>347900</v>
+        <v>343000</v>
       </c>
     </row>
     <row r="562">
@@ -29381,10 +29381,10 @@
         <v>5</v>
       </c>
       <c r="N654" t="n">
-        <v>27186</v>
+        <v>27309.572727273</v>
       </c>
       <c r="O654" t="n">
-        <v>135930</v>
+        <v>136547.863636365</v>
       </c>
       <c r="P654" t="n">
         <v>43900</v>
@@ -30984,10 +30984,10 @@
         <v>11</v>
       </c>
       <c r="N689" t="n">
-        <v>10713.21</v>
+        <v>10792.371650246</v>
       </c>
       <c r="O689" t="n">
-        <v>117845.31</v>
+        <v>118716.088152706</v>
       </c>
       <c r="P689" t="n">
         <v>20900</v>
@@ -31677,10 +31677,10 @@
         <v>182</v>
       </c>
       <c r="N704" t="n">
-        <v>1803.0159286464</v>
+        <v>1803.0159327966</v>
       </c>
       <c r="O704" t="n">
-        <v>328148.8990136448</v>
+        <v>328148.8997689812</v>
       </c>
       <c r="P704" t="n">
         <v>2500</v>
@@ -32414,10 +32414,10 @@
         <v>2</v>
       </c>
       <c r="N720" t="n">
-        <v>1906.180625</v>
+        <v>1906.1803846154</v>
       </c>
       <c r="O720" t="n">
-        <v>3812.36125</v>
+        <v>3812.3607692308</v>
       </c>
       <c r="P720" t="n">
         <v>2900</v>
@@ -37495,10 +37495,10 @@
         <v>135</v>
       </c>
       <c r="N829" t="n">
-        <v>703.79497049501</v>
+        <v>703.79496992783</v>
       </c>
       <c r="O829" t="n">
-        <v>95012.32101682636</v>
+        <v>95012.32094025705</v>
       </c>
       <c r="P829" t="n">
         <v>900</v>
@@ -55042,10 +55042,10 @@
         <v>61</v>
       </c>
       <c r="N1201" t="n">
-        <v>7480</v>
+        <v>7524.8351648352</v>
       </c>
       <c r="O1201" t="n">
-        <v>456280</v>
+        <v>459014.9450549472</v>
       </c>
       <c r="P1201" t="n">
         <v>9500</v>

--- a/bodegas/02.xlsx
+++ b/bodegas/02.xlsx
@@ -1531,10 +1531,10 @@
         <v>13</v>
       </c>
       <c r="N28" t="n">
-        <v>6272.8550526316</v>
+        <v>6272.8550704225</v>
       </c>
       <c r="O28" t="n">
-        <v>81547.1156842108</v>
+        <v>81547.1159154925</v>
       </c>
       <c r="P28" t="n">
         <v>7900</v>
@@ -2715,10 +2715,10 @@
         <v>4</v>
       </c>
       <c r="N57" t="n">
-        <v>2053.9877300613</v>
+        <v>1800</v>
       </c>
       <c r="O57" t="n">
-        <v>8215.950920245201</v>
+        <v>7200</v>
       </c>
       <c r="P57" t="n">
         <v>2200</v>
@@ -3769,10 +3769,10 @@
         <v>8</v>
       </c>
       <c r="N81" t="n">
-        <v>23504.638888889</v>
+        <v>22267.552777778</v>
       </c>
       <c r="O81" t="n">
-        <v>188037.111111112</v>
+        <v>178140.422222224</v>
       </c>
       <c r="P81" t="n">
         <v>46300</v>
@@ -10674,10 +10674,10 @@
         <v>9</v>
       </c>
       <c r="N237" t="n">
-        <v>13642.54185766</v>
+        <v>13593.35</v>
       </c>
       <c r="O237" t="n">
-        <v>122782.87671894</v>
+        <v>122340.15</v>
       </c>
       <c r="P237" t="n">
         <v>25500</v>
@@ -11012,10 +11012,10 @@
         <v>42</v>
       </c>
       <c r="N245" t="n">
-        <v>2808.3040151157</v>
+        <v>2804.33</v>
       </c>
       <c r="O245" t="n">
-        <v>117948.7686348594</v>
+        <v>117781.86</v>
       </c>
       <c r="P245" t="n">
         <v>4900</v>
@@ -11366,10 +11366,10 @@
         <v>20</v>
       </c>
       <c r="N253" t="n">
-        <v>2584.0407928094</v>
+        <v>2582.2554090804</v>
       </c>
       <c r="O253" t="n">
-        <v>51680.815856188</v>
+        <v>51645.108181608</v>
       </c>
       <c r="P253" t="n">
         <v>4500</v>
@@ -11452,22 +11452,22 @@
         <v>0</v>
       </c>
       <c r="L255" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M255" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="N255" t="n">
-        <v>5216.8960111863</v>
+        <v>5216.8960094242</v>
       </c>
       <c r="O255" t="n">
-        <v>193025.1524138931</v>
+        <v>177374.4643204228</v>
       </c>
       <c r="P255" t="n">
         <v>8500</v>
       </c>
       <c r="Q255" t="n">
-        <v>314500</v>
+        <v>289000</v>
       </c>
     </row>
     <row r="256">
@@ -11786,10 +11786,10 @@
         <v>279</v>
       </c>
       <c r="N262" t="n">
-        <v>3161.3542590035</v>
+        <v>3158.8608322644</v>
       </c>
       <c r="O262" t="n">
-        <v>882017.8382619765</v>
+        <v>881322.1722017676</v>
       </c>
       <c r="P262" t="n">
         <v>5600</v>
@@ -12101,10 +12101,10 @@
         <v>37</v>
       </c>
       <c r="N269" t="n">
-        <v>1482.16796875</v>
+        <v>1480</v>
       </c>
       <c r="O269" t="n">
-        <v>54840.21484375</v>
+        <v>54760</v>
       </c>
       <c r="P269" t="n">
         <v>2600</v>
@@ -12524,10 +12524,10 @@
         <v>2</v>
       </c>
       <c r="N278" t="n">
-        <v>8807.775100401601</v>
+        <v>8796</v>
       </c>
       <c r="O278" t="n">
-        <v>17615.5502008032</v>
+        <v>17592</v>
       </c>
       <c r="P278" t="n">
         <v>14900</v>
@@ -12831,10 +12831,10 @@
         <v>98</v>
       </c>
       <c r="N285" t="n">
-        <v>2619.5155335628</v>
+        <v>2612.77</v>
       </c>
       <c r="O285" t="n">
-        <v>256712.5222891544</v>
+        <v>256051.46</v>
       </c>
       <c r="P285" t="n">
         <v>4900</v>
@@ -12877,10 +12877,10 @@
         <v>122</v>
       </c>
       <c r="N286" t="n">
-        <v>4362.7231895528</v>
+        <v>4357.55</v>
       </c>
       <c r="O286" t="n">
-        <v>532252.2291254416</v>
+        <v>531621.1</v>
       </c>
       <c r="P286" t="n">
         <v>7500</v>
@@ -12964,10 +12964,10 @@
         <v>24</v>
       </c>
       <c r="N288" t="n">
-        <v>4890.9300496586</v>
+        <v>4890.9300497203</v>
       </c>
       <c r="O288" t="n">
-        <v>117382.3211918064</v>
+        <v>117382.3211932872</v>
       </c>
       <c r="P288" t="n">
         <v>8200</v>
@@ -13411,22 +13411,22 @@
         <v>0</v>
       </c>
       <c r="L298" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M298" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N298" t="n">
-        <v>3594.2535785953</v>
+        <v>3594.2535742972</v>
       </c>
       <c r="O298" t="n">
-        <v>17971.2678929765</v>
+        <v>14377.0142971888</v>
       </c>
       <c r="P298" t="n">
         <v>6500</v>
       </c>
       <c r="Q298" t="n">
-        <v>32500</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="299">
@@ -13512,10 +13512,10 @@
         <v>1</v>
       </c>
       <c r="N300" t="n">
-        <v>500.91436884092</v>
+        <v>489.88</v>
       </c>
       <c r="O300" t="n">
-        <v>500.91436884092</v>
+        <v>489.88</v>
       </c>
       <c r="P300" t="n">
         <v>700</v>
@@ -13732,10 +13732,10 @@
         <v>8</v>
       </c>
       <c r="N305" t="n">
-        <v>14849.377704918</v>
+        <v>14822.378834244</v>
       </c>
       <c r="O305" t="n">
-        <v>118795.021639344</v>
+        <v>118579.030673952</v>
       </c>
       <c r="P305" t="n">
         <v>24900</v>
@@ -14041,10 +14041,10 @@
         <v>7</v>
       </c>
       <c r="N312" t="n">
-        <v>2672.0057001239</v>
+        <v>2665.4</v>
       </c>
       <c r="O312" t="n">
-        <v>18704.0399008673</v>
+        <v>18657.8</v>
       </c>
       <c r="P312" t="n">
         <v>20900</v>
@@ -14630,10 +14630,10 @@
         <v>23</v>
       </c>
       <c r="N325" t="n">
-        <v>3041.6600137268</v>
+        <v>3041.6600137646</v>
       </c>
       <c r="O325" t="n">
-        <v>69958.1803157164</v>
+        <v>69958.1803165858</v>
       </c>
       <c r="P325" t="n">
         <v>5500</v>
@@ -14676,10 +14676,10 @@
         <v>49</v>
       </c>
       <c r="N326" t="n">
-        <v>4372.2107926742</v>
+        <v>4374.7145640659</v>
       </c>
       <c r="O326" t="n">
-        <v>214238.3288410358</v>
+        <v>214361.0136392291</v>
       </c>
       <c r="P326" t="n">
         <v>7500</v>
@@ -15516,10 +15516,10 @@
         <v>11</v>
       </c>
       <c r="N345" t="n">
-        <v>9422.619187996501</v>
+        <v>9414.309999999999</v>
       </c>
       <c r="O345" t="n">
-        <v>103648.8110679615</v>
+        <v>103557.41</v>
       </c>
       <c r="P345" t="n">
         <v>16900</v>
@@ -15873,22 +15873,22 @@
         <v>0</v>
       </c>
       <c r="L353" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M353" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N353" t="n">
-        <v>16960.16635514</v>
+        <v>16897</v>
       </c>
       <c r="O353" t="n">
-        <v>288322.82803738</v>
+        <v>270352</v>
       </c>
       <c r="P353" t="n">
         <v>27900</v>
       </c>
       <c r="Q353" t="n">
-        <v>474300</v>
+        <v>446400</v>
       </c>
     </row>
     <row r="354">
@@ -16247,10 +16247,10 @@
         <v>14</v>
       </c>
       <c r="N361" t="n">
-        <v>11939.712442396</v>
+        <v>11921.4</v>
       </c>
       <c r="O361" t="n">
-        <v>167155.974193544</v>
+        <v>166899.6</v>
       </c>
       <c r="P361" t="n">
         <v>19900</v>
@@ -16563,10 +16563,10 @@
         <v>11</v>
       </c>
       <c r="N368" t="n">
-        <v>9926.065993788799</v>
+        <v>9903</v>
       </c>
       <c r="O368" t="n">
-        <v>109186.7259316768</v>
+        <v>108933</v>
       </c>
       <c r="P368" t="n">
         <v>15900</v>
@@ -16834,10 +16834,10 @@
         <v>29</v>
       </c>
       <c r="N374" t="n">
-        <v>1690.5907183908</v>
+        <v>1830.8887033195</v>
       </c>
       <c r="O374" t="n">
-        <v>49027.1308333332</v>
+        <v>53095.7723962655</v>
       </c>
       <c r="P374" t="n">
         <v>2900</v>
@@ -16880,10 +16880,10 @@
         <v>112</v>
       </c>
       <c r="N375" t="n">
-        <v>1550.194110545</v>
+        <v>1550.1942738685</v>
       </c>
       <c r="O375" t="n">
-        <v>173621.74038104</v>
+        <v>173621.758673272</v>
       </c>
       <c r="P375" t="n">
         <v>2500</v>
@@ -16972,10 +16972,10 @@
         <v>126</v>
       </c>
       <c r="N377" t="n">
-        <v>2403.5145969448</v>
+        <v>2549.7269035153</v>
       </c>
       <c r="O377" t="n">
-        <v>302842.8392150448</v>
+        <v>321265.5898429278</v>
       </c>
       <c r="P377" t="n">
         <v>3500</v>
@@ -18991,10 +18991,10 @@
         <v>11</v>
       </c>
       <c r="N422" t="n">
-        <v>9396.9148264984</v>
+        <v>9338</v>
       </c>
       <c r="O422" t="n">
-        <v>103366.0630914824</v>
+        <v>102718</v>
       </c>
       <c r="P422" t="n">
         <v>15500</v>
@@ -19366,10 +19366,10 @@
         <v>5</v>
       </c>
       <c r="N431" t="n">
-        <v>8799.4430248307</v>
+        <v>8794.48</v>
       </c>
       <c r="O431" t="n">
-        <v>43997.2151241535</v>
+        <v>43972.39999999999</v>
       </c>
       <c r="P431" t="n">
         <v>14500</v>
@@ -19448,10 +19448,10 @@
         <v>39</v>
       </c>
       <c r="N433" t="n">
-        <v>2523.5712699748</v>
+        <v>2517.22</v>
       </c>
       <c r="O433" t="n">
-        <v>98419.27952901721</v>
+        <v>98171.57999999999</v>
       </c>
       <c r="P433" t="n">
         <v>4200</v>
@@ -19901,22 +19901,22 @@
         <v>0</v>
       </c>
       <c r="L444" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M444" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N444" t="n">
         <v>13595</v>
       </c>
       <c r="O444" t="n">
-        <v>81570</v>
+        <v>67975</v>
       </c>
       <c r="P444" t="n">
         <v>20400</v>
       </c>
       <c r="Q444" t="n">
-        <v>122400</v>
+        <v>102000</v>
       </c>
     </row>
     <row r="445">
@@ -19994,10 +19994,10 @@
         <v>3</v>
       </c>
       <c r="N446" t="n">
-        <v>14161.073142857</v>
+        <v>14060.64</v>
       </c>
       <c r="O446" t="n">
-        <v>42483.219428571</v>
+        <v>42181.92</v>
       </c>
       <c r="P446" t="n">
         <v>22900</v>
@@ -20263,10 +20263,10 @@
         <v>1</v>
       </c>
       <c r="N452" t="n">
-        <v>4285.1958660508</v>
+        <v>4285.1959694477</v>
       </c>
       <c r="O452" t="n">
-        <v>4285.1958660508</v>
+        <v>4285.1959694477</v>
       </c>
       <c r="P452" t="n">
         <v>6900</v>
@@ -20691,10 +20691,10 @@
         <v>1</v>
       </c>
       <c r="N462" t="n">
-        <v>12379.333333333</v>
+        <v>11980</v>
       </c>
       <c r="O462" t="n">
-        <v>12379.333333333</v>
+        <v>11980</v>
       </c>
       <c r="P462" t="n">
         <v>19500</v>
@@ -21208,10 +21208,10 @@
         <v>7</v>
       </c>
       <c r="N474" t="n">
-        <v>27871.270433071</v>
+        <v>27123.76496063</v>
       </c>
       <c r="O474" t="n">
-        <v>195098.893031497</v>
+        <v>189866.35472441</v>
       </c>
       <c r="P474" t="n">
         <v>44500</v>
@@ -21254,10 +21254,10 @@
         <v>1</v>
       </c>
       <c r="N475" t="n">
-        <v>17070.322056338</v>
+        <v>16974.69</v>
       </c>
       <c r="O475" t="n">
-        <v>17070.322056338</v>
+        <v>16974.69</v>
       </c>
       <c r="P475" t="n">
         <v>26900</v>
@@ -21295,10 +21295,10 @@
         <v>2</v>
       </c>
       <c r="N476" t="n">
-        <v>4110.4025485437</v>
+        <v>4100.45</v>
       </c>
       <c r="O476" t="n">
-        <v>8220.805097087399</v>
+        <v>8200.9</v>
       </c>
       <c r="P476" t="n">
         <v>26900</v>
@@ -21555,22 +21555,22 @@
         <v>0</v>
       </c>
       <c r="L482" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M482" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N482" t="n">
         <v>4958</v>
       </c>
       <c r="O482" t="n">
-        <v>29748</v>
+        <v>19832</v>
       </c>
       <c r="P482" t="n">
         <v>8500</v>
       </c>
       <c r="Q482" t="n">
-        <v>51000</v>
+        <v>34000</v>
       </c>
     </row>
     <row r="483">
@@ -21688,22 +21688,22 @@
         <v>0</v>
       </c>
       <c r="L485" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M485" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N485" t="n">
         <v>6925.19</v>
       </c>
       <c r="O485" t="n">
-        <v>76177.09</v>
+        <v>62326.71</v>
       </c>
       <c r="P485" t="n">
         <v>12800</v>
       </c>
       <c r="Q485" t="n">
-        <v>140800</v>
+        <v>115200</v>
       </c>
     </row>
     <row r="486">
@@ -24790,10 +24790,10 @@
         <v>3</v>
       </c>
       <c r="N554" t="n">
-        <v>15867.472527473</v>
+        <v>15824</v>
       </c>
       <c r="O554" t="n">
-        <v>47602.417582419</v>
+        <v>47472</v>
       </c>
       <c r="P554" t="n">
         <v>26900</v>
@@ -24964,10 +24964,10 @@
         <v>3</v>
       </c>
       <c r="N558" t="n">
-        <v>3494.4765957447</v>
+        <v>3486</v>
       </c>
       <c r="O558" t="n">
-        <v>10483.4297872341</v>
+        <v>10458</v>
       </c>
       <c r="P558" t="n">
         <v>6900</v>
@@ -25004,22 +25004,22 @@
         <v>0</v>
       </c>
       <c r="L559" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M559" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="N559" t="n">
-        <v>1778.4727221703</v>
+        <v>1778.4727234441</v>
       </c>
       <c r="O559" t="n">
-        <v>106708.363330218</v>
+        <v>101372.9452363137</v>
       </c>
       <c r="P559" t="n">
         <v>4900</v>
       </c>
       <c r="Q559" t="n">
-        <v>294000</v>
+        <v>279300</v>
       </c>
     </row>
     <row r="560">
@@ -27138,10 +27138,10 @@
         <v>19</v>
       </c>
       <c r="N605" t="n">
-        <v>8872.340618996799</v>
+        <v>8858.16</v>
       </c>
       <c r="O605" t="n">
-        <v>168574.4717609392</v>
+        <v>168305.04</v>
       </c>
       <c r="P605" t="n">
         <v>15500</v>
@@ -27594,10 +27594,10 @@
         <v>95</v>
       </c>
       <c r="N615" t="n">
-        <v>2336.84913125</v>
+        <v>2328.11868125</v>
       </c>
       <c r="O615" t="n">
-        <v>222000.66746875</v>
+        <v>221171.27471875</v>
       </c>
       <c r="P615" t="n">
         <v>4500</v>
@@ -27873,10 +27873,10 @@
         <v>6</v>
       </c>
       <c r="N621" t="n">
-        <v>35287.397849462</v>
+        <v>34912</v>
       </c>
       <c r="O621" t="n">
-        <v>211724.387096772</v>
+        <v>209472</v>
       </c>
       <c r="P621" t="n">
         <v>56900</v>
@@ -28609,10 +28609,10 @@
         <v>71</v>
       </c>
       <c r="N637" t="n">
-        <v>3922.9680788177</v>
+        <v>3903.7379310345</v>
       </c>
       <c r="O637" t="n">
-        <v>278530.7335960567</v>
+        <v>277165.3931034495</v>
       </c>
       <c r="P637" t="n">
         <v>7500</v>
@@ -28655,10 +28655,10 @@
         <v>3</v>
       </c>
       <c r="N638" t="n">
-        <v>33317.307692308</v>
+        <v>33000</v>
       </c>
       <c r="O638" t="n">
-        <v>99951.92307692399</v>
+        <v>99000</v>
       </c>
       <c r="P638" t="n">
         <v>52900</v>
@@ -29115,10 +29115,10 @@
         <v>11</v>
       </c>
       <c r="N648" t="n">
-        <v>9751.4516129032</v>
+        <v>8637</v>
       </c>
       <c r="O648" t="n">
-        <v>107265.9677419352</v>
+        <v>95007</v>
       </c>
       <c r="P648" t="n">
         <v>14500</v>
@@ -29391,10 +29391,10 @@
         <v>5</v>
       </c>
       <c r="N654" t="n">
-        <v>7668.5070422535</v>
+        <v>7562</v>
       </c>
       <c r="O654" t="n">
-        <v>38342.5352112675</v>
+        <v>37810</v>
       </c>
       <c r="P654" t="n">
         <v>12900</v>
@@ -29437,10 +29437,10 @@
         <v>12</v>
       </c>
       <c r="N655" t="n">
-        <v>3901.1562753036</v>
+        <v>3898</v>
       </c>
       <c r="O655" t="n">
-        <v>46813.8753036432</v>
+        <v>46776</v>
       </c>
       <c r="P655" t="n">
         <v>6900</v>
@@ -29483,10 +29483,10 @@
         <v>27</v>
       </c>
       <c r="N656" t="n">
-        <v>13606.546707504</v>
+        <v>13565</v>
       </c>
       <c r="O656" t="n">
-        <v>367376.761102608</v>
+        <v>366255</v>
       </c>
       <c r="P656" t="n">
         <v>22500</v>
@@ -29529,10 +29529,10 @@
         <v>15</v>
       </c>
       <c r="N657" t="n">
-        <v>7647.7960893855</v>
+        <v>7635</v>
       </c>
       <c r="O657" t="n">
-        <v>114716.9413407825</v>
+        <v>114525</v>
       </c>
       <c r="P657" t="n">
         <v>13900</v>
@@ -29575,10 +29575,10 @@
         <v>2</v>
       </c>
       <c r="N658" t="n">
-        <v>5690.8504672897</v>
+        <v>5682</v>
       </c>
       <c r="O658" t="n">
-        <v>11381.7009345794</v>
+        <v>11364</v>
       </c>
       <c r="P658" t="n">
         <v>9900</v>
@@ -29621,10 +29621,10 @@
         <v>6</v>
       </c>
       <c r="N659" t="n">
-        <v>5465.19</v>
+        <v>5438</v>
       </c>
       <c r="O659" t="n">
-        <v>32791.14</v>
+        <v>32628</v>
       </c>
       <c r="P659" t="n">
         <v>8900</v>
@@ -30442,10 +30442,10 @@
         <v>59</v>
       </c>
       <c r="N677" t="n">
-        <v>5319.824120603</v>
+        <v>5215</v>
       </c>
       <c r="O677" t="n">
-        <v>313869.623115577</v>
+        <v>307685</v>
       </c>
       <c r="P677" t="n">
         <v>8900</v>
@@ -31224,10 +31224,10 @@
         <v>50</v>
       </c>
       <c r="N694" t="n">
-        <v>5483.2964690207</v>
+        <v>5476</v>
       </c>
       <c r="O694" t="n">
-        <v>274164.823451035</v>
+        <v>273800</v>
       </c>
       <c r="P694" t="n">
         <v>8900</v>
@@ -32150,10 +32150,10 @@
         <v>1</v>
       </c>
       <c r="N714" t="n">
-        <v>1592.2821517241</v>
+        <v>1789.7745116279</v>
       </c>
       <c r="O714" t="n">
-        <v>1592.2821517241</v>
+        <v>1789.7745116279</v>
       </c>
       <c r="P714" t="n">
         <v>2500</v>
@@ -37182,10 +37182,10 @@
         <v>17</v>
       </c>
       <c r="N822" t="n">
-        <v>3110.839841954</v>
+        <v>3110.8397979798</v>
       </c>
       <c r="O822" t="n">
-        <v>52884.277313218</v>
+        <v>52884.2765656566</v>
       </c>
       <c r="P822" t="n">
         <v>4500</v>
@@ -42617,22 +42617,22 @@
         <v>0</v>
       </c>
       <c r="L936" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M936" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N936" t="n">
         <v>5697.97</v>
       </c>
       <c r="O936" t="n">
-        <v>11395.94</v>
+        <v>5697.97</v>
       </c>
       <c r="P936" t="n">
         <v>19500</v>
       </c>
       <c r="Q936" t="n">
-        <v>39000</v>
+        <v>19500</v>
       </c>
     </row>
     <row r="937">
@@ -42813,22 +42813,22 @@
         <v>0</v>
       </c>
       <c r="L940" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M940" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="N940" t="n">
         <v>2320.4</v>
       </c>
       <c r="O940" t="n">
-        <v>74252.8</v>
+        <v>67291.60000000001</v>
       </c>
       <c r="P940" t="n">
         <v>4600</v>
       </c>
       <c r="Q940" t="n">
-        <v>147200</v>
+        <v>133400</v>
       </c>
     </row>
     <row r="941">
@@ -43396,10 +43396,10 @@
         <v>6</v>
       </c>
       <c r="N952" t="n">
-        <v>3098.3874489796</v>
+        <v>3067.0906122449</v>
       </c>
       <c r="O952" t="n">
-        <v>18590.3246938776</v>
+        <v>18402.5436734694</v>
       </c>
       <c r="P952" t="n">
         <v>7200</v>
@@ -44651,10 +44651,10 @@
         <v>4</v>
       </c>
       <c r="N978" t="n">
-        <v>10993.181190476</v>
+        <v>10737.525714286</v>
       </c>
       <c r="O978" t="n">
-        <v>43972.724761904</v>
+        <v>42950.102857144</v>
       </c>
       <c r="P978" t="n">
         <v>18900</v>
@@ -53219,10 +53219,10 @@
         <v>3</v>
       </c>
       <c r="N1161" t="n">
-        <v>17225.733333333</v>
+        <v>10335.44</v>
       </c>
       <c r="O1161" t="n">
-        <v>51677.19999999899</v>
+        <v>31006.32</v>
       </c>
       <c r="P1161" t="n">
         <v>10900</v>
@@ -53489,22 +53489,22 @@
         <v>0</v>
       </c>
       <c r="L1167" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1167" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N1167" t="n">
         <v>5120.05</v>
       </c>
       <c r="O1167" t="n">
-        <v>20480.2</v>
+        <v>10240.1</v>
       </c>
       <c r="P1167" t="n">
         <v>5700</v>
       </c>
       <c r="Q1167" t="n">
-        <v>22800</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="1168">
@@ -53525,22 +53525,22 @@
         <v>0</v>
       </c>
       <c r="L1168" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1168" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N1168" t="n">
         <v>3885.95</v>
       </c>
       <c r="O1168" t="n">
-        <v>7771.9</v>
+        <v>0</v>
       </c>
       <c r="P1168" t="n">
         <v>6700</v>
       </c>
       <c r="Q1168" t="n">
-        <v>13400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1169">
@@ -55368,22 +55368,22 @@
         <v>0</v>
       </c>
       <c r="L1208" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1208" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N1208" t="n">
-        <v>4598.7284768212</v>
+        <v>4576</v>
       </c>
       <c r="O1208" t="n">
-        <v>22993.642384106</v>
+        <v>13728</v>
       </c>
       <c r="P1208" t="n">
         <v>5900</v>
       </c>
       <c r="Q1208" t="n">
-        <v>29500</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="1209">
@@ -55414,22 +55414,22 @@
         <v>0</v>
       </c>
       <c r="L1209" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1209" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N1209" t="n">
         <v>5280</v>
       </c>
       <c r="O1209" t="n">
-        <v>47520</v>
+        <v>36960</v>
       </c>
       <c r="P1209" t="n">
         <v>6900</v>
       </c>
       <c r="Q1209" t="n">
-        <v>62100</v>
+        <v>48300</v>
       </c>
     </row>
     <row r="1210">
@@ -58349,22 +58349,22 @@
         <v>0</v>
       </c>
       <c r="L1272" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1272" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="N1272" t="n">
         <v>6272.36</v>
       </c>
       <c r="O1272" t="n">
-        <v>156809</v>
+        <v>137991.92</v>
       </c>
       <c r="P1272" t="n">
         <v>10500</v>
       </c>
       <c r="Q1272" t="n">
-        <v>262500</v>
+        <v>231000</v>
       </c>
     </row>
     <row r="1273">
@@ -58533,22 +58533,22 @@
         <v>0</v>
       </c>
       <c r="L1276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1276" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N1276" t="n">
         <v>9046.99</v>
       </c>
       <c r="O1276" t="n">
-        <v>27140.97</v>
+        <v>18093.98</v>
       </c>
       <c r="P1276" t="n">
         <v>22500</v>
       </c>
       <c r="Q1276" t="n">
-        <v>67500</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="1277">
@@ -58773,22 +58773,22 @@
         <v>0</v>
       </c>
       <c r="L1281" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1281" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N1281" t="n">
-        <v>3088.1445833333</v>
+        <v>3088.1452173913</v>
       </c>
       <c r="O1281" t="n">
-        <v>37057.7349999996</v>
+        <v>30881.452173913</v>
       </c>
       <c r="P1281" t="n">
         <v>8500</v>
       </c>
       <c r="Q1281" t="n">
-        <v>102000</v>
+        <v>85000</v>
       </c>
     </row>
     <row r="1282">
@@ -66262,22 +66262,22 @@
         <v>0</v>
       </c>
       <c r="L1444" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1444" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N1444" t="n">
-        <v>7046.7388888889</v>
+        <v>7046.7392307692</v>
       </c>
       <c r="O1444" t="n">
-        <v>21140.2166666667</v>
+        <v>14093.4784615384</v>
       </c>
       <c r="P1444" t="n">
         <v>22900</v>
       </c>
       <c r="Q1444" t="n">
-        <v>68700</v>
+        <v>45800</v>
       </c>
     </row>
     <row r="1445">
@@ -66682,10 +66682,10 @@
         <v>9</v>
       </c>
       <c r="N1453" t="n">
-        <v>3732.8768115942</v>
+        <v>4365.5677966102</v>
       </c>
       <c r="O1453" t="n">
-        <v>33595.8913043478</v>
+        <v>39290.1101694918</v>
       </c>
       <c r="P1453" t="n">
         <v>4500</v>
@@ -66820,10 +66820,10 @@
         <v>8</v>
       </c>
       <c r="N1456" t="n">
-        <v>4566.0211267606</v>
+        <v>4550</v>
       </c>
       <c r="O1456" t="n">
-        <v>36528.1690140848</v>
+        <v>36400</v>
       </c>
       <c r="P1456" t="n">
         <v>5500</v>

--- a/bodegas/02.xlsx
+++ b/bodegas/02.xlsx
@@ -11360,22 +11360,22 @@
         <v>0</v>
       </c>
       <c r="L253" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M253" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="N253" t="n">
-        <v>2582.2554027233</v>
+        <v>2582.2553995381</v>
       </c>
       <c r="O253" t="n">
-        <v>51645.108054466</v>
+        <v>43898.3417921477</v>
       </c>
       <c r="P253" t="n">
         <v>4500</v>
       </c>
       <c r="Q253" t="n">
-        <v>90000</v>
+        <v>76500</v>
       </c>
     </row>
     <row r="254">
@@ -12008,22 +12008,22 @@
         <v>0</v>
       </c>
       <c r="L267" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M267" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="N267" t="n">
-        <v>3230.0666176471</v>
+        <v>3230.0665925926</v>
       </c>
       <c r="O267" t="n">
-        <v>129202.664705884</v>
+        <v>119512.4639259262</v>
       </c>
       <c r="P267" t="n">
         <v>6200</v>
       </c>
       <c r="Q267" t="n">
-        <v>248000</v>
+        <v>229400</v>
       </c>
     </row>
     <row r="268">
@@ -12871,22 +12871,22 @@
         <v>0</v>
       </c>
       <c r="L286" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M286" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="N286" t="n">
         <v>4357.55</v>
       </c>
       <c r="O286" t="n">
-        <v>531621.1</v>
+        <v>518548.45</v>
       </c>
       <c r="P286" t="n">
         <v>7500</v>
       </c>
       <c r="Q286" t="n">
-        <v>915000</v>
+        <v>892500</v>
       </c>
     </row>
     <row r="287">
@@ -13639,22 +13639,22 @@
         <v>0</v>
       </c>
       <c r="L303" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M303" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="N303" t="n">
         <v>2953.73</v>
       </c>
       <c r="O303" t="n">
-        <v>183131.26</v>
+        <v>147686.5</v>
       </c>
       <c r="P303" t="n">
         <v>4900</v>
       </c>
       <c r="Q303" t="n">
-        <v>303800</v>
+        <v>245000</v>
       </c>
     </row>
     <row r="304">
@@ -15108,22 +15108,22 @@
         <v>0</v>
       </c>
       <c r="L336" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M336" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="N336" t="n">
         <v>6242.93</v>
       </c>
       <c r="O336" t="n">
-        <v>106129.81</v>
+        <v>87401.02</v>
       </c>
       <c r="P336" t="n">
         <v>10400</v>
       </c>
       <c r="Q336" t="n">
-        <v>176800</v>
+        <v>145600</v>
       </c>
     </row>
     <row r="337">
@@ -16247,10 +16247,10 @@
         <v>17</v>
       </c>
       <c r="N361" t="n">
-        <v>11921.4</v>
+        <v>11949.297191888</v>
       </c>
       <c r="O361" t="n">
-        <v>202663.8</v>
+        <v>203138.052262096</v>
       </c>
       <c r="P361" t="n">
         <v>19900</v>
@@ -16742,10 +16742,10 @@
         <v>203</v>
       </c>
       <c r="N372" t="n">
-        <v>1630.9240698598</v>
+        <v>1630.9240720148</v>
       </c>
       <c r="O372" t="n">
-        <v>331077.5861815394</v>
+        <v>331077.5866190044</v>
       </c>
       <c r="P372" t="n">
         <v>2500</v>
@@ -16880,10 +16880,10 @@
         <v>112</v>
       </c>
       <c r="N375" t="n">
-        <v>1550.1941645158</v>
+        <v>1550.1941668538</v>
       </c>
       <c r="O375" t="n">
-        <v>173621.7464257696</v>
+        <v>173621.7466876256</v>
       </c>
       <c r="P375" t="n">
         <v>2500</v>
@@ -16966,22 +16966,22 @@
         <v>0</v>
       </c>
       <c r="L377" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M377" t="n">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="N377" t="n">
-        <v>2403.5147075539</v>
+        <v>2403.51472848</v>
       </c>
       <c r="O377" t="n">
-        <v>302842.8531517914</v>
+        <v>288421.7674176</v>
       </c>
       <c r="P377" t="n">
         <v>3500</v>
       </c>
       <c r="Q377" t="n">
-        <v>441000</v>
+        <v>420000</v>
       </c>
     </row>
     <row r="378">
@@ -19442,22 +19442,22 @@
         <v>0</v>
       </c>
       <c r="L433" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M433" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="N433" t="n">
         <v>2517.22</v>
       </c>
       <c r="O433" t="n">
-        <v>98171.57999999999</v>
+        <v>83068.25999999999</v>
       </c>
       <c r="P433" t="n">
         <v>4200</v>
       </c>
       <c r="Q433" t="n">
-        <v>163800</v>
+        <v>138600</v>
       </c>
     </row>
     <row r="434">
@@ -21341,10 +21341,10 @@
         <v>5</v>
       </c>
       <c r="N477" t="n">
-        <v>8332.779613402099</v>
+        <v>8397.710363636401</v>
       </c>
       <c r="O477" t="n">
-        <v>41663.89806701049</v>
+        <v>41988.55181818201</v>
       </c>
       <c r="P477" t="n">
         <v>14900</v>
@@ -28557,22 +28557,22 @@
         <v>0</v>
       </c>
       <c r="L636" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M636" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="N636" t="n">
-        <v>3903.7383067896</v>
+        <v>3903.7383529412</v>
       </c>
       <c r="O636" t="n">
-        <v>277165.4197820616</v>
+        <v>265454.2080000016</v>
       </c>
       <c r="P636" t="n">
         <v>7500</v>
       </c>
       <c r="Q636" t="n">
-        <v>532500</v>
+        <v>510000</v>
       </c>
     </row>
     <row r="637">
@@ -32104,10 +32104,10 @@
         <v>1</v>
       </c>
       <c r="N713" t="n">
-        <v>1592.2821517241</v>
+        <v>1592.2821853389</v>
       </c>
       <c r="O713" t="n">
-        <v>1592.2821517241</v>
+        <v>1592.2821853389</v>
       </c>
       <c r="P713" t="n">
         <v>2500</v>
@@ -36525,22 +36525,22 @@
         <v>0</v>
       </c>
       <c r="L808" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M808" t="n">
-        <v>759</v>
+        <v>687</v>
       </c>
       <c r="N808" t="n">
-        <v>517.29287307808</v>
+        <v>517.2929433161599</v>
       </c>
       <c r="O808" t="n">
-        <v>392625.2906662627</v>
+        <v>355380.2520582019</v>
       </c>
       <c r="P808" t="n">
         <v>900</v>
       </c>
       <c r="Q808" t="n">
-        <v>683100</v>
+        <v>618300</v>
       </c>
     </row>
     <row r="809">
@@ -37130,22 +37130,22 @@
         <v>0</v>
       </c>
       <c r="L821" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M821" t="n">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="N821" t="n">
-        <v>3110.8397028838</v>
+        <v>3110.8396848556</v>
       </c>
       <c r="O821" t="n">
-        <v>407520.0010777778</v>
+        <v>388854.96060695</v>
       </c>
       <c r="P821" t="n">
         <v>4500</v>
       </c>
       <c r="Q821" t="n">
-        <v>589500</v>
+        <v>562500</v>
       </c>
     </row>
     <row r="822">
@@ -40295,25 +40295,25 @@
         <v>3</v>
       </c>
       <c r="K888" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="L888" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M888" t="n">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="N888" t="n">
         <v>3057.26</v>
       </c>
       <c r="O888" t="n">
-        <v>9171.780000000001</v>
+        <v>134519.44</v>
       </c>
       <c r="P888" t="n">
         <v>4900</v>
       </c>
       <c r="Q888" t="n">
-        <v>14700</v>
+        <v>215600</v>
       </c>
     </row>
     <row r="889">
@@ -54918,22 +54918,22 @@
         <v>0</v>
       </c>
       <c r="L1198" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M1198" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="N1198" t="n">
         <v>6336</v>
       </c>
       <c r="O1198" t="n">
-        <v>348480</v>
+        <v>323136</v>
       </c>
       <c r="P1198" t="n">
         <v>7500</v>
       </c>
       <c r="Q1198" t="n">
-        <v>412500</v>
+        <v>382500</v>
       </c>
     </row>
     <row r="1199">
@@ -55148,22 +55148,22 @@
         <v>0</v>
       </c>
       <c r="L1203" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1203" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="N1203" t="n">
         <v>4400</v>
       </c>
       <c r="O1203" t="n">
-        <v>127600</v>
+        <v>114400</v>
       </c>
       <c r="P1203" t="n">
         <v>5900</v>
       </c>
       <c r="Q1203" t="n">
-        <v>171100</v>
+        <v>153400</v>
       </c>
     </row>
     <row r="1204">

--- a/bodegas/02.xlsx
+++ b/bodegas/02.xlsx
@@ -12604,7 +12604,7 @@
         </is>
       </c>
       <c r="J280" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="K280" t="n">
         <v>0</v>
@@ -12613,19 +12613,19 @@
         <v>0</v>
       </c>
       <c r="M280" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="N280" t="n">
         <v>5002</v>
       </c>
       <c r="O280" t="n">
-        <v>30012</v>
+        <v>130052</v>
       </c>
       <c r="P280" t="n">
         <v>8400</v>
       </c>
       <c r="Q280" t="n">
-        <v>50400</v>
+        <v>218400</v>
       </c>
     </row>
     <row r="281">
@@ -16969,10 +16969,10 @@
         <v>116</v>
       </c>
       <c r="N377" t="n">
-        <v>2403.515543043</v>
+        <v>2403.5155820371</v>
       </c>
       <c r="O377" t="n">
-        <v>278807.802992988</v>
+        <v>278807.8075163036</v>
       </c>
       <c r="P377" t="n">
         <v>3500</v>
@@ -37133,10 +37133,10 @@
         <v>125</v>
       </c>
       <c r="N821" t="n">
-        <v>3110.8396334311</v>
+        <v>3110.8396273474</v>
       </c>
       <c r="O821" t="n">
-        <v>388854.9541788875</v>
+        <v>388854.953418425</v>
       </c>
       <c r="P821" t="n">
         <v>4500</v>
@@ -37364,10 +37364,10 @@
         <v>339</v>
       </c>
       <c r="N826" t="n">
-        <v>703.79488487659</v>
+        <v>703.79488357273</v>
       </c>
       <c r="O826" t="n">
-        <v>238586.465973164</v>
+        <v>238586.4655311555</v>
       </c>
       <c r="P826" t="n">
         <v>900</v>

--- a/bodegas/02.xlsx
+++ b/bodegas/02.xlsx
@@ -771,10 +771,10 @@
         <v>6</v>
       </c>
       <c r="N9" t="n">
-        <v>27108.144192256</v>
+        <v>27000</v>
       </c>
       <c r="O9" t="n">
-        <v>162648.865153536</v>
+        <v>162000</v>
       </c>
       <c r="P9" t="n">
         <v>20000</v>
@@ -895,10 +895,10 @@
         <v>3</v>
       </c>
       <c r="N12" t="n">
-        <v>27117.391304348</v>
+        <v>27000</v>
       </c>
       <c r="O12" t="n">
-        <v>81352.173913044</v>
+        <v>81000</v>
       </c>
       <c r="P12" t="n">
         <v>30000</v>
@@ -11504,10 +11504,10 @@
         <v>32</v>
       </c>
       <c r="N256" t="n">
-        <v>5224.6087374335</v>
+        <v>5216.895993495</v>
       </c>
       <c r="O256" t="n">
-        <v>167187.479597872</v>
+        <v>166940.67179184</v>
       </c>
       <c r="P256" t="n">
         <v>8500</v>
@@ -13732,10 +13732,10 @@
         <v>7</v>
       </c>
       <c r="N305" t="n">
-        <v>14831.411358927</v>
+        <v>14822.378829982</v>
       </c>
       <c r="O305" t="n">
-        <v>103819.879512489</v>
+        <v>103756.651809874</v>
       </c>
       <c r="P305" t="n">
         <v>24900</v>
@@ -14586,10 +14586,10 @@
         <v>6</v>
       </c>
       <c r="N324" t="n">
-        <v>15071.76</v>
+        <v>14386.68</v>
       </c>
       <c r="O324" t="n">
-        <v>90430.56</v>
+        <v>86320.08</v>
       </c>
       <c r="P324" t="n">
         <v>21900</v>
@@ -16293,10 +16293,10 @@
         <v>17</v>
       </c>
       <c r="N362" t="n">
-        <v>11959.066350711</v>
+        <v>11921.4</v>
       </c>
       <c r="O362" t="n">
-        <v>203304.127962087</v>
+        <v>202663.8</v>
       </c>
       <c r="P362" t="n">
         <v>19900</v>
@@ -18092,10 +18092,10 @@
         <v>7</v>
       </c>
       <c r="N402" t="n">
-        <v>10907.343571429</v>
+        <v>10836.973636364</v>
       </c>
       <c r="O402" t="n">
-        <v>76351.40500000301</v>
+        <v>75858.81545454801</v>
       </c>
       <c r="P402" t="n">
         <v>19900</v>
@@ -18991,10 +18991,10 @@
         <v>11</v>
       </c>
       <c r="N422" t="n">
-        <v>9460.065359477099</v>
+        <v>9338</v>
       </c>
       <c r="O422" t="n">
-        <v>104060.7189542481</v>
+        <v>102718</v>
       </c>
       <c r="P422" t="n">
         <v>15500</v>
@@ -19530,10 +19530,10 @@
         <v>9</v>
       </c>
       <c r="N435" t="n">
-        <v>22541.90975</v>
+        <v>22485.6955</v>
       </c>
       <c r="O435" t="n">
-        <v>202877.18775</v>
+        <v>202371.2595</v>
       </c>
       <c r="P435" t="n">
         <v>36500</v>
@@ -19612,10 +19612,10 @@
         <v>1</v>
       </c>
       <c r="N437" t="n">
-        <v>39703.055555556</v>
+        <v>38630</v>
       </c>
       <c r="O437" t="n">
-        <v>39703.055555556</v>
+        <v>38630</v>
       </c>
       <c r="P437" t="n">
         <v>46500</v>
@@ -19702,10 +19702,10 @@
         <v>11</v>
       </c>
       <c r="N439" t="n">
-        <v>24573.894298246</v>
+        <v>24538.02</v>
       </c>
       <c r="O439" t="n">
-        <v>270312.837280706</v>
+        <v>269918.22</v>
       </c>
       <c r="P439" t="n">
         <v>52900</v>
@@ -20691,10 +20691,10 @@
         <v>1</v>
       </c>
       <c r="N462" t="n">
-        <v>12393.103448276</v>
+        <v>11980</v>
       </c>
       <c r="O462" t="n">
-        <v>12393.103448276</v>
+        <v>11980</v>
       </c>
       <c r="P462" t="n">
         <v>19500</v>
@@ -21167,10 +21167,10 @@
         <v>7</v>
       </c>
       <c r="N473" t="n">
-        <v>27232.25996</v>
+        <v>27123.76488</v>
       </c>
       <c r="O473" t="n">
-        <v>190625.81972</v>
+        <v>189866.35416</v>
       </c>
       <c r="P473" t="n">
         <v>44500</v>
@@ -21566,10 +21566,10 @@
         <v>13</v>
       </c>
       <c r="N482" t="n">
-        <v>27011.040935673</v>
+        <v>26854</v>
       </c>
       <c r="O482" t="n">
-        <v>351143.532163749</v>
+        <v>349102</v>
       </c>
       <c r="P482" t="n">
         <v>43900</v>
@@ -22613,10 +22613,10 @@
         <v>15</v>
       </c>
       <c r="N506" t="n">
-        <v>13079.564264151</v>
+        <v>12981.59</v>
       </c>
       <c r="O506" t="n">
-        <v>196193.463962265</v>
+        <v>194723.85</v>
       </c>
       <c r="P506" t="n">
         <v>21900</v>
@@ -27832,10 +27832,10 @@
         <v>10</v>
       </c>
       <c r="N620" t="n">
-        <v>9198.3277962348</v>
+        <v>9178</v>
       </c>
       <c r="O620" t="n">
-        <v>91983.277962348</v>
+        <v>91780</v>
       </c>
       <c r="P620" t="n">
         <v>14900</v>
@@ -27878,10 +27878,10 @@
         <v>116</v>
       </c>
       <c r="N621" t="n">
-        <v>4567.8948290973</v>
+        <v>4544</v>
       </c>
       <c r="O621" t="n">
-        <v>529875.8001752868</v>
+        <v>527104</v>
       </c>
       <c r="P621" t="n">
         <v>7900</v>
@@ -27970,10 +27970,10 @@
         <v>20</v>
       </c>
       <c r="N623" t="n">
-        <v>13948.467680608</v>
+        <v>13922</v>
       </c>
       <c r="O623" t="n">
-        <v>278969.35361216</v>
+        <v>278440</v>
       </c>
       <c r="P623" t="n">
         <v>22900</v>
@@ -28062,10 +28062,10 @@
         <v>12</v>
       </c>
       <c r="N625" t="n">
-        <v>25260.382352941</v>
+        <v>25076</v>
       </c>
       <c r="O625" t="n">
-        <v>303124.588235292</v>
+        <v>300912</v>
       </c>
       <c r="P625" t="n">
         <v>40900</v>
@@ -28936,10 +28936,10 @@
         <v>4</v>
       </c>
       <c r="N644" t="n">
-        <v>14306.769230769</v>
+        <v>14090</v>
       </c>
       <c r="O644" t="n">
-        <v>57227.076923076</v>
+        <v>56360</v>
       </c>
       <c r="P644" t="n">
         <v>22900</v>
@@ -29028,10 +29028,10 @@
         <v>14</v>
       </c>
       <c r="N646" t="n">
-        <v>13121.945155393</v>
+        <v>13098</v>
       </c>
       <c r="O646" t="n">
-        <v>183707.232175502</v>
+        <v>183372</v>
       </c>
       <c r="P646" t="n">
         <v>21200</v>
@@ -29718,10 +29718,10 @@
         <v>30</v>
       </c>
       <c r="N661" t="n">
-        <v>17123.621290098</v>
+        <v>17075.989518828</v>
       </c>
       <c r="O661" t="n">
-        <v>513708.63870294</v>
+        <v>512279.68556484</v>
       </c>
       <c r="P661" t="n">
         <v>27500</v>
@@ -30079,10 +30079,10 @@
         <v>6</v>
       </c>
       <c r="N669" t="n">
-        <v>17325.987730061</v>
+        <v>17168</v>
       </c>
       <c r="O669" t="n">
-        <v>103955.926380366</v>
+        <v>103008</v>
       </c>
       <c r="P669" t="n">
         <v>27900</v>
@@ -30125,10 +30125,10 @@
         <v>2</v>
       </c>
       <c r="N670" t="n">
-        <v>27289.075933076</v>
+        <v>27254</v>
       </c>
       <c r="O670" t="n">
-        <v>54578.151866152</v>
+        <v>54508</v>
       </c>
       <c r="P670" t="n">
         <v>43900</v>
@@ -30355,10 +30355,10 @@
         <v>30</v>
       </c>
       <c r="N675" t="n">
-        <v>40316.604863222</v>
+        <v>40073</v>
       </c>
       <c r="O675" t="n">
-        <v>1209498.14589666</v>
+        <v>1202190</v>
       </c>
       <c r="P675" t="n">
         <v>64900</v>
@@ -39739,10 +39739,10 @@
         <v>1</v>
       </c>
       <c r="N876" t="n">
-        <v>10639.697586207</v>
+        <v>10548.76</v>
       </c>
       <c r="O876" t="n">
-        <v>10639.697586207</v>
+        <v>10548.76</v>
       </c>
       <c r="P876" t="n">
         <v>35900</v>
@@ -43988,10 +43988,10 @@
         <v>6</v>
       </c>
       <c r="N964" t="n">
-        <v>2830.7108053691</v>
+        <v>2356.29</v>
       </c>
       <c r="O964" t="n">
-        <v>16984.2648322146</v>
+        <v>14137.74</v>
       </c>
       <c r="P964" t="n">
         <v>6500</v>
